--- a/display/EcoGainsSim_Daily_v2.xlsx
+++ b/display/EcoGainsSim_Daily_v2.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:CJ51"/>
+  <dimension ref="B1:CX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.75" customWidth="1" min="1" max="1"/>
@@ -615,9 +615,9 @@
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="2.88" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
     <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="2.88" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
@@ -627,11 +627,11 @@
     <col width="8" customWidth="1" min="24" max="24"/>
     <col width="8" customWidth="1" min="25" max="25"/>
     <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="2.88" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
     <col width="8" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
     <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="2.88" customWidth="1" min="31" max="31"/>
     <col width="8" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="8" customWidth="1" min="34" max="34"/>
@@ -639,19 +639,19 @@
     <col width="8" customWidth="1" min="36" max="36"/>
     <col width="8" customWidth="1" min="37" max="37"/>
     <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="2.88" customWidth="1" min="39" max="39"/>
+    <col width="8" customWidth="1" min="39" max="39"/>
     <col width="8" customWidth="1" min="40" max="40"/>
     <col width="8" customWidth="1" min="41" max="41"/>
     <col width="8" customWidth="1" min="42" max="42"/>
     <col width="8" customWidth="1" min="43" max="43"/>
     <col width="8" customWidth="1" min="44" max="44"/>
-    <col width="8" customWidth="1" min="45" max="45"/>
+    <col width="2.88" customWidth="1" min="45" max="45"/>
     <col width="8" customWidth="1" min="46" max="46"/>
     <col width="8" customWidth="1" min="47" max="47"/>
     <col width="8" customWidth="1" min="48" max="48"/>
     <col width="8" customWidth="1" min="49" max="49"/>
     <col width="8" customWidth="1" min="50" max="50"/>
-    <col width="2.88" customWidth="1" min="51" max="51"/>
+    <col width="8" customWidth="1" min="51" max="51"/>
     <col width="8" customWidth="1" min="52" max="52"/>
     <col width="8" customWidth="1" min="53" max="53"/>
     <col width="8" customWidth="1" min="54" max="54"/>
@@ -659,11 +659,11 @@
     <col width="8" customWidth="1" min="56" max="56"/>
     <col width="8" customWidth="1" min="57" max="57"/>
     <col width="8" customWidth="1" min="58" max="58"/>
-    <col width="8" customWidth="1" min="59" max="59"/>
+    <col width="2.88" customWidth="1" min="59" max="59"/>
     <col width="8" customWidth="1" min="60" max="60"/>
     <col width="8" customWidth="1" min="61" max="61"/>
     <col width="8" customWidth="1" min="62" max="62"/>
-    <col width="2.88" customWidth="1" min="63" max="63"/>
+    <col width="8" customWidth="1" min="63" max="63"/>
     <col width="8" customWidth="1" min="64" max="64"/>
     <col width="8" customWidth="1" min="65" max="65"/>
     <col width="8" customWidth="1" min="66" max="66"/>
@@ -673,9 +673,9 @@
     <col width="8" customWidth="1" min="70" max="70"/>
     <col width="8" customWidth="1" min="71" max="71"/>
     <col width="8" customWidth="1" min="72" max="72"/>
-    <col width="8" customWidth="1" min="73" max="73"/>
+    <col width="2.88" customWidth="1" min="73" max="73"/>
     <col width="8" customWidth="1" min="74" max="74"/>
-    <col width="2.88" customWidth="1" min="75" max="75"/>
+    <col width="8" customWidth="1" min="75" max="75"/>
     <col width="8" customWidth="1" min="76" max="76"/>
     <col width="8" customWidth="1" min="77" max="77"/>
     <col width="8" customWidth="1" min="78" max="78"/>
@@ -688,7 +688,21 @@
     <col width="8" customWidth="1" min="85" max="85"/>
     <col width="8" customWidth="1" min="86" max="86"/>
     <col width="2.88" customWidth="1" min="87" max="87"/>
-    <col width="21" customWidth="1" min="88" max="88"/>
+    <col width="8" customWidth="1" min="88" max="88"/>
+    <col width="8" customWidth="1" min="89" max="89"/>
+    <col width="8" customWidth="1" min="90" max="90"/>
+    <col width="8" customWidth="1" min="91" max="91"/>
+    <col width="8" customWidth="1" min="92" max="92"/>
+    <col width="8" customWidth="1" min="93" max="93"/>
+    <col width="8" customWidth="1" min="94" max="94"/>
+    <col width="8" customWidth="1" min="95" max="95"/>
+    <col width="8" customWidth="1" min="96" max="96"/>
+    <col width="8" customWidth="1" min="97" max="97"/>
+    <col width="8" customWidth="1" min="98" max="98"/>
+    <col width="8" customWidth="1" min="99" max="99"/>
+    <col width="8" customWidth="1" min="100" max="100"/>
+    <col width="2.88" customWidth="1" min="101" max="101"/>
+    <col width="21" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,14 +711,14 @@
           <t>DAILY RESOURCE GAINS + NET — 33-day calendar, per earner (day 1 = Wednesday)</t>
         </is>
       </c>
-      <c r="CJ1" s="2" t="inlineStr">
+      <c r="CX1" s="2" t="inlineStr">
         <is>
           <t>source dropdown list</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="CJ2" s="2" t="inlineStr">
+      <c r="CX2" s="2" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
@@ -726,7 +740,7 @@
           <t>◀ filters (dropdowns) — the whole table re-simulates on change</t>
         </is>
       </c>
-      <c r="CJ3" s="2" t="inlineStr">
+      <c r="CX3" s="2" t="inlineStr">
         <is>
           <t>Ads</t>
         </is>
@@ -743,7 +757,7 @@
           <t>0-9</t>
         </is>
       </c>
-      <c r="CJ4" s="2" t="inlineStr">
+      <c r="CX4" s="2" t="inlineStr">
         <is>
           <t>Bomb Challenge</t>
         </is>
@@ -760,14 +774,14 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="CJ5" s="2" t="inlineStr">
+      <c r="CX5" s="2" t="inlineStr">
         <is>
           <t>Bomb's Ballet</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="CJ6" s="2" t="inlineStr">
+      <c r="CX6" s="2" t="inlineStr">
         <is>
           <t>Chuck Challenge</t>
         </is>
@@ -789,13 +803,13 @@
       <c r="L7" s="6" t="n"/>
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>◄ NEW (cal_new, simulated) ►</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n"/>
       <c r="S7" s="7" t="n"/>
       <c r="T7" s="7" t="n"/>
       <c r="U7" s="7" t="n"/>
@@ -804,56 +818,53 @@
       <c r="X7" s="7" t="n"/>
       <c r="Y7" s="7" t="n"/>
       <c r="Z7" s="7" t="n"/>
-      <c r="AB7" s="8" t="inlineStr">
+      <c r="AA7" s="7" t="n"/>
+      <c r="AB7" s="7" t="n"/>
+      <c r="AC7" s="7" t="n"/>
+      <c r="AD7" s="7" t="n"/>
+      <c r="AF7" s="8" t="inlineStr">
         <is>
           <t>Δ  NEW − CURRENT (same day)</t>
         </is>
       </c>
-      <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="8" t="n"/>
-      <c r="AE7" s="8" t="n"/>
-      <c r="AF7" s="8" t="n"/>
       <c r="AG7" s="8" t="n"/>
       <c r="AH7" s="8" t="n"/>
       <c r="AI7" s="8" t="n"/>
       <c r="AJ7" s="8" t="n"/>
       <c r="AK7" s="8" t="n"/>
       <c r="AL7" s="8" t="n"/>
-      <c r="AN7" s="9" t="inlineStr">
+      <c r="AM7" s="8" t="n"/>
+      <c r="AN7" s="8" t="n"/>
+      <c r="AO7" s="8" t="n"/>
+      <c r="AP7" s="8" t="n"/>
+      <c r="AQ7" s="8" t="n"/>
+      <c r="AR7" s="8" t="n"/>
+      <c r="AT7" s="9" t="inlineStr">
         <is>
           <t>◄ ACTUAL SPEND / earner (data_econ_daily) ►</t>
         </is>
       </c>
-      <c r="AO7" s="9" t="n"/>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="9" t="n"/>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
       <c r="AU7" s="9" t="n"/>
       <c r="AV7" s="9" t="n"/>
       <c r="AW7" s="9" t="n"/>
       <c r="AX7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="inlineStr">
-        <is>
-          <t>◄ CURRENT NET / earner (gain − spend) ►</t>
-        </is>
-      </c>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
       <c r="BA7" s="9" t="n"/>
       <c r="BB7" s="9" t="n"/>
       <c r="BC7" s="9" t="n"/>
       <c r="BD7" s="9" t="n"/>
       <c r="BE7" s="9" t="n"/>
       <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="9" t="n"/>
-      <c r="BH7" s="9" t="n"/>
+      <c r="BH7" s="9" t="inlineStr">
+        <is>
+          <t>◄ CURRENT NET / earner (gain − spend) ►</t>
+        </is>
+      </c>
       <c r="BI7" s="9" t="n"/>
       <c r="BJ7" s="9" t="n"/>
-      <c r="BL7" s="9" t="inlineStr">
-        <is>
-          <t>◄ NEW NET / earner (gain + sim Δ − spend) ►</t>
-        </is>
-      </c>
+      <c r="BK7" s="9" t="n"/>
+      <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="9" t="n"/>
       <c r="BN7" s="9" t="n"/>
       <c r="BO7" s="9" t="n"/>
@@ -862,24 +873,41 @@
       <c r="BR7" s="9" t="n"/>
       <c r="BS7" s="9" t="n"/>
       <c r="BT7" s="9" t="n"/>
-      <c r="BU7" s="9" t="n"/>
-      <c r="BV7" s="9" t="n"/>
-      <c r="BX7" s="8" t="inlineStr">
+      <c r="BV7" s="9" t="inlineStr">
+        <is>
+          <t>◄ NEW NET / earner (gain + sim Δ − spend) ►</t>
+        </is>
+      </c>
+      <c r="BW7" s="9" t="n"/>
+      <c r="BX7" s="9" t="n"/>
+      <c r="BY7" s="9" t="n"/>
+      <c r="BZ7" s="9" t="n"/>
+      <c r="CA7" s="9" t="n"/>
+      <c r="CB7" s="9" t="n"/>
+      <c r="CC7" s="9" t="n"/>
+      <c r="CD7" s="9" t="n"/>
+      <c r="CE7" s="9" t="n"/>
+      <c r="CF7" s="9" t="n"/>
+      <c r="CG7" s="9" t="n"/>
+      <c r="CH7" s="9" t="n"/>
+      <c r="CJ7" s="8" t="inlineStr">
         <is>
           <t>Δ  NET (new − cur; == sim Δ)</t>
         </is>
       </c>
-      <c r="BY7" s="8" t="n"/>
-      <c r="BZ7" s="8" t="n"/>
-      <c r="CA7" s="8" t="n"/>
-      <c r="CB7" s="8" t="n"/>
-      <c r="CC7" s="8" t="n"/>
-      <c r="CD7" s="8" t="n"/>
-      <c r="CE7" s="8" t="n"/>
-      <c r="CF7" s="8" t="n"/>
-      <c r="CG7" s="8" t="n"/>
-      <c r="CH7" s="8" t="n"/>
-      <c r="CJ7" s="2" t="inlineStr">
+      <c r="CK7" s="8" t="n"/>
+      <c r="CL7" s="8" t="n"/>
+      <c r="CM7" s="8" t="n"/>
+      <c r="CN7" s="8" t="n"/>
+      <c r="CO7" s="8" t="n"/>
+      <c r="CP7" s="8" t="n"/>
+      <c r="CQ7" s="8" t="n"/>
+      <c r="CR7" s="8" t="n"/>
+      <c r="CS7" s="8" t="n"/>
+      <c r="CT7" s="8" t="n"/>
+      <c r="CU7" s="8" t="n"/>
+      <c r="CV7" s="8" t="n"/>
+      <c r="CX7" s="2" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
@@ -951,337 +979,407 @@
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="S8" s="12" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="R8" s="12" t="inlineStr">
+      <c r="T8" s="12" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr">
+      <c r="U8" s="12" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="T8" s="12" t="inlineStr">
+      <c r="V8" s="12" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="U8" s="12" t="inlineStr">
+      <c r="W8" s="12" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="V8" s="12" t="inlineStr">
+      <c r="X8" s="12" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="W8" s="12" t="inlineStr">
+      <c r="Y8" s="12" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="X8" s="12" t="inlineStr">
+      <c r="Z8" s="12" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="Y8" s="12" t="inlineStr">
+      <c r="AA8" s="12" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="Z8" s="12" t="inlineStr">
+      <c r="AB8" s="12" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AB8" s="13" t="inlineStr">
+      <c r="AC8" s="12" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AD8" s="12" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AF8" s="13" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="AC8" s="13" t="inlineStr">
+      <c r="AG8" s="13" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="AD8" s="13" t="inlineStr">
+      <c r="AH8" s="13" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="AE8" s="13" t="inlineStr">
+      <c r="AI8" s="13" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="AF8" s="13" t="inlineStr">
+      <c r="AJ8" s="13" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AG8" s="13" t="inlineStr">
+      <c r="AK8" s="13" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="AH8" s="13" t="inlineStr">
+      <c r="AL8" s="13" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="AI8" s="13" t="inlineStr">
+      <c r="AM8" s="13" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="AJ8" s="13" t="inlineStr">
+      <c r="AN8" s="13" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="AK8" s="13" t="inlineStr">
+      <c r="AO8" s="13" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AL8" s="13" t="inlineStr">
+      <c r="AP8" s="13" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AN8" s="14" t="inlineStr">
+      <c r="AQ8" s="13" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="AR8" s="13" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="AT8" s="14" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="AO8" s="14" t="inlineStr">
+      <c r="AU8" s="14" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="AP8" s="14" t="inlineStr">
+      <c r="AV8" s="14" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="AQ8" s="14" t="inlineStr">
+      <c r="AW8" s="14" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="AR8" s="14" t="inlineStr">
+      <c r="AX8" s="14" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AS8" s="14" t="inlineStr">
+      <c r="AY8" s="14" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="AT8" s="14" t="inlineStr">
+      <c r="AZ8" s="14" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="AU8" s="14" t="inlineStr">
+      <c r="BA8" s="14" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="AV8" s="14" t="inlineStr">
+      <c r="BB8" s="14" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="AW8" s="14" t="inlineStr">
+      <c r="BC8" s="14" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="AX8" s="14" t="inlineStr">
+      <c r="BD8" s="14" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="AZ8" s="14" t="inlineStr">
+      <c r="BE8" s="14" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="BF8" s="14" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="BH8" s="14" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="BA8" s="14" t="inlineStr">
+      <c r="BI8" s="14" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="BB8" s="14" t="inlineStr">
+      <c r="BJ8" s="14" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="BC8" s="14" t="inlineStr">
+      <c r="BK8" s="14" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="BD8" s="14" t="inlineStr">
+      <c r="BL8" s="14" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="BE8" s="14" t="inlineStr">
+      <c r="BM8" s="14" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="BF8" s="14" t="inlineStr">
+      <c r="BN8" s="14" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="BG8" s="14" t="inlineStr">
+      <c r="BO8" s="14" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="BH8" s="14" t="inlineStr">
+      <c r="BP8" s="14" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="BI8" s="14" t="inlineStr">
+      <c r="BQ8" s="14" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="BJ8" s="14" t="inlineStr">
+      <c r="BR8" s="14" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="BL8" s="14" t="inlineStr">
+      <c r="BS8" s="14" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="BT8" s="14" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="BV8" s="14" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="BM8" s="14" t="inlineStr">
+      <c r="BW8" s="14" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="BN8" s="14" t="inlineStr">
+      <c r="BX8" s="14" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="BO8" s="14" t="inlineStr">
+      <c r="BY8" s="14" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="BP8" s="14" t="inlineStr">
+      <c r="BZ8" s="14" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="BQ8" s="14" t="inlineStr">
+      <c r="CA8" s="14" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="BR8" s="14" t="inlineStr">
+      <c r="CB8" s="14" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="BS8" s="14" t="inlineStr">
+      <c r="CC8" s="14" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="BT8" s="14" t="inlineStr">
+      <c r="CD8" s="14" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="BU8" s="14" t="inlineStr">
+      <c r="CE8" s="14" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="BV8" s="14" t="inlineStr">
+      <c r="CF8" s="14" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="BX8" s="13" t="inlineStr">
+      <c r="CG8" s="14" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="CH8" s="14" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="CJ8" s="13" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="BY8" s="13" t="inlineStr">
+      <c r="CK8" s="13" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="BZ8" s="13" t="inlineStr">
+      <c r="CL8" s="13" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="CA8" s="13" t="inlineStr">
+      <c r="CM8" s="13" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="CB8" s="13" t="inlineStr">
+      <c r="CN8" s="13" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="CC8" s="13" t="inlineStr">
+      <c r="CO8" s="13" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="CD8" s="13" t="inlineStr">
+      <c r="CP8" s="13" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="CE8" s="13" t="inlineStr">
+      <c r="CQ8" s="13" t="inlineStr">
         <is>
           <t>UL Bomb</t>
         </is>
       </c>
-      <c r="CF8" s="13" t="inlineStr">
+      <c r="CR8" s="13" t="inlineStr">
         <is>
           <t>UL Chuck</t>
         </is>
       </c>
-      <c r="CG8" s="13" t="inlineStr">
+      <c r="CS8" s="13" t="inlineStr">
         <is>
           <t>UL Red</t>
         </is>
       </c>
-      <c r="CH8" s="13" t="inlineStr">
+      <c r="CT8" s="13" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="CJ8" s="2" t="inlineStr">
+      <c r="CU8" s="13" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="CV8" s="13" t="inlineStr">
+        <is>
+          <t>SPTx2</t>
+        </is>
+      </c>
+      <c r="CX8" s="2" t="inlineStr">
         <is>
           <t>Daily Gift</t>
         </is>
@@ -1310,12 +1408,12 @@
       <c r="L9" s="16" t="n"/>
       <c r="M9" s="16" t="n"/>
       <c r="N9" s="16" t="n"/>
-      <c r="P9" s="16">
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="R9" s="16">
         <f>LET(payer,$C$3, segment,$C$4, source,$C$5, ECOGAINS_DAILY(payer, segment, source, "NEW", sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="16" t="n"/>
       <c r="S9" s="16" t="n"/>
       <c r="T9" s="16" t="n"/>
       <c r="U9" s="16" t="n"/>
@@ -1324,52 +1422,50 @@
       <c r="X9" s="16" t="n"/>
       <c r="Y9" s="16" t="n"/>
       <c r="Z9" s="16" t="n"/>
-      <c r="AB9" s="17">
+      <c r="AA9" s="16" t="n"/>
+      <c r="AB9" s="16" t="n"/>
+      <c r="AC9" s="16" t="n"/>
+      <c r="AD9" s="16" t="n"/>
+      <c r="AF9" s="17">
         <f>LET(payer,$C$3, segment,$C$4, source,$C$5, ECOGAINS_DAILY(payer, segment, source, "DIFF", sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="AC9" s="17" t="n"/>
-      <c r="AD9" s="17" t="n"/>
-      <c r="AE9" s="17" t="n"/>
-      <c r="AF9" s="17" t="n"/>
       <c r="AG9" s="17" t="n"/>
       <c r="AH9" s="17" t="n"/>
       <c r="AI9" s="17" t="n"/>
       <c r="AJ9" s="17" t="n"/>
       <c r="AK9" s="17" t="n"/>
       <c r="AL9" s="17" t="n"/>
-      <c r="AN9" s="16">
+      <c r="AM9" s="17" t="n"/>
+      <c r="AN9" s="17" t="n"/>
+      <c r="AO9" s="17" t="n"/>
+      <c r="AP9" s="17" t="n"/>
+      <c r="AQ9" s="17" t="n"/>
+      <c r="AR9" s="17" t="n"/>
+      <c r="AT9" s="16">
         <f>LET(payer,$C$3, segment,$C$4, source,$C$5, ECOGAINS_DAILY(payer, segment, source, "SPEND", sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="AO9" s="16" t="n"/>
-      <c r="AP9" s="16" t="n"/>
-      <c r="AQ9" s="16" t="n"/>
-      <c r="AR9" s="16" t="n"/>
-      <c r="AS9" s="16" t="n"/>
-      <c r="AT9" s="16" t="n"/>
       <c r="AU9" s="16" t="n"/>
       <c r="AV9" s="16" t="n"/>
       <c r="AW9" s="16" t="n"/>
       <c r="AX9" s="16" t="n"/>
-      <c r="AZ9" s="18">
+      <c r="AY9" s="16" t="n"/>
+      <c r="AZ9" s="16" t="n"/>
+      <c r="BA9" s="16" t="n"/>
+      <c r="BB9" s="16" t="n"/>
+      <c r="BC9" s="16" t="n"/>
+      <c r="BD9" s="16" t="n"/>
+      <c r="BE9" s="16" t="n"/>
+      <c r="BF9" s="16" t="n"/>
+      <c r="BH9" s="18">
         <f>LET(payer,$C$3, segment,$C$4, source,$C$5, ECOGAINS_DAILY(payer, segment, source, "CURNET", sim_refresh!$A$1))</f>
         <v/>
       </c>
-      <c r="BA9" s="18" t="n"/>
-      <c r="BB9" s="18" t="n"/>
-      <c r="BC9" s="18" t="n"/>
-      <c r="BD9" s="18" t="n"/>
-      <c r="BE9" s="18" t="n"/>
-      <c r="BF9" s="18" t="n"/>
-      <c r="BG9" s="18" t="n"/>
-      <c r="BH9" s="18" t="n"/>
       <c r="BI9" s="18" t="n"/>
       <c r="BJ9" s="18" t="n"/>
-      <c r="BL9" s="18">
-        <f>LET(payer,$C$3, segment,$C$4, source,$C$5, ECOGAINS_DAILY(payer, segment, source, "NEWNET", sim_refresh!$A$1))</f>
-        <v/>
-      </c>
+      <c r="BK9" s="18" t="n"/>
+      <c r="BL9" s="18" t="n"/>
       <c r="BM9" s="18" t="n"/>
       <c r="BN9" s="18" t="n"/>
       <c r="BO9" s="18" t="n"/>
@@ -1378,53 +1474,75 @@
       <c r="BR9" s="18" t="n"/>
       <c r="BS9" s="18" t="n"/>
       <c r="BT9" s="18" t="n"/>
-      <c r="BU9" s="18" t="n"/>
-      <c r="BV9" s="18" t="n"/>
-      <c r="BX9" s="17">
-        <f>IFERROR(BL9-AZ9,"")</f>
-        <v/>
-      </c>
-      <c r="BY9" s="17">
-        <f>IFERROR(BM9-BA9,"")</f>
-        <v/>
-      </c>
-      <c r="BZ9" s="17">
-        <f>IFERROR(BN9-BB9,"")</f>
-        <v/>
-      </c>
-      <c r="CA9" s="17">
-        <f>IFERROR(BO9-BC9,"")</f>
-        <v/>
-      </c>
-      <c r="CB9" s="17">
-        <f>IFERROR(BP9-BD9,"")</f>
-        <v/>
-      </c>
-      <c r="CC9" s="17">
-        <f>IFERROR(BQ9-BE9,"")</f>
-        <v/>
-      </c>
-      <c r="CD9" s="17">
-        <f>IFERROR(BR9-BF9,"")</f>
-        <v/>
-      </c>
-      <c r="CE9" s="17">
-        <f>IFERROR(BS9-BG9,"")</f>
-        <v/>
-      </c>
-      <c r="CF9" s="17">
-        <f>IFERROR(BT9-BH9,"")</f>
-        <v/>
-      </c>
-      <c r="CG9" s="17">
-        <f>IFERROR(BU9-BI9,"")</f>
-        <v/>
-      </c>
-      <c r="CH9" s="17">
-        <f>IFERROR(BV9-BJ9,"")</f>
-        <v/>
-      </c>
-      <c r="CJ9" s="2" t="inlineStr">
+      <c r="BV9" s="18">
+        <f>LET(payer,$C$3, segment,$C$4, source,$C$5, ECOGAINS_DAILY(payer, segment, source, "NEWNET", sim_refresh!$A$1))</f>
+        <v/>
+      </c>
+      <c r="BW9" s="18" t="n"/>
+      <c r="BX9" s="18" t="n"/>
+      <c r="BY9" s="18" t="n"/>
+      <c r="BZ9" s="18" t="n"/>
+      <c r="CA9" s="18" t="n"/>
+      <c r="CB9" s="18" t="n"/>
+      <c r="CC9" s="18" t="n"/>
+      <c r="CD9" s="18" t="n"/>
+      <c r="CE9" s="18" t="n"/>
+      <c r="CF9" s="18" t="n"/>
+      <c r="CG9" s="18" t="n"/>
+      <c r="CH9" s="18" t="n"/>
+      <c r="CJ9" s="17">
+        <f>IFERROR(BV9-BH9,"")</f>
+        <v/>
+      </c>
+      <c r="CK9" s="17">
+        <f>IFERROR(BW9-BI9,"")</f>
+        <v/>
+      </c>
+      <c r="CL9" s="17">
+        <f>IFERROR(BX9-BJ9,"")</f>
+        <v/>
+      </c>
+      <c r="CM9" s="17">
+        <f>IFERROR(BY9-BK9,"")</f>
+        <v/>
+      </c>
+      <c r="CN9" s="17">
+        <f>IFERROR(BZ9-BL9,"")</f>
+        <v/>
+      </c>
+      <c r="CO9" s="17">
+        <f>IFERROR(CA9-BM9,"")</f>
+        <v/>
+      </c>
+      <c r="CP9" s="17">
+        <f>IFERROR(CB9-BN9,"")</f>
+        <v/>
+      </c>
+      <c r="CQ9" s="17">
+        <f>IFERROR(CC9-BO9,"")</f>
+        <v/>
+      </c>
+      <c r="CR9" s="17">
+        <f>IFERROR(CD9-BP9,"")</f>
+        <v/>
+      </c>
+      <c r="CS9" s="17">
+        <f>IFERROR(CE9-BQ9,"")</f>
+        <v/>
+      </c>
+      <c r="CT9" s="17">
+        <f>IFERROR(CF9-BR9,"")</f>
+        <v/>
+      </c>
+      <c r="CU9" s="17">
+        <f>IFERROR(CG9-BS9,"")</f>
+        <v/>
+      </c>
+      <c r="CV9" s="17">
+        <f>IFERROR(CH9-BT9,"")</f>
+        <v/>
+      </c>
+      <c r="CX9" s="2" t="inlineStr">
         <is>
           <t>Daily Night Sky Prize</t>
         </is>
@@ -1450,8 +1568,8 @@
       <c r="L10" s="16" t="n"/>
       <c r="M10" s="16" t="n"/>
       <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
       <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
       <c r="R10" s="16" t="n"/>
       <c r="S10" s="16" t="n"/>
       <c r="T10" s="16" t="n"/>
@@ -1461,10 +1579,10 @@
       <c r="X10" s="16" t="n"/>
       <c r="Y10" s="16" t="n"/>
       <c r="Z10" s="16" t="n"/>
-      <c r="AB10" s="17" t="n"/>
-      <c r="AC10" s="17" t="n"/>
-      <c r="AD10" s="17" t="n"/>
-      <c r="AE10" s="17" t="n"/>
+      <c r="AA10" s="16" t="n"/>
+      <c r="AB10" s="16" t="n"/>
+      <c r="AC10" s="16" t="n"/>
+      <c r="AD10" s="16" t="n"/>
       <c r="AF10" s="17" t="n"/>
       <c r="AG10" s="17" t="n"/>
       <c r="AH10" s="17" t="n"/>
@@ -1472,28 +1590,29 @@
       <c r="AJ10" s="17" t="n"/>
       <c r="AK10" s="17" t="n"/>
       <c r="AL10" s="17" t="n"/>
-      <c r="AN10" s="16" t="n"/>
-      <c r="AO10" s="16" t="n"/>
-      <c r="AP10" s="16" t="n"/>
-      <c r="AQ10" s="16" t="n"/>
-      <c r="AR10" s="16" t="n"/>
-      <c r="AS10" s="16" t="n"/>
+      <c r="AM10" s="17" t="n"/>
+      <c r="AN10" s="17" t="n"/>
+      <c r="AO10" s="17" t="n"/>
+      <c r="AP10" s="17" t="n"/>
+      <c r="AQ10" s="17" t="n"/>
+      <c r="AR10" s="17" t="n"/>
       <c r="AT10" s="16" t="n"/>
       <c r="AU10" s="16" t="n"/>
       <c r="AV10" s="16" t="n"/>
       <c r="AW10" s="16" t="n"/>
       <c r="AX10" s="16" t="n"/>
-      <c r="AZ10" s="18" t="n"/>
-      <c r="BA10" s="18" t="n"/>
-      <c r="BB10" s="18" t="n"/>
-      <c r="BC10" s="18" t="n"/>
-      <c r="BD10" s="18" t="n"/>
-      <c r="BE10" s="18" t="n"/>
-      <c r="BF10" s="18" t="n"/>
-      <c r="BG10" s="18" t="n"/>
+      <c r="AY10" s="16" t="n"/>
+      <c r="AZ10" s="16" t="n"/>
+      <c r="BA10" s="16" t="n"/>
+      <c r="BB10" s="16" t="n"/>
+      <c r="BC10" s="16" t="n"/>
+      <c r="BD10" s="16" t="n"/>
+      <c r="BE10" s="16" t="n"/>
+      <c r="BF10" s="16" t="n"/>
       <c r="BH10" s="18" t="n"/>
       <c r="BI10" s="18" t="n"/>
       <c r="BJ10" s="18" t="n"/>
+      <c r="BK10" s="18" t="n"/>
       <c r="BL10" s="18" t="n"/>
       <c r="BM10" s="18" t="n"/>
       <c r="BN10" s="18" t="n"/>
@@ -1503,53 +1622,72 @@
       <c r="BR10" s="18" t="n"/>
       <c r="BS10" s="18" t="n"/>
       <c r="BT10" s="18" t="n"/>
-      <c r="BU10" s="18" t="n"/>
       <c r="BV10" s="18" t="n"/>
-      <c r="BX10" s="17">
-        <f>IFERROR(BL10-AZ10,"")</f>
-        <v/>
-      </c>
-      <c r="BY10" s="17">
-        <f>IFERROR(BM10-BA10,"")</f>
-        <v/>
-      </c>
-      <c r="BZ10" s="17">
-        <f>IFERROR(BN10-BB10,"")</f>
-        <v/>
-      </c>
-      <c r="CA10" s="17">
-        <f>IFERROR(BO10-BC10,"")</f>
-        <v/>
-      </c>
-      <c r="CB10" s="17">
-        <f>IFERROR(BP10-BD10,"")</f>
-        <v/>
-      </c>
-      <c r="CC10" s="17">
-        <f>IFERROR(BQ10-BE10,"")</f>
-        <v/>
-      </c>
-      <c r="CD10" s="17">
-        <f>IFERROR(BR10-BF10,"")</f>
-        <v/>
-      </c>
-      <c r="CE10" s="17">
-        <f>IFERROR(BS10-BG10,"")</f>
-        <v/>
-      </c>
-      <c r="CF10" s="17">
-        <f>IFERROR(BT10-BH10,"")</f>
-        <v/>
-      </c>
-      <c r="CG10" s="17">
-        <f>IFERROR(BU10-BI10,"")</f>
-        <v/>
-      </c>
-      <c r="CH10" s="17">
-        <f>IFERROR(BV10-BJ10,"")</f>
-        <v/>
-      </c>
-      <c r="CJ10" s="2" t="inlineStr">
+      <c r="BW10" s="18" t="n"/>
+      <c r="BX10" s="18" t="n"/>
+      <c r="BY10" s="18" t="n"/>
+      <c r="BZ10" s="18" t="n"/>
+      <c r="CA10" s="18" t="n"/>
+      <c r="CB10" s="18" t="n"/>
+      <c r="CC10" s="18" t="n"/>
+      <c r="CD10" s="18" t="n"/>
+      <c r="CE10" s="18" t="n"/>
+      <c r="CF10" s="18" t="n"/>
+      <c r="CG10" s="18" t="n"/>
+      <c r="CH10" s="18" t="n"/>
+      <c r="CJ10" s="17">
+        <f>IFERROR(BV10-BH10,"")</f>
+        <v/>
+      </c>
+      <c r="CK10" s="17">
+        <f>IFERROR(BW10-BI10,"")</f>
+        <v/>
+      </c>
+      <c r="CL10" s="17">
+        <f>IFERROR(BX10-BJ10,"")</f>
+        <v/>
+      </c>
+      <c r="CM10" s="17">
+        <f>IFERROR(BY10-BK10,"")</f>
+        <v/>
+      </c>
+      <c r="CN10" s="17">
+        <f>IFERROR(BZ10-BL10,"")</f>
+        <v/>
+      </c>
+      <c r="CO10" s="17">
+        <f>IFERROR(CA10-BM10,"")</f>
+        <v/>
+      </c>
+      <c r="CP10" s="17">
+        <f>IFERROR(CB10-BN10,"")</f>
+        <v/>
+      </c>
+      <c r="CQ10" s="17">
+        <f>IFERROR(CC10-BO10,"")</f>
+        <v/>
+      </c>
+      <c r="CR10" s="17">
+        <f>IFERROR(CD10-BP10,"")</f>
+        <v/>
+      </c>
+      <c r="CS10" s="17">
+        <f>IFERROR(CE10-BQ10,"")</f>
+        <v/>
+      </c>
+      <c r="CT10" s="17">
+        <f>IFERROR(CF10-BR10,"")</f>
+        <v/>
+      </c>
+      <c r="CU10" s="17">
+        <f>IFERROR(CG10-BS10,"")</f>
+        <v/>
+      </c>
+      <c r="CV10" s="17">
+        <f>IFERROR(CH10-BT10,"")</f>
+        <v/>
+      </c>
+      <c r="CX10" s="2" t="inlineStr">
         <is>
           <t>Flock Flurry</t>
         </is>
@@ -1575,8 +1713,8 @@
       <c r="L11" s="16" t="n"/>
       <c r="M11" s="16" t="n"/>
       <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
       <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
       <c r="R11" s="16" t="n"/>
       <c r="S11" s="16" t="n"/>
       <c r="T11" s="16" t="n"/>
@@ -1586,10 +1724,10 @@
       <c r="X11" s="16" t="n"/>
       <c r="Y11" s="16" t="n"/>
       <c r="Z11" s="16" t="n"/>
-      <c r="AB11" s="17" t="n"/>
-      <c r="AC11" s="17" t="n"/>
-      <c r="AD11" s="17" t="n"/>
-      <c r="AE11" s="17" t="n"/>
+      <c r="AA11" s="16" t="n"/>
+      <c r="AB11" s="16" t="n"/>
+      <c r="AC11" s="16" t="n"/>
+      <c r="AD11" s="16" t="n"/>
       <c r="AF11" s="17" t="n"/>
       <c r="AG11" s="17" t="n"/>
       <c r="AH11" s="17" t="n"/>
@@ -1597,28 +1735,29 @@
       <c r="AJ11" s="17" t="n"/>
       <c r="AK11" s="17" t="n"/>
       <c r="AL11" s="17" t="n"/>
-      <c r="AN11" s="16" t="n"/>
-      <c r="AO11" s="16" t="n"/>
-      <c r="AP11" s="16" t="n"/>
-      <c r="AQ11" s="16" t="n"/>
-      <c r="AR11" s="16" t="n"/>
-      <c r="AS11" s="16" t="n"/>
+      <c r="AM11" s="17" t="n"/>
+      <c r="AN11" s="17" t="n"/>
+      <c r="AO11" s="17" t="n"/>
+      <c r="AP11" s="17" t="n"/>
+      <c r="AQ11" s="17" t="n"/>
+      <c r="AR11" s="17" t="n"/>
       <c r="AT11" s="16" t="n"/>
       <c r="AU11" s="16" t="n"/>
       <c r="AV11" s="16" t="n"/>
       <c r="AW11" s="16" t="n"/>
       <c r="AX11" s="16" t="n"/>
-      <c r="AZ11" s="18" t="n"/>
-      <c r="BA11" s="18" t="n"/>
-      <c r="BB11" s="18" t="n"/>
-      <c r="BC11" s="18" t="n"/>
-      <c r="BD11" s="18" t="n"/>
-      <c r="BE11" s="18" t="n"/>
-      <c r="BF11" s="18" t="n"/>
-      <c r="BG11" s="18" t="n"/>
+      <c r="AY11" s="16" t="n"/>
+      <c r="AZ11" s="16" t="n"/>
+      <c r="BA11" s="16" t="n"/>
+      <c r="BB11" s="16" t="n"/>
+      <c r="BC11" s="16" t="n"/>
+      <c r="BD11" s="16" t="n"/>
+      <c r="BE11" s="16" t="n"/>
+      <c r="BF11" s="16" t="n"/>
       <c r="BH11" s="18" t="n"/>
       <c r="BI11" s="18" t="n"/>
       <c r="BJ11" s="18" t="n"/>
+      <c r="BK11" s="18" t="n"/>
       <c r="BL11" s="18" t="n"/>
       <c r="BM11" s="18" t="n"/>
       <c r="BN11" s="18" t="n"/>
@@ -1628,53 +1767,72 @@
       <c r="BR11" s="18" t="n"/>
       <c r="BS11" s="18" t="n"/>
       <c r="BT11" s="18" t="n"/>
-      <c r="BU11" s="18" t="n"/>
       <c r="BV11" s="18" t="n"/>
-      <c r="BX11" s="17">
-        <f>IFERROR(BL11-AZ11,"")</f>
-        <v/>
-      </c>
-      <c r="BY11" s="17">
-        <f>IFERROR(BM11-BA11,"")</f>
-        <v/>
-      </c>
-      <c r="BZ11" s="17">
-        <f>IFERROR(BN11-BB11,"")</f>
-        <v/>
-      </c>
-      <c r="CA11" s="17">
-        <f>IFERROR(BO11-BC11,"")</f>
-        <v/>
-      </c>
-      <c r="CB11" s="17">
-        <f>IFERROR(BP11-BD11,"")</f>
-        <v/>
-      </c>
-      <c r="CC11" s="17">
-        <f>IFERROR(BQ11-BE11,"")</f>
-        <v/>
-      </c>
-      <c r="CD11" s="17">
-        <f>IFERROR(BR11-BF11,"")</f>
-        <v/>
-      </c>
-      <c r="CE11" s="17">
-        <f>IFERROR(BS11-BG11,"")</f>
-        <v/>
-      </c>
-      <c r="CF11" s="17">
-        <f>IFERROR(BT11-BH11,"")</f>
-        <v/>
-      </c>
-      <c r="CG11" s="17">
-        <f>IFERROR(BU11-BI11,"")</f>
-        <v/>
-      </c>
-      <c r="CH11" s="17">
-        <f>IFERROR(BV11-BJ11,"")</f>
-        <v/>
-      </c>
-      <c r="CJ11" s="2" t="inlineStr">
+      <c r="BW11" s="18" t="n"/>
+      <c r="BX11" s="18" t="n"/>
+      <c r="BY11" s="18" t="n"/>
+      <c r="BZ11" s="18" t="n"/>
+      <c r="CA11" s="18" t="n"/>
+      <c r="CB11" s="18" t="n"/>
+      <c r="CC11" s="18" t="n"/>
+      <c r="CD11" s="18" t="n"/>
+      <c r="CE11" s="18" t="n"/>
+      <c r="CF11" s="18" t="n"/>
+      <c r="CG11" s="18" t="n"/>
+      <c r="CH11" s="18" t="n"/>
+      <c r="CJ11" s="17">
+        <f>IFERROR(BV11-BH11,"")</f>
+        <v/>
+      </c>
+      <c r="CK11" s="17">
+        <f>IFERROR(BW11-BI11,"")</f>
+        <v/>
+      </c>
+      <c r="CL11" s="17">
+        <f>IFERROR(BX11-BJ11,"")</f>
+        <v/>
+      </c>
+      <c r="CM11" s="17">
+        <f>IFERROR(BY11-BK11,"")</f>
+        <v/>
+      </c>
+      <c r="CN11" s="17">
+        <f>IFERROR(BZ11-BL11,"")</f>
+        <v/>
+      </c>
+      <c r="CO11" s="17">
+        <f>IFERROR(CA11-BM11,"")</f>
+        <v/>
+      </c>
+      <c r="CP11" s="17">
+        <f>IFERROR(CB11-BN11,"")</f>
+        <v/>
+      </c>
+      <c r="CQ11" s="17">
+        <f>IFERROR(CC11-BO11,"")</f>
+        <v/>
+      </c>
+      <c r="CR11" s="17">
+        <f>IFERROR(CD11-BP11,"")</f>
+        <v/>
+      </c>
+      <c r="CS11" s="17">
+        <f>IFERROR(CE11-BQ11,"")</f>
+        <v/>
+      </c>
+      <c r="CT11" s="17">
+        <f>IFERROR(CF11-BR11,"")</f>
+        <v/>
+      </c>
+      <c r="CU11" s="17">
+        <f>IFERROR(CG11-BS11,"")</f>
+        <v/>
+      </c>
+      <c r="CV11" s="17">
+        <f>IFERROR(CH11-BT11,"")</f>
+        <v/>
+      </c>
+      <c r="CX11" s="2" t="inlineStr">
         <is>
           <t>Hatchling Hideaway</t>
         </is>
@@ -1700,8 +1858,8 @@
       <c r="L12" s="16" t="n"/>
       <c r="M12" s="16" t="n"/>
       <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
       <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
       <c r="R12" s="16" t="n"/>
       <c r="S12" s="16" t="n"/>
       <c r="T12" s="16" t="n"/>
@@ -1711,10 +1869,10 @@
       <c r="X12" s="16" t="n"/>
       <c r="Y12" s="16" t="n"/>
       <c r="Z12" s="16" t="n"/>
-      <c r="AB12" s="17" t="n"/>
-      <c r="AC12" s="17" t="n"/>
-      <c r="AD12" s="17" t="n"/>
-      <c r="AE12" s="17" t="n"/>
+      <c r="AA12" s="16" t="n"/>
+      <c r="AB12" s="16" t="n"/>
+      <c r="AC12" s="16" t="n"/>
+      <c r="AD12" s="16" t="n"/>
       <c r="AF12" s="17" t="n"/>
       <c r="AG12" s="17" t="n"/>
       <c r="AH12" s="17" t="n"/>
@@ -1722,28 +1880,29 @@
       <c r="AJ12" s="17" t="n"/>
       <c r="AK12" s="17" t="n"/>
       <c r="AL12" s="17" t="n"/>
-      <c r="AN12" s="16" t="n"/>
-      <c r="AO12" s="16" t="n"/>
-      <c r="AP12" s="16" t="n"/>
-      <c r="AQ12" s="16" t="n"/>
-      <c r="AR12" s="16" t="n"/>
-      <c r="AS12" s="16" t="n"/>
+      <c r="AM12" s="17" t="n"/>
+      <c r="AN12" s="17" t="n"/>
+      <c r="AO12" s="17" t="n"/>
+      <c r="AP12" s="17" t="n"/>
+      <c r="AQ12" s="17" t="n"/>
+      <c r="AR12" s="17" t="n"/>
       <c r="AT12" s="16" t="n"/>
       <c r="AU12" s="16" t="n"/>
       <c r="AV12" s="16" t="n"/>
       <c r="AW12" s="16" t="n"/>
       <c r="AX12" s="16" t="n"/>
-      <c r="AZ12" s="18" t="n"/>
-      <c r="BA12" s="18" t="n"/>
-      <c r="BB12" s="18" t="n"/>
-      <c r="BC12" s="18" t="n"/>
-      <c r="BD12" s="18" t="n"/>
-      <c r="BE12" s="18" t="n"/>
-      <c r="BF12" s="18" t="n"/>
-      <c r="BG12" s="18" t="n"/>
+      <c r="AY12" s="16" t="n"/>
+      <c r="AZ12" s="16" t="n"/>
+      <c r="BA12" s="16" t="n"/>
+      <c r="BB12" s="16" t="n"/>
+      <c r="BC12" s="16" t="n"/>
+      <c r="BD12" s="16" t="n"/>
+      <c r="BE12" s="16" t="n"/>
+      <c r="BF12" s="16" t="n"/>
       <c r="BH12" s="18" t="n"/>
       <c r="BI12" s="18" t="n"/>
       <c r="BJ12" s="18" t="n"/>
+      <c r="BK12" s="18" t="n"/>
       <c r="BL12" s="18" t="n"/>
       <c r="BM12" s="18" t="n"/>
       <c r="BN12" s="18" t="n"/>
@@ -1753,53 +1912,72 @@
       <c r="BR12" s="18" t="n"/>
       <c r="BS12" s="18" t="n"/>
       <c r="BT12" s="18" t="n"/>
-      <c r="BU12" s="18" t="n"/>
       <c r="BV12" s="18" t="n"/>
-      <c r="BX12" s="17">
-        <f>IFERROR(BL12-AZ12,"")</f>
-        <v/>
-      </c>
-      <c r="BY12" s="17">
-        <f>IFERROR(BM12-BA12,"")</f>
-        <v/>
-      </c>
-      <c r="BZ12" s="17">
-        <f>IFERROR(BN12-BB12,"")</f>
-        <v/>
-      </c>
-      <c r="CA12" s="17">
-        <f>IFERROR(BO12-BC12,"")</f>
-        <v/>
-      </c>
-      <c r="CB12" s="17">
-        <f>IFERROR(BP12-BD12,"")</f>
-        <v/>
-      </c>
-      <c r="CC12" s="17">
-        <f>IFERROR(BQ12-BE12,"")</f>
-        <v/>
-      </c>
-      <c r="CD12" s="17">
-        <f>IFERROR(BR12-BF12,"")</f>
-        <v/>
-      </c>
-      <c r="CE12" s="17">
-        <f>IFERROR(BS12-BG12,"")</f>
-        <v/>
-      </c>
-      <c r="CF12" s="17">
-        <f>IFERROR(BT12-BH12,"")</f>
-        <v/>
-      </c>
-      <c r="CG12" s="17">
-        <f>IFERROR(BU12-BI12,"")</f>
-        <v/>
-      </c>
-      <c r="CH12" s="17">
-        <f>IFERROR(BV12-BJ12,"")</f>
-        <v/>
-      </c>
-      <c r="CJ12" s="2" t="inlineStr">
+      <c r="BW12" s="18" t="n"/>
+      <c r="BX12" s="18" t="n"/>
+      <c r="BY12" s="18" t="n"/>
+      <c r="BZ12" s="18" t="n"/>
+      <c r="CA12" s="18" t="n"/>
+      <c r="CB12" s="18" t="n"/>
+      <c r="CC12" s="18" t="n"/>
+      <c r="CD12" s="18" t="n"/>
+      <c r="CE12" s="18" t="n"/>
+      <c r="CF12" s="18" t="n"/>
+      <c r="CG12" s="18" t="n"/>
+      <c r="CH12" s="18" t="n"/>
+      <c r="CJ12" s="17">
+        <f>IFERROR(BV12-BH12,"")</f>
+        <v/>
+      </c>
+      <c r="CK12" s="17">
+        <f>IFERROR(BW12-BI12,"")</f>
+        <v/>
+      </c>
+      <c r="CL12" s="17">
+        <f>IFERROR(BX12-BJ12,"")</f>
+        <v/>
+      </c>
+      <c r="CM12" s="17">
+        <f>IFERROR(BY12-BK12,"")</f>
+        <v/>
+      </c>
+      <c r="CN12" s="17">
+        <f>IFERROR(BZ12-BL12,"")</f>
+        <v/>
+      </c>
+      <c r="CO12" s="17">
+        <f>IFERROR(CA12-BM12,"")</f>
+        <v/>
+      </c>
+      <c r="CP12" s="17">
+        <f>IFERROR(CB12-BN12,"")</f>
+        <v/>
+      </c>
+      <c r="CQ12" s="17">
+        <f>IFERROR(CC12-BO12,"")</f>
+        <v/>
+      </c>
+      <c r="CR12" s="17">
+        <f>IFERROR(CD12-BP12,"")</f>
+        <v/>
+      </c>
+      <c r="CS12" s="17">
+        <f>IFERROR(CE12-BQ12,"")</f>
+        <v/>
+      </c>
+      <c r="CT12" s="17">
+        <f>IFERROR(CF12-BR12,"")</f>
+        <v/>
+      </c>
+      <c r="CU12" s="17">
+        <f>IFERROR(CG12-BS12,"")</f>
+        <v/>
+      </c>
+      <c r="CV12" s="17">
+        <f>IFERROR(CH12-BT12,"")</f>
+        <v/>
+      </c>
+      <c r="CX12" s="2" t="inlineStr">
         <is>
           <t>Jigsaw</t>
         </is>
@@ -1825,8 +2003,8 @@
       <c r="L13" s="16" t="n"/>
       <c r="M13" s="16" t="n"/>
       <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
       <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
       <c r="R13" s="16" t="n"/>
       <c r="S13" s="16" t="n"/>
       <c r="T13" s="16" t="n"/>
@@ -1836,10 +2014,10 @@
       <c r="X13" s="16" t="n"/>
       <c r="Y13" s="16" t="n"/>
       <c r="Z13" s="16" t="n"/>
-      <c r="AB13" s="17" t="n"/>
-      <c r="AC13" s="17" t="n"/>
-      <c r="AD13" s="17" t="n"/>
-      <c r="AE13" s="17" t="n"/>
+      <c r="AA13" s="16" t="n"/>
+      <c r="AB13" s="16" t="n"/>
+      <c r="AC13" s="16" t="n"/>
+      <c r="AD13" s="16" t="n"/>
       <c r="AF13" s="17" t="n"/>
       <c r="AG13" s="17" t="n"/>
       <c r="AH13" s="17" t="n"/>
@@ -1847,28 +2025,29 @@
       <c r="AJ13" s="17" t="n"/>
       <c r="AK13" s="17" t="n"/>
       <c r="AL13" s="17" t="n"/>
-      <c r="AN13" s="16" t="n"/>
-      <c r="AO13" s="16" t="n"/>
-      <c r="AP13" s="16" t="n"/>
-      <c r="AQ13" s="16" t="n"/>
-      <c r="AR13" s="16" t="n"/>
-      <c r="AS13" s="16" t="n"/>
+      <c r="AM13" s="17" t="n"/>
+      <c r="AN13" s="17" t="n"/>
+      <c r="AO13" s="17" t="n"/>
+      <c r="AP13" s="17" t="n"/>
+      <c r="AQ13" s="17" t="n"/>
+      <c r="AR13" s="17" t="n"/>
       <c r="AT13" s="16" t="n"/>
       <c r="AU13" s="16" t="n"/>
       <c r="AV13" s="16" t="n"/>
       <c r="AW13" s="16" t="n"/>
       <c r="AX13" s="16" t="n"/>
-      <c r="AZ13" s="18" t="n"/>
-      <c r="BA13" s="18" t="n"/>
-      <c r="BB13" s="18" t="n"/>
-      <c r="BC13" s="18" t="n"/>
-      <c r="BD13" s="18" t="n"/>
-      <c r="BE13" s="18" t="n"/>
-      <c r="BF13" s="18" t="n"/>
-      <c r="BG13" s="18" t="n"/>
+      <c r="AY13" s="16" t="n"/>
+      <c r="AZ13" s="16" t="n"/>
+      <c r="BA13" s="16" t="n"/>
+      <c r="BB13" s="16" t="n"/>
+      <c r="BC13" s="16" t="n"/>
+      <c r="BD13" s="16" t="n"/>
+      <c r="BE13" s="16" t="n"/>
+      <c r="BF13" s="16" t="n"/>
       <c r="BH13" s="18" t="n"/>
       <c r="BI13" s="18" t="n"/>
       <c r="BJ13" s="18" t="n"/>
+      <c r="BK13" s="18" t="n"/>
       <c r="BL13" s="18" t="n"/>
       <c r="BM13" s="18" t="n"/>
       <c r="BN13" s="18" t="n"/>
@@ -1878,53 +2057,72 @@
       <c r="BR13" s="18" t="n"/>
       <c r="BS13" s="18" t="n"/>
       <c r="BT13" s="18" t="n"/>
-      <c r="BU13" s="18" t="n"/>
       <c r="BV13" s="18" t="n"/>
-      <c r="BX13" s="17">
-        <f>IFERROR(BL13-AZ13,"")</f>
-        <v/>
-      </c>
-      <c r="BY13" s="17">
-        <f>IFERROR(BM13-BA13,"")</f>
-        <v/>
-      </c>
-      <c r="BZ13" s="17">
-        <f>IFERROR(BN13-BB13,"")</f>
-        <v/>
-      </c>
-      <c r="CA13" s="17">
-        <f>IFERROR(BO13-BC13,"")</f>
-        <v/>
-      </c>
-      <c r="CB13" s="17">
-        <f>IFERROR(BP13-BD13,"")</f>
-        <v/>
-      </c>
-      <c r="CC13" s="17">
-        <f>IFERROR(BQ13-BE13,"")</f>
-        <v/>
-      </c>
-      <c r="CD13" s="17">
-        <f>IFERROR(BR13-BF13,"")</f>
-        <v/>
-      </c>
-      <c r="CE13" s="17">
-        <f>IFERROR(BS13-BG13,"")</f>
-        <v/>
-      </c>
-      <c r="CF13" s="17">
-        <f>IFERROR(BT13-BH13,"")</f>
-        <v/>
-      </c>
-      <c r="CG13" s="17">
-        <f>IFERROR(BU13-BI13,"")</f>
-        <v/>
-      </c>
-      <c r="CH13" s="17">
-        <f>IFERROR(BV13-BJ13,"")</f>
-        <v/>
-      </c>
-      <c r="CJ13" s="2" t="inlineStr">
+      <c r="BW13" s="18" t="n"/>
+      <c r="BX13" s="18" t="n"/>
+      <c r="BY13" s="18" t="n"/>
+      <c r="BZ13" s="18" t="n"/>
+      <c r="CA13" s="18" t="n"/>
+      <c r="CB13" s="18" t="n"/>
+      <c r="CC13" s="18" t="n"/>
+      <c r="CD13" s="18" t="n"/>
+      <c r="CE13" s="18" t="n"/>
+      <c r="CF13" s="18" t="n"/>
+      <c r="CG13" s="18" t="n"/>
+      <c r="CH13" s="18" t="n"/>
+      <c r="CJ13" s="17">
+        <f>IFERROR(BV13-BH13,"")</f>
+        <v/>
+      </c>
+      <c r="CK13" s="17">
+        <f>IFERROR(BW13-BI13,"")</f>
+        <v/>
+      </c>
+      <c r="CL13" s="17">
+        <f>IFERROR(BX13-BJ13,"")</f>
+        <v/>
+      </c>
+      <c r="CM13" s="17">
+        <f>IFERROR(BY13-BK13,"")</f>
+        <v/>
+      </c>
+      <c r="CN13" s="17">
+        <f>IFERROR(BZ13-BL13,"")</f>
+        <v/>
+      </c>
+      <c r="CO13" s="17">
+        <f>IFERROR(CA13-BM13,"")</f>
+        <v/>
+      </c>
+      <c r="CP13" s="17">
+        <f>IFERROR(CB13-BN13,"")</f>
+        <v/>
+      </c>
+      <c r="CQ13" s="17">
+        <f>IFERROR(CC13-BO13,"")</f>
+        <v/>
+      </c>
+      <c r="CR13" s="17">
+        <f>IFERROR(CD13-BP13,"")</f>
+        <v/>
+      </c>
+      <c r="CS13" s="17">
+        <f>IFERROR(CE13-BQ13,"")</f>
+        <v/>
+      </c>
+      <c r="CT13" s="17">
+        <f>IFERROR(CF13-BR13,"")</f>
+        <v/>
+      </c>
+      <c r="CU13" s="17">
+        <f>IFERROR(CG13-BS13,"")</f>
+        <v/>
+      </c>
+      <c r="CV13" s="17">
+        <f>IFERROR(CH13-BT13,"")</f>
+        <v/>
+      </c>
+      <c r="CX13" s="2" t="inlineStr">
         <is>
           <t>Kite Festival</t>
         </is>
@@ -1950,8 +2148,8 @@
       <c r="L14" s="16" t="n"/>
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
       <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
       <c r="R14" s="16" t="n"/>
       <c r="S14" s="16" t="n"/>
       <c r="T14" s="16" t="n"/>
@@ -1961,10 +2159,10 @@
       <c r="X14" s="16" t="n"/>
       <c r="Y14" s="16" t="n"/>
       <c r="Z14" s="16" t="n"/>
-      <c r="AB14" s="17" t="n"/>
-      <c r="AC14" s="17" t="n"/>
-      <c r="AD14" s="17" t="n"/>
-      <c r="AE14" s="17" t="n"/>
+      <c r="AA14" s="16" t="n"/>
+      <c r="AB14" s="16" t="n"/>
+      <c r="AC14" s="16" t="n"/>
+      <c r="AD14" s="16" t="n"/>
       <c r="AF14" s="17" t="n"/>
       <c r="AG14" s="17" t="n"/>
       <c r="AH14" s="17" t="n"/>
@@ -1972,28 +2170,29 @@
       <c r="AJ14" s="17" t="n"/>
       <c r="AK14" s="17" t="n"/>
       <c r="AL14" s="17" t="n"/>
-      <c r="AN14" s="16" t="n"/>
-      <c r="AO14" s="16" t="n"/>
-      <c r="AP14" s="16" t="n"/>
-      <c r="AQ14" s="16" t="n"/>
-      <c r="AR14" s="16" t="n"/>
-      <c r="AS14" s="16" t="n"/>
+      <c r="AM14" s="17" t="n"/>
+      <c r="AN14" s="17" t="n"/>
+      <c r="AO14" s="17" t="n"/>
+      <c r="AP14" s="17" t="n"/>
+      <c r="AQ14" s="17" t="n"/>
+      <c r="AR14" s="17" t="n"/>
       <c r="AT14" s="16" t="n"/>
       <c r="AU14" s="16" t="n"/>
       <c r="AV14" s="16" t="n"/>
       <c r="AW14" s="16" t="n"/>
       <c r="AX14" s="16" t="n"/>
-      <c r="AZ14" s="18" t="n"/>
-      <c r="BA14" s="18" t="n"/>
-      <c r="BB14" s="18" t="n"/>
-      <c r="BC14" s="18" t="n"/>
-      <c r="BD14" s="18" t="n"/>
-      <c r="BE14" s="18" t="n"/>
-      <c r="BF14" s="18" t="n"/>
-      <c r="BG14" s="18" t="n"/>
+      <c r="AY14" s="16" t="n"/>
+      <c r="AZ14" s="16" t="n"/>
+      <c r="BA14" s="16" t="n"/>
+      <c r="BB14" s="16" t="n"/>
+      <c r="BC14" s="16" t="n"/>
+      <c r="BD14" s="16" t="n"/>
+      <c r="BE14" s="16" t="n"/>
+      <c r="BF14" s="16" t="n"/>
       <c r="BH14" s="18" t="n"/>
       <c r="BI14" s="18" t="n"/>
       <c r="BJ14" s="18" t="n"/>
+      <c r="BK14" s="18" t="n"/>
       <c r="BL14" s="18" t="n"/>
       <c r="BM14" s="18" t="n"/>
       <c r="BN14" s="18" t="n"/>
@@ -2003,53 +2202,72 @@
       <c r="BR14" s="18" t="n"/>
       <c r="BS14" s="18" t="n"/>
       <c r="BT14" s="18" t="n"/>
-      <c r="BU14" s="18" t="n"/>
       <c r="BV14" s="18" t="n"/>
-      <c r="BX14" s="17">
-        <f>IFERROR(BL14-AZ14,"")</f>
-        <v/>
-      </c>
-      <c r="BY14" s="17">
-        <f>IFERROR(BM14-BA14,"")</f>
-        <v/>
-      </c>
-      <c r="BZ14" s="17">
-        <f>IFERROR(BN14-BB14,"")</f>
-        <v/>
-      </c>
-      <c r="CA14" s="17">
-        <f>IFERROR(BO14-BC14,"")</f>
-        <v/>
-      </c>
-      <c r="CB14" s="17">
-        <f>IFERROR(BP14-BD14,"")</f>
-        <v/>
-      </c>
-      <c r="CC14" s="17">
-        <f>IFERROR(BQ14-BE14,"")</f>
-        <v/>
-      </c>
-      <c r="CD14" s="17">
-        <f>IFERROR(BR14-BF14,"")</f>
-        <v/>
-      </c>
-      <c r="CE14" s="17">
-        <f>IFERROR(BS14-BG14,"")</f>
-        <v/>
-      </c>
-      <c r="CF14" s="17">
-        <f>IFERROR(BT14-BH14,"")</f>
-        <v/>
-      </c>
-      <c r="CG14" s="17">
-        <f>IFERROR(BU14-BI14,"")</f>
-        <v/>
-      </c>
-      <c r="CH14" s="17">
-        <f>IFERROR(BV14-BJ14,"")</f>
-        <v/>
-      </c>
-      <c r="CJ14" s="2" t="inlineStr">
+      <c r="BW14" s="18" t="n"/>
+      <c r="BX14" s="18" t="n"/>
+      <c r="BY14" s="18" t="n"/>
+      <c r="BZ14" s="18" t="n"/>
+      <c r="CA14" s="18" t="n"/>
+      <c r="CB14" s="18" t="n"/>
+      <c r="CC14" s="18" t="n"/>
+      <c r="CD14" s="18" t="n"/>
+      <c r="CE14" s="18" t="n"/>
+      <c r="CF14" s="18" t="n"/>
+      <c r="CG14" s="18" t="n"/>
+      <c r="CH14" s="18" t="n"/>
+      <c r="CJ14" s="17">
+        <f>IFERROR(BV14-BH14,"")</f>
+        <v/>
+      </c>
+      <c r="CK14" s="17">
+        <f>IFERROR(BW14-BI14,"")</f>
+        <v/>
+      </c>
+      <c r="CL14" s="17">
+        <f>IFERROR(BX14-BJ14,"")</f>
+        <v/>
+      </c>
+      <c r="CM14" s="17">
+        <f>IFERROR(BY14-BK14,"")</f>
+        <v/>
+      </c>
+      <c r="CN14" s="17">
+        <f>IFERROR(BZ14-BL14,"")</f>
+        <v/>
+      </c>
+      <c r="CO14" s="17">
+        <f>IFERROR(CA14-BM14,"")</f>
+        <v/>
+      </c>
+      <c r="CP14" s="17">
+        <f>IFERROR(CB14-BN14,"")</f>
+        <v/>
+      </c>
+      <c r="CQ14" s="17">
+        <f>IFERROR(CC14-BO14,"")</f>
+        <v/>
+      </c>
+      <c r="CR14" s="17">
+        <f>IFERROR(CD14-BP14,"")</f>
+        <v/>
+      </c>
+      <c r="CS14" s="17">
+        <f>IFERROR(CE14-BQ14,"")</f>
+        <v/>
+      </c>
+      <c r="CT14" s="17">
+        <f>IFERROR(CF14-BR14,"")</f>
+        <v/>
+      </c>
+      <c r="CU14" s="17">
+        <f>IFERROR(CG14-BS14,"")</f>
+        <v/>
+      </c>
+      <c r="CV14" s="17">
+        <f>IFERROR(CH14-BT14,"")</f>
+        <v/>
+      </c>
+      <c r="CX14" s="2" t="inlineStr">
         <is>
           <t>Level Race</t>
         </is>
@@ -2075,8 +2293,8 @@
       <c r="L15" s="16" t="n"/>
       <c r="M15" s="16" t="n"/>
       <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
       <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="16" t="n"/>
       <c r="R15" s="16" t="n"/>
       <c r="S15" s="16" t="n"/>
       <c r="T15" s="16" t="n"/>
@@ -2086,10 +2304,10 @@
       <c r="X15" s="16" t="n"/>
       <c r="Y15" s="16" t="n"/>
       <c r="Z15" s="16" t="n"/>
-      <c r="AB15" s="17" t="n"/>
-      <c r="AC15" s="17" t="n"/>
-      <c r="AD15" s="17" t="n"/>
-      <c r="AE15" s="17" t="n"/>
+      <c r="AA15" s="16" t="n"/>
+      <c r="AB15" s="16" t="n"/>
+      <c r="AC15" s="16" t="n"/>
+      <c r="AD15" s="16" t="n"/>
       <c r="AF15" s="17" t="n"/>
       <c r="AG15" s="17" t="n"/>
       <c r="AH15" s="17" t="n"/>
@@ -2097,28 +2315,29 @@
       <c r="AJ15" s="17" t="n"/>
       <c r="AK15" s="17" t="n"/>
       <c r="AL15" s="17" t="n"/>
-      <c r="AN15" s="16" t="n"/>
-      <c r="AO15" s="16" t="n"/>
-      <c r="AP15" s="16" t="n"/>
-      <c r="AQ15" s="16" t="n"/>
-      <c r="AR15" s="16" t="n"/>
-      <c r="AS15" s="16" t="n"/>
+      <c r="AM15" s="17" t="n"/>
+      <c r="AN15" s="17" t="n"/>
+      <c r="AO15" s="17" t="n"/>
+      <c r="AP15" s="17" t="n"/>
+      <c r="AQ15" s="17" t="n"/>
+      <c r="AR15" s="17" t="n"/>
       <c r="AT15" s="16" t="n"/>
       <c r="AU15" s="16" t="n"/>
       <c r="AV15" s="16" t="n"/>
       <c r="AW15" s="16" t="n"/>
       <c r="AX15" s="16" t="n"/>
-      <c r="AZ15" s="18" t="n"/>
-      <c r="BA15" s="18" t="n"/>
-      <c r="BB15" s="18" t="n"/>
-      <c r="BC15" s="18" t="n"/>
-      <c r="BD15" s="18" t="n"/>
-      <c r="BE15" s="18" t="n"/>
-      <c r="BF15" s="18" t="n"/>
-      <c r="BG15" s="18" t="n"/>
+      <c r="AY15" s="16" t="n"/>
+      <c r="AZ15" s="16" t="n"/>
+      <c r="BA15" s="16" t="n"/>
+      <c r="BB15" s="16" t="n"/>
+      <c r="BC15" s="16" t="n"/>
+      <c r="BD15" s="16" t="n"/>
+      <c r="BE15" s="16" t="n"/>
+      <c r="BF15" s="16" t="n"/>
       <c r="BH15" s="18" t="n"/>
       <c r="BI15" s="18" t="n"/>
       <c r="BJ15" s="18" t="n"/>
+      <c r="BK15" s="18" t="n"/>
       <c r="BL15" s="18" t="n"/>
       <c r="BM15" s="18" t="n"/>
       <c r="BN15" s="18" t="n"/>
@@ -2128,53 +2347,72 @@
       <c r="BR15" s="18" t="n"/>
       <c r="BS15" s="18" t="n"/>
       <c r="BT15" s="18" t="n"/>
-      <c r="BU15" s="18" t="n"/>
       <c r="BV15" s="18" t="n"/>
-      <c r="BX15" s="17">
-        <f>IFERROR(BL15-AZ15,"")</f>
-        <v/>
-      </c>
-      <c r="BY15" s="17">
-        <f>IFERROR(BM15-BA15,"")</f>
-        <v/>
-      </c>
-      <c r="BZ15" s="17">
-        <f>IFERROR(BN15-BB15,"")</f>
-        <v/>
-      </c>
-      <c r="CA15" s="17">
-        <f>IFERROR(BO15-BC15,"")</f>
-        <v/>
-      </c>
-      <c r="CB15" s="17">
-        <f>IFERROR(BP15-BD15,"")</f>
-        <v/>
-      </c>
-      <c r="CC15" s="17">
-        <f>IFERROR(BQ15-BE15,"")</f>
-        <v/>
-      </c>
-      <c r="CD15" s="17">
-        <f>IFERROR(BR15-BF15,"")</f>
-        <v/>
-      </c>
-      <c r="CE15" s="17">
-        <f>IFERROR(BS15-BG15,"")</f>
-        <v/>
-      </c>
-      <c r="CF15" s="17">
-        <f>IFERROR(BT15-BH15,"")</f>
-        <v/>
-      </c>
-      <c r="CG15" s="17">
-        <f>IFERROR(BU15-BI15,"")</f>
-        <v/>
-      </c>
-      <c r="CH15" s="17">
-        <f>IFERROR(BV15-BJ15,"")</f>
-        <v/>
-      </c>
-      <c r="CJ15" s="2" t="inlineStr">
+      <c r="BW15" s="18" t="n"/>
+      <c r="BX15" s="18" t="n"/>
+      <c r="BY15" s="18" t="n"/>
+      <c r="BZ15" s="18" t="n"/>
+      <c r="CA15" s="18" t="n"/>
+      <c r="CB15" s="18" t="n"/>
+      <c r="CC15" s="18" t="n"/>
+      <c r="CD15" s="18" t="n"/>
+      <c r="CE15" s="18" t="n"/>
+      <c r="CF15" s="18" t="n"/>
+      <c r="CG15" s="18" t="n"/>
+      <c r="CH15" s="18" t="n"/>
+      <c r="CJ15" s="17">
+        <f>IFERROR(BV15-BH15,"")</f>
+        <v/>
+      </c>
+      <c r="CK15" s="17">
+        <f>IFERROR(BW15-BI15,"")</f>
+        <v/>
+      </c>
+      <c r="CL15" s="17">
+        <f>IFERROR(BX15-BJ15,"")</f>
+        <v/>
+      </c>
+      <c r="CM15" s="17">
+        <f>IFERROR(BY15-BK15,"")</f>
+        <v/>
+      </c>
+      <c r="CN15" s="17">
+        <f>IFERROR(BZ15-BL15,"")</f>
+        <v/>
+      </c>
+      <c r="CO15" s="17">
+        <f>IFERROR(CA15-BM15,"")</f>
+        <v/>
+      </c>
+      <c r="CP15" s="17">
+        <f>IFERROR(CB15-BN15,"")</f>
+        <v/>
+      </c>
+      <c r="CQ15" s="17">
+        <f>IFERROR(CC15-BO15,"")</f>
+        <v/>
+      </c>
+      <c r="CR15" s="17">
+        <f>IFERROR(CD15-BP15,"")</f>
+        <v/>
+      </c>
+      <c r="CS15" s="17">
+        <f>IFERROR(CE15-BQ15,"")</f>
+        <v/>
+      </c>
+      <c r="CT15" s="17">
+        <f>IFERROR(CF15-BR15,"")</f>
+        <v/>
+      </c>
+      <c r="CU15" s="17">
+        <f>IFERROR(CG15-BS15,"")</f>
+        <v/>
+      </c>
+      <c r="CV15" s="17">
+        <f>IFERROR(CH15-BT15,"")</f>
+        <v/>
+      </c>
+      <c r="CX15" s="2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -2200,8 +2438,8 @@
       <c r="L16" s="16" t="n"/>
       <c r="M16" s="16" t="n"/>
       <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
       <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
       <c r="R16" s="16" t="n"/>
       <c r="S16" s="16" t="n"/>
       <c r="T16" s="16" t="n"/>
@@ -2211,10 +2449,10 @@
       <c r="X16" s="16" t="n"/>
       <c r="Y16" s="16" t="n"/>
       <c r="Z16" s="16" t="n"/>
-      <c r="AB16" s="17" t="n"/>
-      <c r="AC16" s="17" t="n"/>
-      <c r="AD16" s="17" t="n"/>
-      <c r="AE16" s="17" t="n"/>
+      <c r="AA16" s="16" t="n"/>
+      <c r="AB16" s="16" t="n"/>
+      <c r="AC16" s="16" t="n"/>
+      <c r="AD16" s="16" t="n"/>
       <c r="AF16" s="17" t="n"/>
       <c r="AG16" s="17" t="n"/>
       <c r="AH16" s="17" t="n"/>
@@ -2222,28 +2460,29 @@
       <c r="AJ16" s="17" t="n"/>
       <c r="AK16" s="17" t="n"/>
       <c r="AL16" s="17" t="n"/>
-      <c r="AN16" s="16" t="n"/>
-      <c r="AO16" s="16" t="n"/>
-      <c r="AP16" s="16" t="n"/>
-      <c r="AQ16" s="16" t="n"/>
-      <c r="AR16" s="16" t="n"/>
-      <c r="AS16" s="16" t="n"/>
+      <c r="AM16" s="17" t="n"/>
+      <c r="AN16" s="17" t="n"/>
+      <c r="AO16" s="17" t="n"/>
+      <c r="AP16" s="17" t="n"/>
+      <c r="AQ16" s="17" t="n"/>
+      <c r="AR16" s="17" t="n"/>
       <c r="AT16" s="16" t="n"/>
       <c r="AU16" s="16" t="n"/>
       <c r="AV16" s="16" t="n"/>
       <c r="AW16" s="16" t="n"/>
       <c r="AX16" s="16" t="n"/>
-      <c r="AZ16" s="18" t="n"/>
-      <c r="BA16" s="18" t="n"/>
-      <c r="BB16" s="18" t="n"/>
-      <c r="BC16" s="18" t="n"/>
-      <c r="BD16" s="18" t="n"/>
-      <c r="BE16" s="18" t="n"/>
-      <c r="BF16" s="18" t="n"/>
-      <c r="BG16" s="18" t="n"/>
+      <c r="AY16" s="16" t="n"/>
+      <c r="AZ16" s="16" t="n"/>
+      <c r="BA16" s="16" t="n"/>
+      <c r="BB16" s="16" t="n"/>
+      <c r="BC16" s="16" t="n"/>
+      <c r="BD16" s="16" t="n"/>
+      <c r="BE16" s="16" t="n"/>
+      <c r="BF16" s="16" t="n"/>
       <c r="BH16" s="18" t="n"/>
       <c r="BI16" s="18" t="n"/>
       <c r="BJ16" s="18" t="n"/>
+      <c r="BK16" s="18" t="n"/>
       <c r="BL16" s="18" t="n"/>
       <c r="BM16" s="18" t="n"/>
       <c r="BN16" s="18" t="n"/>
@@ -2253,53 +2492,72 @@
       <c r="BR16" s="18" t="n"/>
       <c r="BS16" s="18" t="n"/>
       <c r="BT16" s="18" t="n"/>
-      <c r="BU16" s="18" t="n"/>
       <c r="BV16" s="18" t="n"/>
-      <c r="BX16" s="17">
-        <f>IFERROR(BL16-AZ16,"")</f>
-        <v/>
-      </c>
-      <c r="BY16" s="17">
-        <f>IFERROR(BM16-BA16,"")</f>
-        <v/>
-      </c>
-      <c r="BZ16" s="17">
-        <f>IFERROR(BN16-BB16,"")</f>
-        <v/>
-      </c>
-      <c r="CA16" s="17">
-        <f>IFERROR(BO16-BC16,"")</f>
-        <v/>
-      </c>
-      <c r="CB16" s="17">
-        <f>IFERROR(BP16-BD16,"")</f>
-        <v/>
-      </c>
-      <c r="CC16" s="17">
-        <f>IFERROR(BQ16-BE16,"")</f>
-        <v/>
-      </c>
-      <c r="CD16" s="17">
-        <f>IFERROR(BR16-BF16,"")</f>
-        <v/>
-      </c>
-      <c r="CE16" s="17">
-        <f>IFERROR(BS16-BG16,"")</f>
-        <v/>
-      </c>
-      <c r="CF16" s="17">
-        <f>IFERROR(BT16-BH16,"")</f>
-        <v/>
-      </c>
-      <c r="CG16" s="17">
-        <f>IFERROR(BU16-BI16,"")</f>
-        <v/>
-      </c>
-      <c r="CH16" s="17">
-        <f>IFERROR(BV16-BJ16,"")</f>
-        <v/>
-      </c>
-      <c r="CJ16" s="2" t="inlineStr">
+      <c r="BW16" s="18" t="n"/>
+      <c r="BX16" s="18" t="n"/>
+      <c r="BY16" s="18" t="n"/>
+      <c r="BZ16" s="18" t="n"/>
+      <c r="CA16" s="18" t="n"/>
+      <c r="CB16" s="18" t="n"/>
+      <c r="CC16" s="18" t="n"/>
+      <c r="CD16" s="18" t="n"/>
+      <c r="CE16" s="18" t="n"/>
+      <c r="CF16" s="18" t="n"/>
+      <c r="CG16" s="18" t="n"/>
+      <c r="CH16" s="18" t="n"/>
+      <c r="CJ16" s="17">
+        <f>IFERROR(BV16-BH16,"")</f>
+        <v/>
+      </c>
+      <c r="CK16" s="17">
+        <f>IFERROR(BW16-BI16,"")</f>
+        <v/>
+      </c>
+      <c r="CL16" s="17">
+        <f>IFERROR(BX16-BJ16,"")</f>
+        <v/>
+      </c>
+      <c r="CM16" s="17">
+        <f>IFERROR(BY16-BK16,"")</f>
+        <v/>
+      </c>
+      <c r="CN16" s="17">
+        <f>IFERROR(BZ16-BL16,"")</f>
+        <v/>
+      </c>
+      <c r="CO16" s="17">
+        <f>IFERROR(CA16-BM16,"")</f>
+        <v/>
+      </c>
+      <c r="CP16" s="17">
+        <f>IFERROR(CB16-BN16,"")</f>
+        <v/>
+      </c>
+      <c r="CQ16" s="17">
+        <f>IFERROR(CC16-BO16,"")</f>
+        <v/>
+      </c>
+      <c r="CR16" s="17">
+        <f>IFERROR(CD16-BP16,"")</f>
+        <v/>
+      </c>
+      <c r="CS16" s="17">
+        <f>IFERROR(CE16-BQ16,"")</f>
+        <v/>
+      </c>
+      <c r="CT16" s="17">
+        <f>IFERROR(CF16-BR16,"")</f>
+        <v/>
+      </c>
+      <c r="CU16" s="17">
+        <f>IFERROR(CG16-BS16,"")</f>
+        <v/>
+      </c>
+      <c r="CV16" s="17">
+        <f>IFERROR(CH16-BT16,"")</f>
+        <v/>
+      </c>
+      <c r="CX16" s="2" t="inlineStr">
         <is>
           <t>Photoshoot</t>
         </is>
@@ -2325,8 +2583,8 @@
       <c r="L17" s="16" t="n"/>
       <c r="M17" s="16" t="n"/>
       <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
       <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
       <c r="R17" s="16" t="n"/>
       <c r="S17" s="16" t="n"/>
       <c r="T17" s="16" t="n"/>
@@ -2336,10 +2594,10 @@
       <c r="X17" s="16" t="n"/>
       <c r="Y17" s="16" t="n"/>
       <c r="Z17" s="16" t="n"/>
-      <c r="AB17" s="17" t="n"/>
-      <c r="AC17" s="17" t="n"/>
-      <c r="AD17" s="17" t="n"/>
-      <c r="AE17" s="17" t="n"/>
+      <c r="AA17" s="16" t="n"/>
+      <c r="AB17" s="16" t="n"/>
+      <c r="AC17" s="16" t="n"/>
+      <c r="AD17" s="16" t="n"/>
       <c r="AF17" s="17" t="n"/>
       <c r="AG17" s="17" t="n"/>
       <c r="AH17" s="17" t="n"/>
@@ -2347,28 +2605,29 @@
       <c r="AJ17" s="17" t="n"/>
       <c r="AK17" s="17" t="n"/>
       <c r="AL17" s="17" t="n"/>
-      <c r="AN17" s="16" t="n"/>
-      <c r="AO17" s="16" t="n"/>
-      <c r="AP17" s="16" t="n"/>
-      <c r="AQ17" s="16" t="n"/>
-      <c r="AR17" s="16" t="n"/>
-      <c r="AS17" s="16" t="n"/>
+      <c r="AM17" s="17" t="n"/>
+      <c r="AN17" s="17" t="n"/>
+      <c r="AO17" s="17" t="n"/>
+      <c r="AP17" s="17" t="n"/>
+      <c r="AQ17" s="17" t="n"/>
+      <c r="AR17" s="17" t="n"/>
       <c r="AT17" s="16" t="n"/>
       <c r="AU17" s="16" t="n"/>
       <c r="AV17" s="16" t="n"/>
       <c r="AW17" s="16" t="n"/>
       <c r="AX17" s="16" t="n"/>
-      <c r="AZ17" s="18" t="n"/>
-      <c r="BA17" s="18" t="n"/>
-      <c r="BB17" s="18" t="n"/>
-      <c r="BC17" s="18" t="n"/>
-      <c r="BD17" s="18" t="n"/>
-      <c r="BE17" s="18" t="n"/>
-      <c r="BF17" s="18" t="n"/>
-      <c r="BG17" s="18" t="n"/>
+      <c r="AY17" s="16" t="n"/>
+      <c r="AZ17" s="16" t="n"/>
+      <c r="BA17" s="16" t="n"/>
+      <c r="BB17" s="16" t="n"/>
+      <c r="BC17" s="16" t="n"/>
+      <c r="BD17" s="16" t="n"/>
+      <c r="BE17" s="16" t="n"/>
+      <c r="BF17" s="16" t="n"/>
       <c r="BH17" s="18" t="n"/>
       <c r="BI17" s="18" t="n"/>
       <c r="BJ17" s="18" t="n"/>
+      <c r="BK17" s="18" t="n"/>
       <c r="BL17" s="18" t="n"/>
       <c r="BM17" s="18" t="n"/>
       <c r="BN17" s="18" t="n"/>
@@ -2378,53 +2637,72 @@
       <c r="BR17" s="18" t="n"/>
       <c r="BS17" s="18" t="n"/>
       <c r="BT17" s="18" t="n"/>
-      <c r="BU17" s="18" t="n"/>
       <c r="BV17" s="18" t="n"/>
-      <c r="BX17" s="17">
-        <f>IFERROR(BL17-AZ17,"")</f>
-        <v/>
-      </c>
-      <c r="BY17" s="17">
-        <f>IFERROR(BM17-BA17,"")</f>
-        <v/>
-      </c>
-      <c r="BZ17" s="17">
-        <f>IFERROR(BN17-BB17,"")</f>
-        <v/>
-      </c>
-      <c r="CA17" s="17">
-        <f>IFERROR(BO17-BC17,"")</f>
-        <v/>
-      </c>
-      <c r="CB17" s="17">
-        <f>IFERROR(BP17-BD17,"")</f>
-        <v/>
-      </c>
-      <c r="CC17" s="17">
-        <f>IFERROR(BQ17-BE17,"")</f>
-        <v/>
-      </c>
-      <c r="CD17" s="17">
-        <f>IFERROR(BR17-BF17,"")</f>
-        <v/>
-      </c>
-      <c r="CE17" s="17">
-        <f>IFERROR(BS17-BG17,"")</f>
-        <v/>
-      </c>
-      <c r="CF17" s="17">
-        <f>IFERROR(BT17-BH17,"")</f>
-        <v/>
-      </c>
-      <c r="CG17" s="17">
-        <f>IFERROR(BU17-BI17,"")</f>
-        <v/>
-      </c>
-      <c r="CH17" s="17">
-        <f>IFERROR(BV17-BJ17,"")</f>
-        <v/>
-      </c>
-      <c r="CJ17" s="2" t="inlineStr">
+      <c r="BW17" s="18" t="n"/>
+      <c r="BX17" s="18" t="n"/>
+      <c r="BY17" s="18" t="n"/>
+      <c r="BZ17" s="18" t="n"/>
+      <c r="CA17" s="18" t="n"/>
+      <c r="CB17" s="18" t="n"/>
+      <c r="CC17" s="18" t="n"/>
+      <c r="CD17" s="18" t="n"/>
+      <c r="CE17" s="18" t="n"/>
+      <c r="CF17" s="18" t="n"/>
+      <c r="CG17" s="18" t="n"/>
+      <c r="CH17" s="18" t="n"/>
+      <c r="CJ17" s="17">
+        <f>IFERROR(BV17-BH17,"")</f>
+        <v/>
+      </c>
+      <c r="CK17" s="17">
+        <f>IFERROR(BW17-BI17,"")</f>
+        <v/>
+      </c>
+      <c r="CL17" s="17">
+        <f>IFERROR(BX17-BJ17,"")</f>
+        <v/>
+      </c>
+      <c r="CM17" s="17">
+        <f>IFERROR(BY17-BK17,"")</f>
+        <v/>
+      </c>
+      <c r="CN17" s="17">
+        <f>IFERROR(BZ17-BL17,"")</f>
+        <v/>
+      </c>
+      <c r="CO17" s="17">
+        <f>IFERROR(CA17-BM17,"")</f>
+        <v/>
+      </c>
+      <c r="CP17" s="17">
+        <f>IFERROR(CB17-BN17,"")</f>
+        <v/>
+      </c>
+      <c r="CQ17" s="17">
+        <f>IFERROR(CC17-BO17,"")</f>
+        <v/>
+      </c>
+      <c r="CR17" s="17">
+        <f>IFERROR(CD17-BP17,"")</f>
+        <v/>
+      </c>
+      <c r="CS17" s="17">
+        <f>IFERROR(CE17-BQ17,"")</f>
+        <v/>
+      </c>
+      <c r="CT17" s="17">
+        <f>IFERROR(CF17-BR17,"")</f>
+        <v/>
+      </c>
+      <c r="CU17" s="17">
+        <f>IFERROR(CG17-BS17,"")</f>
+        <v/>
+      </c>
+      <c r="CV17" s="17">
+        <f>IFERROR(CH17-BT17,"")</f>
+        <v/>
+      </c>
+      <c r="CX17" s="2" t="inlineStr">
         <is>
           <t>Red Challenge</t>
         </is>
@@ -2450,8 +2728,8 @@
       <c r="L18" s="16" t="n"/>
       <c r="M18" s="16" t="n"/>
       <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
       <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
       <c r="R18" s="16" t="n"/>
       <c r="S18" s="16" t="n"/>
       <c r="T18" s="16" t="n"/>
@@ -2461,10 +2739,10 @@
       <c r="X18" s="16" t="n"/>
       <c r="Y18" s="16" t="n"/>
       <c r="Z18" s="16" t="n"/>
-      <c r="AB18" s="17" t="n"/>
-      <c r="AC18" s="17" t="n"/>
-      <c r="AD18" s="17" t="n"/>
-      <c r="AE18" s="17" t="n"/>
+      <c r="AA18" s="16" t="n"/>
+      <c r="AB18" s="16" t="n"/>
+      <c r="AC18" s="16" t="n"/>
+      <c r="AD18" s="16" t="n"/>
       <c r="AF18" s="17" t="n"/>
       <c r="AG18" s="17" t="n"/>
       <c r="AH18" s="17" t="n"/>
@@ -2472,28 +2750,29 @@
       <c r="AJ18" s="17" t="n"/>
       <c r="AK18" s="17" t="n"/>
       <c r="AL18" s="17" t="n"/>
-      <c r="AN18" s="16" t="n"/>
-      <c r="AO18" s="16" t="n"/>
-      <c r="AP18" s="16" t="n"/>
-      <c r="AQ18" s="16" t="n"/>
-      <c r="AR18" s="16" t="n"/>
-      <c r="AS18" s="16" t="n"/>
+      <c r="AM18" s="17" t="n"/>
+      <c r="AN18" s="17" t="n"/>
+      <c r="AO18" s="17" t="n"/>
+      <c r="AP18" s="17" t="n"/>
+      <c r="AQ18" s="17" t="n"/>
+      <c r="AR18" s="17" t="n"/>
       <c r="AT18" s="16" t="n"/>
       <c r="AU18" s="16" t="n"/>
       <c r="AV18" s="16" t="n"/>
       <c r="AW18" s="16" t="n"/>
       <c r="AX18" s="16" t="n"/>
-      <c r="AZ18" s="18" t="n"/>
-      <c r="BA18" s="18" t="n"/>
-      <c r="BB18" s="18" t="n"/>
-      <c r="BC18" s="18" t="n"/>
-      <c r="BD18" s="18" t="n"/>
-      <c r="BE18" s="18" t="n"/>
-      <c r="BF18" s="18" t="n"/>
-      <c r="BG18" s="18" t="n"/>
+      <c r="AY18" s="16" t="n"/>
+      <c r="AZ18" s="16" t="n"/>
+      <c r="BA18" s="16" t="n"/>
+      <c r="BB18" s="16" t="n"/>
+      <c r="BC18" s="16" t="n"/>
+      <c r="BD18" s="16" t="n"/>
+      <c r="BE18" s="16" t="n"/>
+      <c r="BF18" s="16" t="n"/>
       <c r="BH18" s="18" t="n"/>
       <c r="BI18" s="18" t="n"/>
       <c r="BJ18" s="18" t="n"/>
+      <c r="BK18" s="18" t="n"/>
       <c r="BL18" s="18" t="n"/>
       <c r="BM18" s="18" t="n"/>
       <c r="BN18" s="18" t="n"/>
@@ -2503,53 +2782,72 @@
       <c r="BR18" s="18" t="n"/>
       <c r="BS18" s="18" t="n"/>
       <c r="BT18" s="18" t="n"/>
-      <c r="BU18" s="18" t="n"/>
       <c r="BV18" s="18" t="n"/>
-      <c r="BX18" s="17">
-        <f>IFERROR(BL18-AZ18,"")</f>
-        <v/>
-      </c>
-      <c r="BY18" s="17">
-        <f>IFERROR(BM18-BA18,"")</f>
-        <v/>
-      </c>
-      <c r="BZ18" s="17">
-        <f>IFERROR(BN18-BB18,"")</f>
-        <v/>
-      </c>
-      <c r="CA18" s="17">
-        <f>IFERROR(BO18-BC18,"")</f>
-        <v/>
-      </c>
-      <c r="CB18" s="17">
-        <f>IFERROR(BP18-BD18,"")</f>
-        <v/>
-      </c>
-      <c r="CC18" s="17">
-        <f>IFERROR(BQ18-BE18,"")</f>
-        <v/>
-      </c>
-      <c r="CD18" s="17">
-        <f>IFERROR(BR18-BF18,"")</f>
-        <v/>
-      </c>
-      <c r="CE18" s="17">
-        <f>IFERROR(BS18-BG18,"")</f>
-        <v/>
-      </c>
-      <c r="CF18" s="17">
-        <f>IFERROR(BT18-BH18,"")</f>
-        <v/>
-      </c>
-      <c r="CG18" s="17">
-        <f>IFERROR(BU18-BI18,"")</f>
-        <v/>
-      </c>
-      <c r="CH18" s="17">
-        <f>IFERROR(BV18-BJ18,"")</f>
-        <v/>
-      </c>
-      <c r="CJ18" s="2" t="inlineStr">
+      <c r="BW18" s="18" t="n"/>
+      <c r="BX18" s="18" t="n"/>
+      <c r="BY18" s="18" t="n"/>
+      <c r="BZ18" s="18" t="n"/>
+      <c r="CA18" s="18" t="n"/>
+      <c r="CB18" s="18" t="n"/>
+      <c r="CC18" s="18" t="n"/>
+      <c r="CD18" s="18" t="n"/>
+      <c r="CE18" s="18" t="n"/>
+      <c r="CF18" s="18" t="n"/>
+      <c r="CG18" s="18" t="n"/>
+      <c r="CH18" s="18" t="n"/>
+      <c r="CJ18" s="17">
+        <f>IFERROR(BV18-BH18,"")</f>
+        <v/>
+      </c>
+      <c r="CK18" s="17">
+        <f>IFERROR(BW18-BI18,"")</f>
+        <v/>
+      </c>
+      <c r="CL18" s="17">
+        <f>IFERROR(BX18-BJ18,"")</f>
+        <v/>
+      </c>
+      <c r="CM18" s="17">
+        <f>IFERROR(BY18-BK18,"")</f>
+        <v/>
+      </c>
+      <c r="CN18" s="17">
+        <f>IFERROR(BZ18-BL18,"")</f>
+        <v/>
+      </c>
+      <c r="CO18" s="17">
+        <f>IFERROR(CA18-BM18,"")</f>
+        <v/>
+      </c>
+      <c r="CP18" s="17">
+        <f>IFERROR(CB18-BN18,"")</f>
+        <v/>
+      </c>
+      <c r="CQ18" s="17">
+        <f>IFERROR(CC18-BO18,"")</f>
+        <v/>
+      </c>
+      <c r="CR18" s="17">
+        <f>IFERROR(CD18-BP18,"")</f>
+        <v/>
+      </c>
+      <c r="CS18" s="17">
+        <f>IFERROR(CE18-BQ18,"")</f>
+        <v/>
+      </c>
+      <c r="CT18" s="17">
+        <f>IFERROR(CF18-BR18,"")</f>
+        <v/>
+      </c>
+      <c r="CU18" s="17">
+        <f>IFERROR(CG18-BS18,"")</f>
+        <v/>
+      </c>
+      <c r="CV18" s="17">
+        <f>IFERROR(CH18-BT18,"")</f>
+        <v/>
+      </c>
+      <c r="CX18" s="2" t="inlineStr">
         <is>
           <t>River Rush</t>
         </is>
@@ -2575,8 +2873,8 @@
       <c r="L19" s="16" t="n"/>
       <c r="M19" s="16" t="n"/>
       <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
       <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
       <c r="R19" s="16" t="n"/>
       <c r="S19" s="16" t="n"/>
       <c r="T19" s="16" t="n"/>
@@ -2586,10 +2884,10 @@
       <c r="X19" s="16" t="n"/>
       <c r="Y19" s="16" t="n"/>
       <c r="Z19" s="16" t="n"/>
-      <c r="AB19" s="17" t="n"/>
-      <c r="AC19" s="17" t="n"/>
-      <c r="AD19" s="17" t="n"/>
-      <c r="AE19" s="17" t="n"/>
+      <c r="AA19" s="16" t="n"/>
+      <c r="AB19" s="16" t="n"/>
+      <c r="AC19" s="16" t="n"/>
+      <c r="AD19" s="16" t="n"/>
       <c r="AF19" s="17" t="n"/>
       <c r="AG19" s="17" t="n"/>
       <c r="AH19" s="17" t="n"/>
@@ -2597,28 +2895,29 @@
       <c r="AJ19" s="17" t="n"/>
       <c r="AK19" s="17" t="n"/>
       <c r="AL19" s="17" t="n"/>
-      <c r="AN19" s="16" t="n"/>
-      <c r="AO19" s="16" t="n"/>
-      <c r="AP19" s="16" t="n"/>
-      <c r="AQ19" s="16" t="n"/>
-      <c r="AR19" s="16" t="n"/>
-      <c r="AS19" s="16" t="n"/>
+      <c r="AM19" s="17" t="n"/>
+      <c r="AN19" s="17" t="n"/>
+      <c r="AO19" s="17" t="n"/>
+      <c r="AP19" s="17" t="n"/>
+      <c r="AQ19" s="17" t="n"/>
+      <c r="AR19" s="17" t="n"/>
       <c r="AT19" s="16" t="n"/>
       <c r="AU19" s="16" t="n"/>
       <c r="AV19" s="16" t="n"/>
       <c r="AW19" s="16" t="n"/>
       <c r="AX19" s="16" t="n"/>
-      <c r="AZ19" s="18" t="n"/>
-      <c r="BA19" s="18" t="n"/>
-      <c r="BB19" s="18" t="n"/>
-      <c r="BC19" s="18" t="n"/>
-      <c r="BD19" s="18" t="n"/>
-      <c r="BE19" s="18" t="n"/>
-      <c r="BF19" s="18" t="n"/>
-      <c r="BG19" s="18" t="n"/>
+      <c r="AY19" s="16" t="n"/>
+      <c r="AZ19" s="16" t="n"/>
+      <c r="BA19" s="16" t="n"/>
+      <c r="BB19" s="16" t="n"/>
+      <c r="BC19" s="16" t="n"/>
+      <c r="BD19" s="16" t="n"/>
+      <c r="BE19" s="16" t="n"/>
+      <c r="BF19" s="16" t="n"/>
       <c r="BH19" s="18" t="n"/>
       <c r="BI19" s="18" t="n"/>
       <c r="BJ19" s="18" t="n"/>
+      <c r="BK19" s="18" t="n"/>
       <c r="BL19" s="18" t="n"/>
       <c r="BM19" s="18" t="n"/>
       <c r="BN19" s="18" t="n"/>
@@ -2628,53 +2927,72 @@
       <c r="BR19" s="18" t="n"/>
       <c r="BS19" s="18" t="n"/>
       <c r="BT19" s="18" t="n"/>
-      <c r="BU19" s="18" t="n"/>
       <c r="BV19" s="18" t="n"/>
-      <c r="BX19" s="17">
-        <f>IFERROR(BL19-AZ19,"")</f>
-        <v/>
-      </c>
-      <c r="BY19" s="17">
-        <f>IFERROR(BM19-BA19,"")</f>
-        <v/>
-      </c>
-      <c r="BZ19" s="17">
-        <f>IFERROR(BN19-BB19,"")</f>
-        <v/>
-      </c>
-      <c r="CA19" s="17">
-        <f>IFERROR(BO19-BC19,"")</f>
-        <v/>
-      </c>
-      <c r="CB19" s="17">
-        <f>IFERROR(BP19-BD19,"")</f>
-        <v/>
-      </c>
-      <c r="CC19" s="17">
-        <f>IFERROR(BQ19-BE19,"")</f>
-        <v/>
-      </c>
-      <c r="CD19" s="17">
-        <f>IFERROR(BR19-BF19,"")</f>
-        <v/>
-      </c>
-      <c r="CE19" s="17">
-        <f>IFERROR(BS19-BG19,"")</f>
-        <v/>
-      </c>
-      <c r="CF19" s="17">
-        <f>IFERROR(BT19-BH19,"")</f>
-        <v/>
-      </c>
-      <c r="CG19" s="17">
-        <f>IFERROR(BU19-BI19,"")</f>
-        <v/>
-      </c>
-      <c r="CH19" s="17">
-        <f>IFERROR(BV19-BJ19,"")</f>
-        <v/>
-      </c>
-      <c r="CJ19" s="2" t="inlineStr">
+      <c r="BW19" s="18" t="n"/>
+      <c r="BX19" s="18" t="n"/>
+      <c r="BY19" s="18" t="n"/>
+      <c r="BZ19" s="18" t="n"/>
+      <c r="CA19" s="18" t="n"/>
+      <c r="CB19" s="18" t="n"/>
+      <c r="CC19" s="18" t="n"/>
+      <c r="CD19" s="18" t="n"/>
+      <c r="CE19" s="18" t="n"/>
+      <c r="CF19" s="18" t="n"/>
+      <c r="CG19" s="18" t="n"/>
+      <c r="CH19" s="18" t="n"/>
+      <c r="CJ19" s="17">
+        <f>IFERROR(BV19-BH19,"")</f>
+        <v/>
+      </c>
+      <c r="CK19" s="17">
+        <f>IFERROR(BW19-BI19,"")</f>
+        <v/>
+      </c>
+      <c r="CL19" s="17">
+        <f>IFERROR(BX19-BJ19,"")</f>
+        <v/>
+      </c>
+      <c r="CM19" s="17">
+        <f>IFERROR(BY19-BK19,"")</f>
+        <v/>
+      </c>
+      <c r="CN19" s="17">
+        <f>IFERROR(BZ19-BL19,"")</f>
+        <v/>
+      </c>
+      <c r="CO19" s="17">
+        <f>IFERROR(CA19-BM19,"")</f>
+        <v/>
+      </c>
+      <c r="CP19" s="17">
+        <f>IFERROR(CB19-BN19,"")</f>
+        <v/>
+      </c>
+      <c r="CQ19" s="17">
+        <f>IFERROR(CC19-BO19,"")</f>
+        <v/>
+      </c>
+      <c r="CR19" s="17">
+        <f>IFERROR(CD19-BP19,"")</f>
+        <v/>
+      </c>
+      <c r="CS19" s="17">
+        <f>IFERROR(CE19-BQ19,"")</f>
+        <v/>
+      </c>
+      <c r="CT19" s="17">
+        <f>IFERROR(CF19-BR19,"")</f>
+        <v/>
+      </c>
+      <c r="CU19" s="17">
+        <f>IFERROR(CG19-BS19,"")</f>
+        <v/>
+      </c>
+      <c r="CV19" s="17">
+        <f>IFERROR(CH19-BT19,"")</f>
+        <v/>
+      </c>
+      <c r="CX19" s="2" t="inlineStr">
         <is>
           <t>Saga</t>
         </is>
@@ -2700,8 +3018,8 @@
       <c r="L20" s="16" t="n"/>
       <c r="M20" s="16" t="n"/>
       <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
       <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
       <c r="R20" s="16" t="n"/>
       <c r="S20" s="16" t="n"/>
       <c r="T20" s="16" t="n"/>
@@ -2711,10 +3029,10 @@
       <c r="X20" s="16" t="n"/>
       <c r="Y20" s="16" t="n"/>
       <c r="Z20" s="16" t="n"/>
-      <c r="AB20" s="17" t="n"/>
-      <c r="AC20" s="17" t="n"/>
-      <c r="AD20" s="17" t="n"/>
-      <c r="AE20" s="17" t="n"/>
+      <c r="AA20" s="16" t="n"/>
+      <c r="AB20" s="16" t="n"/>
+      <c r="AC20" s="16" t="n"/>
+      <c r="AD20" s="16" t="n"/>
       <c r="AF20" s="17" t="n"/>
       <c r="AG20" s="17" t="n"/>
       <c r="AH20" s="17" t="n"/>
@@ -2722,28 +3040,29 @@
       <c r="AJ20" s="17" t="n"/>
       <c r="AK20" s="17" t="n"/>
       <c r="AL20" s="17" t="n"/>
-      <c r="AN20" s="16" t="n"/>
-      <c r="AO20" s="16" t="n"/>
-      <c r="AP20" s="16" t="n"/>
-      <c r="AQ20" s="16" t="n"/>
-      <c r="AR20" s="16" t="n"/>
-      <c r="AS20" s="16" t="n"/>
+      <c r="AM20" s="17" t="n"/>
+      <c r="AN20" s="17" t="n"/>
+      <c r="AO20" s="17" t="n"/>
+      <c r="AP20" s="17" t="n"/>
+      <c r="AQ20" s="17" t="n"/>
+      <c r="AR20" s="17" t="n"/>
       <c r="AT20" s="16" t="n"/>
       <c r="AU20" s="16" t="n"/>
       <c r="AV20" s="16" t="n"/>
       <c r="AW20" s="16" t="n"/>
       <c r="AX20" s="16" t="n"/>
-      <c r="AZ20" s="18" t="n"/>
-      <c r="BA20" s="18" t="n"/>
-      <c r="BB20" s="18" t="n"/>
-      <c r="BC20" s="18" t="n"/>
-      <c r="BD20" s="18" t="n"/>
-      <c r="BE20" s="18" t="n"/>
-      <c r="BF20" s="18" t="n"/>
-      <c r="BG20" s="18" t="n"/>
+      <c r="AY20" s="16" t="n"/>
+      <c r="AZ20" s="16" t="n"/>
+      <c r="BA20" s="16" t="n"/>
+      <c r="BB20" s="16" t="n"/>
+      <c r="BC20" s="16" t="n"/>
+      <c r="BD20" s="16" t="n"/>
+      <c r="BE20" s="16" t="n"/>
+      <c r="BF20" s="16" t="n"/>
       <c r="BH20" s="18" t="n"/>
       <c r="BI20" s="18" t="n"/>
       <c r="BJ20" s="18" t="n"/>
+      <c r="BK20" s="18" t="n"/>
       <c r="BL20" s="18" t="n"/>
       <c r="BM20" s="18" t="n"/>
       <c r="BN20" s="18" t="n"/>
@@ -2753,53 +3072,72 @@
       <c r="BR20" s="18" t="n"/>
       <c r="BS20" s="18" t="n"/>
       <c r="BT20" s="18" t="n"/>
-      <c r="BU20" s="18" t="n"/>
       <c r="BV20" s="18" t="n"/>
-      <c r="BX20" s="17">
-        <f>IFERROR(BL20-AZ20,"")</f>
-        <v/>
-      </c>
-      <c r="BY20" s="17">
-        <f>IFERROR(BM20-BA20,"")</f>
-        <v/>
-      </c>
-      <c r="BZ20" s="17">
-        <f>IFERROR(BN20-BB20,"")</f>
-        <v/>
-      </c>
-      <c r="CA20" s="17">
-        <f>IFERROR(BO20-BC20,"")</f>
-        <v/>
-      </c>
-      <c r="CB20" s="17">
-        <f>IFERROR(BP20-BD20,"")</f>
-        <v/>
-      </c>
-      <c r="CC20" s="17">
-        <f>IFERROR(BQ20-BE20,"")</f>
-        <v/>
-      </c>
-      <c r="CD20" s="17">
-        <f>IFERROR(BR20-BF20,"")</f>
-        <v/>
-      </c>
-      <c r="CE20" s="17">
-        <f>IFERROR(BS20-BG20,"")</f>
-        <v/>
-      </c>
-      <c r="CF20" s="17">
-        <f>IFERROR(BT20-BH20,"")</f>
-        <v/>
-      </c>
-      <c r="CG20" s="17">
-        <f>IFERROR(BU20-BI20,"")</f>
-        <v/>
-      </c>
-      <c r="CH20" s="17">
-        <f>IFERROR(BV20-BJ20,"")</f>
-        <v/>
-      </c>
-      <c r="CJ20" s="2" t="inlineStr">
+      <c r="BW20" s="18" t="n"/>
+      <c r="BX20" s="18" t="n"/>
+      <c r="BY20" s="18" t="n"/>
+      <c r="BZ20" s="18" t="n"/>
+      <c r="CA20" s="18" t="n"/>
+      <c r="CB20" s="18" t="n"/>
+      <c r="CC20" s="18" t="n"/>
+      <c r="CD20" s="18" t="n"/>
+      <c r="CE20" s="18" t="n"/>
+      <c r="CF20" s="18" t="n"/>
+      <c r="CG20" s="18" t="n"/>
+      <c r="CH20" s="18" t="n"/>
+      <c r="CJ20" s="17">
+        <f>IFERROR(BV20-BH20,"")</f>
+        <v/>
+      </c>
+      <c r="CK20" s="17">
+        <f>IFERROR(BW20-BI20,"")</f>
+        <v/>
+      </c>
+      <c r="CL20" s="17">
+        <f>IFERROR(BX20-BJ20,"")</f>
+        <v/>
+      </c>
+      <c r="CM20" s="17">
+        <f>IFERROR(BY20-BK20,"")</f>
+        <v/>
+      </c>
+      <c r="CN20" s="17">
+        <f>IFERROR(BZ20-BL20,"")</f>
+        <v/>
+      </c>
+      <c r="CO20" s="17">
+        <f>IFERROR(CA20-BM20,"")</f>
+        <v/>
+      </c>
+      <c r="CP20" s="17">
+        <f>IFERROR(CB20-BN20,"")</f>
+        <v/>
+      </c>
+      <c r="CQ20" s="17">
+        <f>IFERROR(CC20-BO20,"")</f>
+        <v/>
+      </c>
+      <c r="CR20" s="17">
+        <f>IFERROR(CD20-BP20,"")</f>
+        <v/>
+      </c>
+      <c r="CS20" s="17">
+        <f>IFERROR(CE20-BQ20,"")</f>
+        <v/>
+      </c>
+      <c r="CT20" s="17">
+        <f>IFERROR(CF20-BR20,"")</f>
+        <v/>
+      </c>
+      <c r="CU20" s="17">
+        <f>IFERROR(CG20-BS20,"")</f>
+        <v/>
+      </c>
+      <c r="CV20" s="17">
+        <f>IFERROR(CH20-BT20,"")</f>
+        <v/>
+      </c>
+      <c r="CX20" s="2" t="inlineStr">
         <is>
           <t>Season Pass (Free)</t>
         </is>
@@ -2825,8 +3163,8 @@
       <c r="L21" s="16" t="n"/>
       <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="n"/>
+      <c r="O21" s="16" t="n"/>
       <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="16" t="n"/>
       <c r="R21" s="16" t="n"/>
       <c r="S21" s="16" t="n"/>
       <c r="T21" s="16" t="n"/>
@@ -2836,10 +3174,10 @@
       <c r="X21" s="16" t="n"/>
       <c r="Y21" s="16" t="n"/>
       <c r="Z21" s="16" t="n"/>
-      <c r="AB21" s="17" t="n"/>
-      <c r="AC21" s="17" t="n"/>
-      <c r="AD21" s="17" t="n"/>
-      <c r="AE21" s="17" t="n"/>
+      <c r="AA21" s="16" t="n"/>
+      <c r="AB21" s="16" t="n"/>
+      <c r="AC21" s="16" t="n"/>
+      <c r="AD21" s="16" t="n"/>
       <c r="AF21" s="17" t="n"/>
       <c r="AG21" s="17" t="n"/>
       <c r="AH21" s="17" t="n"/>
@@ -2847,28 +3185,29 @@
       <c r="AJ21" s="17" t="n"/>
       <c r="AK21" s="17" t="n"/>
       <c r="AL21" s="17" t="n"/>
-      <c r="AN21" s="16" t="n"/>
-      <c r="AO21" s="16" t="n"/>
-      <c r="AP21" s="16" t="n"/>
-      <c r="AQ21" s="16" t="n"/>
-      <c r="AR21" s="16" t="n"/>
-      <c r="AS21" s="16" t="n"/>
+      <c r="AM21" s="17" t="n"/>
+      <c r="AN21" s="17" t="n"/>
+      <c r="AO21" s="17" t="n"/>
+      <c r="AP21" s="17" t="n"/>
+      <c r="AQ21" s="17" t="n"/>
+      <c r="AR21" s="17" t="n"/>
       <c r="AT21" s="16" t="n"/>
       <c r="AU21" s="16" t="n"/>
       <c r="AV21" s="16" t="n"/>
       <c r="AW21" s="16" t="n"/>
       <c r="AX21" s="16" t="n"/>
-      <c r="AZ21" s="18" t="n"/>
-      <c r="BA21" s="18" t="n"/>
-      <c r="BB21" s="18" t="n"/>
-      <c r="BC21" s="18" t="n"/>
-      <c r="BD21" s="18" t="n"/>
-      <c r="BE21" s="18" t="n"/>
-      <c r="BF21" s="18" t="n"/>
-      <c r="BG21" s="18" t="n"/>
+      <c r="AY21" s="16" t="n"/>
+      <c r="AZ21" s="16" t="n"/>
+      <c r="BA21" s="16" t="n"/>
+      <c r="BB21" s="16" t="n"/>
+      <c r="BC21" s="16" t="n"/>
+      <c r="BD21" s="16" t="n"/>
+      <c r="BE21" s="16" t="n"/>
+      <c r="BF21" s="16" t="n"/>
       <c r="BH21" s="18" t="n"/>
       <c r="BI21" s="18" t="n"/>
       <c r="BJ21" s="18" t="n"/>
+      <c r="BK21" s="18" t="n"/>
       <c r="BL21" s="18" t="n"/>
       <c r="BM21" s="18" t="n"/>
       <c r="BN21" s="18" t="n"/>
@@ -2878,53 +3217,72 @@
       <c r="BR21" s="18" t="n"/>
       <c r="BS21" s="18" t="n"/>
       <c r="BT21" s="18" t="n"/>
-      <c r="BU21" s="18" t="n"/>
       <c r="BV21" s="18" t="n"/>
-      <c r="BX21" s="17">
-        <f>IFERROR(BL21-AZ21,"")</f>
-        <v/>
-      </c>
-      <c r="BY21" s="17">
-        <f>IFERROR(BM21-BA21,"")</f>
-        <v/>
-      </c>
-      <c r="BZ21" s="17">
-        <f>IFERROR(BN21-BB21,"")</f>
-        <v/>
-      </c>
-      <c r="CA21" s="17">
-        <f>IFERROR(BO21-BC21,"")</f>
-        <v/>
-      </c>
-      <c r="CB21" s="17">
-        <f>IFERROR(BP21-BD21,"")</f>
-        <v/>
-      </c>
-      <c r="CC21" s="17">
-        <f>IFERROR(BQ21-BE21,"")</f>
-        <v/>
-      </c>
-      <c r="CD21" s="17">
-        <f>IFERROR(BR21-BF21,"")</f>
-        <v/>
-      </c>
-      <c r="CE21" s="17">
-        <f>IFERROR(BS21-BG21,"")</f>
-        <v/>
-      </c>
-      <c r="CF21" s="17">
-        <f>IFERROR(BT21-BH21,"")</f>
-        <v/>
-      </c>
-      <c r="CG21" s="17">
-        <f>IFERROR(BU21-BI21,"")</f>
-        <v/>
-      </c>
-      <c r="CH21" s="17">
-        <f>IFERROR(BV21-BJ21,"")</f>
-        <v/>
-      </c>
-      <c r="CJ21" s="2" t="inlineStr">
+      <c r="BW21" s="18" t="n"/>
+      <c r="BX21" s="18" t="n"/>
+      <c r="BY21" s="18" t="n"/>
+      <c r="BZ21" s="18" t="n"/>
+      <c r="CA21" s="18" t="n"/>
+      <c r="CB21" s="18" t="n"/>
+      <c r="CC21" s="18" t="n"/>
+      <c r="CD21" s="18" t="n"/>
+      <c r="CE21" s="18" t="n"/>
+      <c r="CF21" s="18" t="n"/>
+      <c r="CG21" s="18" t="n"/>
+      <c r="CH21" s="18" t="n"/>
+      <c r="CJ21" s="17">
+        <f>IFERROR(BV21-BH21,"")</f>
+        <v/>
+      </c>
+      <c r="CK21" s="17">
+        <f>IFERROR(BW21-BI21,"")</f>
+        <v/>
+      </c>
+      <c r="CL21" s="17">
+        <f>IFERROR(BX21-BJ21,"")</f>
+        <v/>
+      </c>
+      <c r="CM21" s="17">
+        <f>IFERROR(BY21-BK21,"")</f>
+        <v/>
+      </c>
+      <c r="CN21" s="17">
+        <f>IFERROR(BZ21-BL21,"")</f>
+        <v/>
+      </c>
+      <c r="CO21" s="17">
+        <f>IFERROR(CA21-BM21,"")</f>
+        <v/>
+      </c>
+      <c r="CP21" s="17">
+        <f>IFERROR(CB21-BN21,"")</f>
+        <v/>
+      </c>
+      <c r="CQ21" s="17">
+        <f>IFERROR(CC21-BO21,"")</f>
+        <v/>
+      </c>
+      <c r="CR21" s="17">
+        <f>IFERROR(CD21-BP21,"")</f>
+        <v/>
+      </c>
+      <c r="CS21" s="17">
+        <f>IFERROR(CE21-BQ21,"")</f>
+        <v/>
+      </c>
+      <c r="CT21" s="17">
+        <f>IFERROR(CF21-BR21,"")</f>
+        <v/>
+      </c>
+      <c r="CU21" s="17">
+        <f>IFERROR(CG21-BS21,"")</f>
+        <v/>
+      </c>
+      <c r="CV21" s="17">
+        <f>IFERROR(CH21-BT21,"")</f>
+        <v/>
+      </c>
+      <c r="CX21" s="2" t="inlineStr">
         <is>
           <t>Target Day</t>
         </is>
@@ -2950,8 +3308,8 @@
       <c r="L22" s="16" t="n"/>
       <c r="M22" s="16" t="n"/>
       <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
       <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="16" t="n"/>
       <c r="R22" s="16" t="n"/>
       <c r="S22" s="16" t="n"/>
       <c r="T22" s="16" t="n"/>
@@ -2961,10 +3319,10 @@
       <c r="X22" s="16" t="n"/>
       <c r="Y22" s="16" t="n"/>
       <c r="Z22" s="16" t="n"/>
-      <c r="AB22" s="17" t="n"/>
-      <c r="AC22" s="17" t="n"/>
-      <c r="AD22" s="17" t="n"/>
-      <c r="AE22" s="17" t="n"/>
+      <c r="AA22" s="16" t="n"/>
+      <c r="AB22" s="16" t="n"/>
+      <c r="AC22" s="16" t="n"/>
+      <c r="AD22" s="16" t="n"/>
       <c r="AF22" s="17" t="n"/>
       <c r="AG22" s="17" t="n"/>
       <c r="AH22" s="17" t="n"/>
@@ -2972,28 +3330,29 @@
       <c r="AJ22" s="17" t="n"/>
       <c r="AK22" s="17" t="n"/>
       <c r="AL22" s="17" t="n"/>
-      <c r="AN22" s="16" t="n"/>
-      <c r="AO22" s="16" t="n"/>
-      <c r="AP22" s="16" t="n"/>
-      <c r="AQ22" s="16" t="n"/>
-      <c r="AR22" s="16" t="n"/>
-      <c r="AS22" s="16" t="n"/>
+      <c r="AM22" s="17" t="n"/>
+      <c r="AN22" s="17" t="n"/>
+      <c r="AO22" s="17" t="n"/>
+      <c r="AP22" s="17" t="n"/>
+      <c r="AQ22" s="17" t="n"/>
+      <c r="AR22" s="17" t="n"/>
       <c r="AT22" s="16" t="n"/>
       <c r="AU22" s="16" t="n"/>
       <c r="AV22" s="16" t="n"/>
       <c r="AW22" s="16" t="n"/>
       <c r="AX22" s="16" t="n"/>
-      <c r="AZ22" s="18" t="n"/>
-      <c r="BA22" s="18" t="n"/>
-      <c r="BB22" s="18" t="n"/>
-      <c r="BC22" s="18" t="n"/>
-      <c r="BD22" s="18" t="n"/>
-      <c r="BE22" s="18" t="n"/>
-      <c r="BF22" s="18" t="n"/>
-      <c r="BG22" s="18" t="n"/>
+      <c r="AY22" s="16" t="n"/>
+      <c r="AZ22" s="16" t="n"/>
+      <c r="BA22" s="16" t="n"/>
+      <c r="BB22" s="16" t="n"/>
+      <c r="BC22" s="16" t="n"/>
+      <c r="BD22" s="16" t="n"/>
+      <c r="BE22" s="16" t="n"/>
+      <c r="BF22" s="16" t="n"/>
       <c r="BH22" s="18" t="n"/>
       <c r="BI22" s="18" t="n"/>
       <c r="BJ22" s="18" t="n"/>
+      <c r="BK22" s="18" t="n"/>
       <c r="BL22" s="18" t="n"/>
       <c r="BM22" s="18" t="n"/>
       <c r="BN22" s="18" t="n"/>
@@ -3003,53 +3362,72 @@
       <c r="BR22" s="18" t="n"/>
       <c r="BS22" s="18" t="n"/>
       <c r="BT22" s="18" t="n"/>
-      <c r="BU22" s="18" t="n"/>
       <c r="BV22" s="18" t="n"/>
-      <c r="BX22" s="17">
-        <f>IFERROR(BL22-AZ22,"")</f>
-        <v/>
-      </c>
-      <c r="BY22" s="17">
-        <f>IFERROR(BM22-BA22,"")</f>
-        <v/>
-      </c>
-      <c r="BZ22" s="17">
-        <f>IFERROR(BN22-BB22,"")</f>
-        <v/>
-      </c>
-      <c r="CA22" s="17">
-        <f>IFERROR(BO22-BC22,"")</f>
-        <v/>
-      </c>
-      <c r="CB22" s="17">
-        <f>IFERROR(BP22-BD22,"")</f>
-        <v/>
-      </c>
-      <c r="CC22" s="17">
-        <f>IFERROR(BQ22-BE22,"")</f>
-        <v/>
-      </c>
-      <c r="CD22" s="17">
-        <f>IFERROR(BR22-BF22,"")</f>
-        <v/>
-      </c>
-      <c r="CE22" s="17">
-        <f>IFERROR(BS22-BG22,"")</f>
-        <v/>
-      </c>
-      <c r="CF22" s="17">
-        <f>IFERROR(BT22-BH22,"")</f>
-        <v/>
-      </c>
-      <c r="CG22" s="17">
-        <f>IFERROR(BU22-BI22,"")</f>
-        <v/>
-      </c>
-      <c r="CH22" s="17">
-        <f>IFERROR(BV22-BJ22,"")</f>
-        <v/>
-      </c>
-      <c r="CJ22" s="2" t="inlineStr">
+      <c r="BW22" s="18" t="n"/>
+      <c r="BX22" s="18" t="n"/>
+      <c r="BY22" s="18" t="n"/>
+      <c r="BZ22" s="18" t="n"/>
+      <c r="CA22" s="18" t="n"/>
+      <c r="CB22" s="18" t="n"/>
+      <c r="CC22" s="18" t="n"/>
+      <c r="CD22" s="18" t="n"/>
+      <c r="CE22" s="18" t="n"/>
+      <c r="CF22" s="18" t="n"/>
+      <c r="CG22" s="18" t="n"/>
+      <c r="CH22" s="18" t="n"/>
+      <c r="CJ22" s="17">
+        <f>IFERROR(BV22-BH22,"")</f>
+        <v/>
+      </c>
+      <c r="CK22" s="17">
+        <f>IFERROR(BW22-BI22,"")</f>
+        <v/>
+      </c>
+      <c r="CL22" s="17">
+        <f>IFERROR(BX22-BJ22,"")</f>
+        <v/>
+      </c>
+      <c r="CM22" s="17">
+        <f>IFERROR(BY22-BK22,"")</f>
+        <v/>
+      </c>
+      <c r="CN22" s="17">
+        <f>IFERROR(BZ22-BL22,"")</f>
+        <v/>
+      </c>
+      <c r="CO22" s="17">
+        <f>IFERROR(CA22-BM22,"")</f>
+        <v/>
+      </c>
+      <c r="CP22" s="17">
+        <f>IFERROR(CB22-BN22,"")</f>
+        <v/>
+      </c>
+      <c r="CQ22" s="17">
+        <f>IFERROR(CC22-BO22,"")</f>
+        <v/>
+      </c>
+      <c r="CR22" s="17">
+        <f>IFERROR(CD22-BP22,"")</f>
+        <v/>
+      </c>
+      <c r="CS22" s="17">
+        <f>IFERROR(CE22-BQ22,"")</f>
+        <v/>
+      </c>
+      <c r="CT22" s="17">
+        <f>IFERROR(CF22-BR22,"")</f>
+        <v/>
+      </c>
+      <c r="CU22" s="17">
+        <f>IFERROR(CG22-BS22,"")</f>
+        <v/>
+      </c>
+      <c r="CV22" s="17">
+        <f>IFERROR(CH22-BT22,"")</f>
+        <v/>
+      </c>
+      <c r="CX22" s="2" t="inlineStr">
         <is>
           <t>Team Event</t>
         </is>
@@ -3075,8 +3453,8 @@
       <c r="L23" s="16" t="n"/>
       <c r="M23" s="16" t="n"/>
       <c r="N23" s="16" t="n"/>
+      <c r="O23" s="16" t="n"/>
       <c r="P23" s="16" t="n"/>
-      <c r="Q23" s="16" t="n"/>
       <c r="R23" s="16" t="n"/>
       <c r="S23" s="16" t="n"/>
       <c r="T23" s="16" t="n"/>
@@ -3086,10 +3464,10 @@
       <c r="X23" s="16" t="n"/>
       <c r="Y23" s="16" t="n"/>
       <c r="Z23" s="16" t="n"/>
-      <c r="AB23" s="17" t="n"/>
-      <c r="AC23" s="17" t="n"/>
-      <c r="AD23" s="17" t="n"/>
-      <c r="AE23" s="17" t="n"/>
+      <c r="AA23" s="16" t="n"/>
+      <c r="AB23" s="16" t="n"/>
+      <c r="AC23" s="16" t="n"/>
+      <c r="AD23" s="16" t="n"/>
       <c r="AF23" s="17" t="n"/>
       <c r="AG23" s="17" t="n"/>
       <c r="AH23" s="17" t="n"/>
@@ -3097,28 +3475,29 @@
       <c r="AJ23" s="17" t="n"/>
       <c r="AK23" s="17" t="n"/>
       <c r="AL23" s="17" t="n"/>
-      <c r="AN23" s="16" t="n"/>
-      <c r="AO23" s="16" t="n"/>
-      <c r="AP23" s="16" t="n"/>
-      <c r="AQ23" s="16" t="n"/>
-      <c r="AR23" s="16" t="n"/>
-      <c r="AS23" s="16" t="n"/>
+      <c r="AM23" s="17" t="n"/>
+      <c r="AN23" s="17" t="n"/>
+      <c r="AO23" s="17" t="n"/>
+      <c r="AP23" s="17" t="n"/>
+      <c r="AQ23" s="17" t="n"/>
+      <c r="AR23" s="17" t="n"/>
       <c r="AT23" s="16" t="n"/>
       <c r="AU23" s="16" t="n"/>
       <c r="AV23" s="16" t="n"/>
       <c r="AW23" s="16" t="n"/>
       <c r="AX23" s="16" t="n"/>
-      <c r="AZ23" s="18" t="n"/>
-      <c r="BA23" s="18" t="n"/>
-      <c r="BB23" s="18" t="n"/>
-      <c r="BC23" s="18" t="n"/>
-      <c r="BD23" s="18" t="n"/>
-      <c r="BE23" s="18" t="n"/>
-      <c r="BF23" s="18" t="n"/>
-      <c r="BG23" s="18" t="n"/>
+      <c r="AY23" s="16" t="n"/>
+      <c r="AZ23" s="16" t="n"/>
+      <c r="BA23" s="16" t="n"/>
+      <c r="BB23" s="16" t="n"/>
+      <c r="BC23" s="16" t="n"/>
+      <c r="BD23" s="16" t="n"/>
+      <c r="BE23" s="16" t="n"/>
+      <c r="BF23" s="16" t="n"/>
       <c r="BH23" s="18" t="n"/>
       <c r="BI23" s="18" t="n"/>
       <c r="BJ23" s="18" t="n"/>
+      <c r="BK23" s="18" t="n"/>
       <c r="BL23" s="18" t="n"/>
       <c r="BM23" s="18" t="n"/>
       <c r="BN23" s="18" t="n"/>
@@ -3128,53 +3507,72 @@
       <c r="BR23" s="18" t="n"/>
       <c r="BS23" s="18" t="n"/>
       <c r="BT23" s="18" t="n"/>
-      <c r="BU23" s="18" t="n"/>
       <c r="BV23" s="18" t="n"/>
-      <c r="BX23" s="17">
-        <f>IFERROR(BL23-AZ23,"")</f>
-        <v/>
-      </c>
-      <c r="BY23" s="17">
-        <f>IFERROR(BM23-BA23,"")</f>
-        <v/>
-      </c>
-      <c r="BZ23" s="17">
-        <f>IFERROR(BN23-BB23,"")</f>
-        <v/>
-      </c>
-      <c r="CA23" s="17">
-        <f>IFERROR(BO23-BC23,"")</f>
-        <v/>
-      </c>
-      <c r="CB23" s="17">
-        <f>IFERROR(BP23-BD23,"")</f>
-        <v/>
-      </c>
-      <c r="CC23" s="17">
-        <f>IFERROR(BQ23-BE23,"")</f>
-        <v/>
-      </c>
-      <c r="CD23" s="17">
-        <f>IFERROR(BR23-BF23,"")</f>
-        <v/>
-      </c>
-      <c r="CE23" s="17">
-        <f>IFERROR(BS23-BG23,"")</f>
-        <v/>
-      </c>
-      <c r="CF23" s="17">
-        <f>IFERROR(BT23-BH23,"")</f>
-        <v/>
-      </c>
-      <c r="CG23" s="17">
-        <f>IFERROR(BU23-BI23,"")</f>
-        <v/>
-      </c>
-      <c r="CH23" s="17">
-        <f>IFERROR(BV23-BJ23,"")</f>
-        <v/>
-      </c>
-      <c r="CJ23" s="2" t="inlineStr">
+      <c r="BW23" s="18" t="n"/>
+      <c r="BX23" s="18" t="n"/>
+      <c r="BY23" s="18" t="n"/>
+      <c r="BZ23" s="18" t="n"/>
+      <c r="CA23" s="18" t="n"/>
+      <c r="CB23" s="18" t="n"/>
+      <c r="CC23" s="18" t="n"/>
+      <c r="CD23" s="18" t="n"/>
+      <c r="CE23" s="18" t="n"/>
+      <c r="CF23" s="18" t="n"/>
+      <c r="CG23" s="18" t="n"/>
+      <c r="CH23" s="18" t="n"/>
+      <c r="CJ23" s="17">
+        <f>IFERROR(BV23-BH23,"")</f>
+        <v/>
+      </c>
+      <c r="CK23" s="17">
+        <f>IFERROR(BW23-BI23,"")</f>
+        <v/>
+      </c>
+      <c r="CL23" s="17">
+        <f>IFERROR(BX23-BJ23,"")</f>
+        <v/>
+      </c>
+      <c r="CM23" s="17">
+        <f>IFERROR(BY23-BK23,"")</f>
+        <v/>
+      </c>
+      <c r="CN23" s="17">
+        <f>IFERROR(BZ23-BL23,"")</f>
+        <v/>
+      </c>
+      <c r="CO23" s="17">
+        <f>IFERROR(CA23-BM23,"")</f>
+        <v/>
+      </c>
+      <c r="CP23" s="17">
+        <f>IFERROR(CB23-BN23,"")</f>
+        <v/>
+      </c>
+      <c r="CQ23" s="17">
+        <f>IFERROR(CC23-BO23,"")</f>
+        <v/>
+      </c>
+      <c r="CR23" s="17">
+        <f>IFERROR(CD23-BP23,"")</f>
+        <v/>
+      </c>
+      <c r="CS23" s="17">
+        <f>IFERROR(CE23-BQ23,"")</f>
+        <v/>
+      </c>
+      <c r="CT23" s="17">
+        <f>IFERROR(CF23-BR23,"")</f>
+        <v/>
+      </c>
+      <c r="CU23" s="17">
+        <f>IFERROR(CG23-BS23,"")</f>
+        <v/>
+      </c>
+      <c r="CV23" s="17">
+        <f>IFERROR(CH23-BT23,"")</f>
+        <v/>
+      </c>
+      <c r="CX23" s="2" t="inlineStr">
         <is>
           <t>Team Race</t>
         </is>
@@ -3200,8 +3598,8 @@
       <c r="L24" s="16" t="n"/>
       <c r="M24" s="16" t="n"/>
       <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
       <c r="P24" s="16" t="n"/>
-      <c r="Q24" s="16" t="n"/>
       <c r="R24" s="16" t="n"/>
       <c r="S24" s="16" t="n"/>
       <c r="T24" s="16" t="n"/>
@@ -3211,10 +3609,10 @@
       <c r="X24" s="16" t="n"/>
       <c r="Y24" s="16" t="n"/>
       <c r="Z24" s="16" t="n"/>
-      <c r="AB24" s="17" t="n"/>
-      <c r="AC24" s="17" t="n"/>
-      <c r="AD24" s="17" t="n"/>
-      <c r="AE24" s="17" t="n"/>
+      <c r="AA24" s="16" t="n"/>
+      <c r="AB24" s="16" t="n"/>
+      <c r="AC24" s="16" t="n"/>
+      <c r="AD24" s="16" t="n"/>
       <c r="AF24" s="17" t="n"/>
       <c r="AG24" s="17" t="n"/>
       <c r="AH24" s="17" t="n"/>
@@ -3222,28 +3620,29 @@
       <c r="AJ24" s="17" t="n"/>
       <c r="AK24" s="17" t="n"/>
       <c r="AL24" s="17" t="n"/>
-      <c r="AN24" s="16" t="n"/>
-      <c r="AO24" s="16" t="n"/>
-      <c r="AP24" s="16" t="n"/>
-      <c r="AQ24" s="16" t="n"/>
-      <c r="AR24" s="16" t="n"/>
-      <c r="AS24" s="16" t="n"/>
+      <c r="AM24" s="17" t="n"/>
+      <c r="AN24" s="17" t="n"/>
+      <c r="AO24" s="17" t="n"/>
+      <c r="AP24" s="17" t="n"/>
+      <c r="AQ24" s="17" t="n"/>
+      <c r="AR24" s="17" t="n"/>
       <c r="AT24" s="16" t="n"/>
       <c r="AU24" s="16" t="n"/>
       <c r="AV24" s="16" t="n"/>
       <c r="AW24" s="16" t="n"/>
       <c r="AX24" s="16" t="n"/>
-      <c r="AZ24" s="18" t="n"/>
-      <c r="BA24" s="18" t="n"/>
-      <c r="BB24" s="18" t="n"/>
-      <c r="BC24" s="18" t="n"/>
-      <c r="BD24" s="18" t="n"/>
-      <c r="BE24" s="18" t="n"/>
-      <c r="BF24" s="18" t="n"/>
-      <c r="BG24" s="18" t="n"/>
+      <c r="AY24" s="16" t="n"/>
+      <c r="AZ24" s="16" t="n"/>
+      <c r="BA24" s="16" t="n"/>
+      <c r="BB24" s="16" t="n"/>
+      <c r="BC24" s="16" t="n"/>
+      <c r="BD24" s="16" t="n"/>
+      <c r="BE24" s="16" t="n"/>
+      <c r="BF24" s="16" t="n"/>
       <c r="BH24" s="18" t="n"/>
       <c r="BI24" s="18" t="n"/>
       <c r="BJ24" s="18" t="n"/>
+      <c r="BK24" s="18" t="n"/>
       <c r="BL24" s="18" t="n"/>
       <c r="BM24" s="18" t="n"/>
       <c r="BN24" s="18" t="n"/>
@@ -3253,53 +3652,72 @@
       <c r="BR24" s="18" t="n"/>
       <c r="BS24" s="18" t="n"/>
       <c r="BT24" s="18" t="n"/>
-      <c r="BU24" s="18" t="n"/>
       <c r="BV24" s="18" t="n"/>
-      <c r="BX24" s="17">
-        <f>IFERROR(BL24-AZ24,"")</f>
-        <v/>
-      </c>
-      <c r="BY24" s="17">
-        <f>IFERROR(BM24-BA24,"")</f>
-        <v/>
-      </c>
-      <c r="BZ24" s="17">
-        <f>IFERROR(BN24-BB24,"")</f>
-        <v/>
-      </c>
-      <c r="CA24" s="17">
-        <f>IFERROR(BO24-BC24,"")</f>
-        <v/>
-      </c>
-      <c r="CB24" s="17">
-        <f>IFERROR(BP24-BD24,"")</f>
-        <v/>
-      </c>
-      <c r="CC24" s="17">
-        <f>IFERROR(BQ24-BE24,"")</f>
-        <v/>
-      </c>
-      <c r="CD24" s="17">
-        <f>IFERROR(BR24-BF24,"")</f>
-        <v/>
-      </c>
-      <c r="CE24" s="17">
-        <f>IFERROR(BS24-BG24,"")</f>
-        <v/>
-      </c>
-      <c r="CF24" s="17">
-        <f>IFERROR(BT24-BH24,"")</f>
-        <v/>
-      </c>
-      <c r="CG24" s="17">
-        <f>IFERROR(BU24-BI24,"")</f>
-        <v/>
-      </c>
-      <c r="CH24" s="17">
-        <f>IFERROR(BV24-BJ24,"")</f>
-        <v/>
-      </c>
-      <c r="CJ24" s="2" t="inlineStr">
+      <c r="BW24" s="18" t="n"/>
+      <c r="BX24" s="18" t="n"/>
+      <c r="BY24" s="18" t="n"/>
+      <c r="BZ24" s="18" t="n"/>
+      <c r="CA24" s="18" t="n"/>
+      <c r="CB24" s="18" t="n"/>
+      <c r="CC24" s="18" t="n"/>
+      <c r="CD24" s="18" t="n"/>
+      <c r="CE24" s="18" t="n"/>
+      <c r="CF24" s="18" t="n"/>
+      <c r="CG24" s="18" t="n"/>
+      <c r="CH24" s="18" t="n"/>
+      <c r="CJ24" s="17">
+        <f>IFERROR(BV24-BH24,"")</f>
+        <v/>
+      </c>
+      <c r="CK24" s="17">
+        <f>IFERROR(BW24-BI24,"")</f>
+        <v/>
+      </c>
+      <c r="CL24" s="17">
+        <f>IFERROR(BX24-BJ24,"")</f>
+        <v/>
+      </c>
+      <c r="CM24" s="17">
+        <f>IFERROR(BY24-BK24,"")</f>
+        <v/>
+      </c>
+      <c r="CN24" s="17">
+        <f>IFERROR(BZ24-BL24,"")</f>
+        <v/>
+      </c>
+      <c r="CO24" s="17">
+        <f>IFERROR(CA24-BM24,"")</f>
+        <v/>
+      </c>
+      <c r="CP24" s="17">
+        <f>IFERROR(CB24-BN24,"")</f>
+        <v/>
+      </c>
+      <c r="CQ24" s="17">
+        <f>IFERROR(CC24-BO24,"")</f>
+        <v/>
+      </c>
+      <c r="CR24" s="17">
+        <f>IFERROR(CD24-BP24,"")</f>
+        <v/>
+      </c>
+      <c r="CS24" s="17">
+        <f>IFERROR(CE24-BQ24,"")</f>
+        <v/>
+      </c>
+      <c r="CT24" s="17">
+        <f>IFERROR(CF24-BR24,"")</f>
+        <v/>
+      </c>
+      <c r="CU24" s="17">
+        <f>IFERROR(CG24-BS24,"")</f>
+        <v/>
+      </c>
+      <c r="CV24" s="17">
+        <f>IFERROR(CH24-BT24,"")</f>
+        <v/>
+      </c>
+      <c r="CX24" s="2" t="inlineStr">
         <is>
           <t>Flash Race</t>
         </is>
@@ -3325,8 +3743,8 @@
       <c r="L25" s="16" t="n"/>
       <c r="M25" s="16" t="n"/>
       <c r="N25" s="16" t="n"/>
+      <c r="O25" s="16" t="n"/>
       <c r="P25" s="16" t="n"/>
-      <c r="Q25" s="16" t="n"/>
       <c r="R25" s="16" t="n"/>
       <c r="S25" s="16" t="n"/>
       <c r="T25" s="16" t="n"/>
@@ -3336,10 +3754,10 @@
       <c r="X25" s="16" t="n"/>
       <c r="Y25" s="16" t="n"/>
       <c r="Z25" s="16" t="n"/>
-      <c r="AB25" s="17" t="n"/>
-      <c r="AC25" s="17" t="n"/>
-      <c r="AD25" s="17" t="n"/>
-      <c r="AE25" s="17" t="n"/>
+      <c r="AA25" s="16" t="n"/>
+      <c r="AB25" s="16" t="n"/>
+      <c r="AC25" s="16" t="n"/>
+      <c r="AD25" s="16" t="n"/>
       <c r="AF25" s="17" t="n"/>
       <c r="AG25" s="17" t="n"/>
       <c r="AH25" s="17" t="n"/>
@@ -3347,28 +3765,29 @@
       <c r="AJ25" s="17" t="n"/>
       <c r="AK25" s="17" t="n"/>
       <c r="AL25" s="17" t="n"/>
-      <c r="AN25" s="16" t="n"/>
-      <c r="AO25" s="16" t="n"/>
-      <c r="AP25" s="16" t="n"/>
-      <c r="AQ25" s="16" t="n"/>
-      <c r="AR25" s="16" t="n"/>
-      <c r="AS25" s="16" t="n"/>
+      <c r="AM25" s="17" t="n"/>
+      <c r="AN25" s="17" t="n"/>
+      <c r="AO25" s="17" t="n"/>
+      <c r="AP25" s="17" t="n"/>
+      <c r="AQ25" s="17" t="n"/>
+      <c r="AR25" s="17" t="n"/>
       <c r="AT25" s="16" t="n"/>
       <c r="AU25" s="16" t="n"/>
       <c r="AV25" s="16" t="n"/>
       <c r="AW25" s="16" t="n"/>
       <c r="AX25" s="16" t="n"/>
-      <c r="AZ25" s="18" t="n"/>
-      <c r="BA25" s="18" t="n"/>
-      <c r="BB25" s="18" t="n"/>
-      <c r="BC25" s="18" t="n"/>
-      <c r="BD25" s="18" t="n"/>
-      <c r="BE25" s="18" t="n"/>
-      <c r="BF25" s="18" t="n"/>
-      <c r="BG25" s="18" t="n"/>
+      <c r="AY25" s="16" t="n"/>
+      <c r="AZ25" s="16" t="n"/>
+      <c r="BA25" s="16" t="n"/>
+      <c r="BB25" s="16" t="n"/>
+      <c r="BC25" s="16" t="n"/>
+      <c r="BD25" s="16" t="n"/>
+      <c r="BE25" s="16" t="n"/>
+      <c r="BF25" s="16" t="n"/>
       <c r="BH25" s="18" t="n"/>
       <c r="BI25" s="18" t="n"/>
       <c r="BJ25" s="18" t="n"/>
+      <c r="BK25" s="18" t="n"/>
       <c r="BL25" s="18" t="n"/>
       <c r="BM25" s="18" t="n"/>
       <c r="BN25" s="18" t="n"/>
@@ -3378,53 +3797,72 @@
       <c r="BR25" s="18" t="n"/>
       <c r="BS25" s="18" t="n"/>
       <c r="BT25" s="18" t="n"/>
-      <c r="BU25" s="18" t="n"/>
       <c r="BV25" s="18" t="n"/>
-      <c r="BX25" s="17">
-        <f>IFERROR(BL25-AZ25,"")</f>
-        <v/>
-      </c>
-      <c r="BY25" s="17">
-        <f>IFERROR(BM25-BA25,"")</f>
-        <v/>
-      </c>
-      <c r="BZ25" s="17">
-        <f>IFERROR(BN25-BB25,"")</f>
-        <v/>
-      </c>
-      <c r="CA25" s="17">
-        <f>IFERROR(BO25-BC25,"")</f>
-        <v/>
-      </c>
-      <c r="CB25" s="17">
-        <f>IFERROR(BP25-BD25,"")</f>
-        <v/>
-      </c>
-      <c r="CC25" s="17">
-        <f>IFERROR(BQ25-BE25,"")</f>
-        <v/>
-      </c>
-      <c r="CD25" s="17">
-        <f>IFERROR(BR25-BF25,"")</f>
-        <v/>
-      </c>
-      <c r="CE25" s="17">
-        <f>IFERROR(BS25-BG25,"")</f>
-        <v/>
-      </c>
-      <c r="CF25" s="17">
-        <f>IFERROR(BT25-BH25,"")</f>
-        <v/>
-      </c>
-      <c r="CG25" s="17">
-        <f>IFERROR(BU25-BI25,"")</f>
-        <v/>
-      </c>
-      <c r="CH25" s="17">
-        <f>IFERROR(BV25-BJ25,"")</f>
-        <v/>
-      </c>
-      <c r="CJ25" s="2" t="inlineStr">
+      <c r="BW25" s="18" t="n"/>
+      <c r="BX25" s="18" t="n"/>
+      <c r="BY25" s="18" t="n"/>
+      <c r="BZ25" s="18" t="n"/>
+      <c r="CA25" s="18" t="n"/>
+      <c r="CB25" s="18" t="n"/>
+      <c r="CC25" s="18" t="n"/>
+      <c r="CD25" s="18" t="n"/>
+      <c r="CE25" s="18" t="n"/>
+      <c r="CF25" s="18" t="n"/>
+      <c r="CG25" s="18" t="n"/>
+      <c r="CH25" s="18" t="n"/>
+      <c r="CJ25" s="17">
+        <f>IFERROR(BV25-BH25,"")</f>
+        <v/>
+      </c>
+      <c r="CK25" s="17">
+        <f>IFERROR(BW25-BI25,"")</f>
+        <v/>
+      </c>
+      <c r="CL25" s="17">
+        <f>IFERROR(BX25-BJ25,"")</f>
+        <v/>
+      </c>
+      <c r="CM25" s="17">
+        <f>IFERROR(BY25-BK25,"")</f>
+        <v/>
+      </c>
+      <c r="CN25" s="17">
+        <f>IFERROR(BZ25-BL25,"")</f>
+        <v/>
+      </c>
+      <c r="CO25" s="17">
+        <f>IFERROR(CA25-BM25,"")</f>
+        <v/>
+      </c>
+      <c r="CP25" s="17">
+        <f>IFERROR(CB25-BN25,"")</f>
+        <v/>
+      </c>
+      <c r="CQ25" s="17">
+        <f>IFERROR(CC25-BO25,"")</f>
+        <v/>
+      </c>
+      <c r="CR25" s="17">
+        <f>IFERROR(CD25-BP25,"")</f>
+        <v/>
+      </c>
+      <c r="CS25" s="17">
+        <f>IFERROR(CE25-BQ25,"")</f>
+        <v/>
+      </c>
+      <c r="CT25" s="17">
+        <f>IFERROR(CF25-BR25,"")</f>
+        <v/>
+      </c>
+      <c r="CU25" s="17">
+        <f>IFERROR(CG25-BS25,"")</f>
+        <v/>
+      </c>
+      <c r="CV25" s="17">
+        <f>IFERROR(CH25-BT25,"")</f>
+        <v/>
+      </c>
+      <c r="CX25" s="2" t="inlineStr">
         <is>
           <t>FlowerCoop</t>
         </is>
@@ -3450,8 +3888,8 @@
       <c r="L26" s="16" t="n"/>
       <c r="M26" s="16" t="n"/>
       <c r="N26" s="16" t="n"/>
+      <c r="O26" s="16" t="n"/>
       <c r="P26" s="16" t="n"/>
-      <c r="Q26" s="16" t="n"/>
       <c r="R26" s="16" t="n"/>
       <c r="S26" s="16" t="n"/>
       <c r="T26" s="16" t="n"/>
@@ -3461,10 +3899,10 @@
       <c r="X26" s="16" t="n"/>
       <c r="Y26" s="16" t="n"/>
       <c r="Z26" s="16" t="n"/>
-      <c r="AB26" s="17" t="n"/>
-      <c r="AC26" s="17" t="n"/>
-      <c r="AD26" s="17" t="n"/>
-      <c r="AE26" s="17" t="n"/>
+      <c r="AA26" s="16" t="n"/>
+      <c r="AB26" s="16" t="n"/>
+      <c r="AC26" s="16" t="n"/>
+      <c r="AD26" s="16" t="n"/>
       <c r="AF26" s="17" t="n"/>
       <c r="AG26" s="17" t="n"/>
       <c r="AH26" s="17" t="n"/>
@@ -3472,28 +3910,29 @@
       <c r="AJ26" s="17" t="n"/>
       <c r="AK26" s="17" t="n"/>
       <c r="AL26" s="17" t="n"/>
-      <c r="AN26" s="16" t="n"/>
-      <c r="AO26" s="16" t="n"/>
-      <c r="AP26" s="16" t="n"/>
-      <c r="AQ26" s="16" t="n"/>
-      <c r="AR26" s="16" t="n"/>
-      <c r="AS26" s="16" t="n"/>
+      <c r="AM26" s="17" t="n"/>
+      <c r="AN26" s="17" t="n"/>
+      <c r="AO26" s="17" t="n"/>
+      <c r="AP26" s="17" t="n"/>
+      <c r="AQ26" s="17" t="n"/>
+      <c r="AR26" s="17" t="n"/>
       <c r="AT26" s="16" t="n"/>
       <c r="AU26" s="16" t="n"/>
       <c r="AV26" s="16" t="n"/>
       <c r="AW26" s="16" t="n"/>
       <c r="AX26" s="16" t="n"/>
-      <c r="AZ26" s="18" t="n"/>
-      <c r="BA26" s="18" t="n"/>
-      <c r="BB26" s="18" t="n"/>
-      <c r="BC26" s="18" t="n"/>
-      <c r="BD26" s="18" t="n"/>
-      <c r="BE26" s="18" t="n"/>
-      <c r="BF26" s="18" t="n"/>
-      <c r="BG26" s="18" t="n"/>
+      <c r="AY26" s="16" t="n"/>
+      <c r="AZ26" s="16" t="n"/>
+      <c r="BA26" s="16" t="n"/>
+      <c r="BB26" s="16" t="n"/>
+      <c r="BC26" s="16" t="n"/>
+      <c r="BD26" s="16" t="n"/>
+      <c r="BE26" s="16" t="n"/>
+      <c r="BF26" s="16" t="n"/>
       <c r="BH26" s="18" t="n"/>
       <c r="BI26" s="18" t="n"/>
       <c r="BJ26" s="18" t="n"/>
+      <c r="BK26" s="18" t="n"/>
       <c r="BL26" s="18" t="n"/>
       <c r="BM26" s="18" t="n"/>
       <c r="BN26" s="18" t="n"/>
@@ -3503,53 +3942,72 @@
       <c r="BR26" s="18" t="n"/>
       <c r="BS26" s="18" t="n"/>
       <c r="BT26" s="18" t="n"/>
-      <c r="BU26" s="18" t="n"/>
       <c r="BV26" s="18" t="n"/>
-      <c r="BX26" s="17">
-        <f>IFERROR(BL26-AZ26,"")</f>
-        <v/>
-      </c>
-      <c r="BY26" s="17">
-        <f>IFERROR(BM26-BA26,"")</f>
-        <v/>
-      </c>
-      <c r="BZ26" s="17">
-        <f>IFERROR(BN26-BB26,"")</f>
-        <v/>
-      </c>
-      <c r="CA26" s="17">
-        <f>IFERROR(BO26-BC26,"")</f>
-        <v/>
-      </c>
-      <c r="CB26" s="17">
-        <f>IFERROR(BP26-BD26,"")</f>
-        <v/>
-      </c>
-      <c r="CC26" s="17">
-        <f>IFERROR(BQ26-BE26,"")</f>
-        <v/>
-      </c>
-      <c r="CD26" s="17">
-        <f>IFERROR(BR26-BF26,"")</f>
-        <v/>
-      </c>
-      <c r="CE26" s="17">
-        <f>IFERROR(BS26-BG26,"")</f>
-        <v/>
-      </c>
-      <c r="CF26" s="17">
-        <f>IFERROR(BT26-BH26,"")</f>
-        <v/>
-      </c>
-      <c r="CG26" s="17">
-        <f>IFERROR(BU26-BI26,"")</f>
-        <v/>
-      </c>
-      <c r="CH26" s="17">
-        <f>IFERROR(BV26-BJ26,"")</f>
-        <v/>
-      </c>
-      <c r="CJ26" s="2" t="inlineStr">
+      <c r="BW26" s="18" t="n"/>
+      <c r="BX26" s="18" t="n"/>
+      <c r="BY26" s="18" t="n"/>
+      <c r="BZ26" s="18" t="n"/>
+      <c r="CA26" s="18" t="n"/>
+      <c r="CB26" s="18" t="n"/>
+      <c r="CC26" s="18" t="n"/>
+      <c r="CD26" s="18" t="n"/>
+      <c r="CE26" s="18" t="n"/>
+      <c r="CF26" s="18" t="n"/>
+      <c r="CG26" s="18" t="n"/>
+      <c r="CH26" s="18" t="n"/>
+      <c r="CJ26" s="17">
+        <f>IFERROR(BV26-BH26,"")</f>
+        <v/>
+      </c>
+      <c r="CK26" s="17">
+        <f>IFERROR(BW26-BI26,"")</f>
+        <v/>
+      </c>
+      <c r="CL26" s="17">
+        <f>IFERROR(BX26-BJ26,"")</f>
+        <v/>
+      </c>
+      <c r="CM26" s="17">
+        <f>IFERROR(BY26-BK26,"")</f>
+        <v/>
+      </c>
+      <c r="CN26" s="17">
+        <f>IFERROR(BZ26-BL26,"")</f>
+        <v/>
+      </c>
+      <c r="CO26" s="17">
+        <f>IFERROR(CA26-BM26,"")</f>
+        <v/>
+      </c>
+      <c r="CP26" s="17">
+        <f>IFERROR(CB26-BN26,"")</f>
+        <v/>
+      </c>
+      <c r="CQ26" s="17">
+        <f>IFERROR(CC26-BO26,"")</f>
+        <v/>
+      </c>
+      <c r="CR26" s="17">
+        <f>IFERROR(CD26-BP26,"")</f>
+        <v/>
+      </c>
+      <c r="CS26" s="17">
+        <f>IFERROR(CE26-BQ26,"")</f>
+        <v/>
+      </c>
+      <c r="CT26" s="17">
+        <f>IFERROR(CF26-BR26,"")</f>
+        <v/>
+      </c>
+      <c r="CU26" s="17">
+        <f>IFERROR(CG26-BS26,"")</f>
+        <v/>
+      </c>
+      <c r="CV26" s="17">
+        <f>IFERROR(CH26-BT26,"")</f>
+        <v/>
+      </c>
+      <c r="CX26" s="2" t="inlineStr">
         <is>
           <t>Rainbow Maker</t>
         </is>
@@ -3575,8 +4033,8 @@
       <c r="L27" s="16" t="n"/>
       <c r="M27" s="16" t="n"/>
       <c r="N27" s="16" t="n"/>
+      <c r="O27" s="16" t="n"/>
       <c r="P27" s="16" t="n"/>
-      <c r="Q27" s="16" t="n"/>
       <c r="R27" s="16" t="n"/>
       <c r="S27" s="16" t="n"/>
       <c r="T27" s="16" t="n"/>
@@ -3586,10 +4044,10 @@
       <c r="X27" s="16" t="n"/>
       <c r="Y27" s="16" t="n"/>
       <c r="Z27" s="16" t="n"/>
-      <c r="AB27" s="17" t="n"/>
-      <c r="AC27" s="17" t="n"/>
-      <c r="AD27" s="17" t="n"/>
-      <c r="AE27" s="17" t="n"/>
+      <c r="AA27" s="16" t="n"/>
+      <c r="AB27" s="16" t="n"/>
+      <c r="AC27" s="16" t="n"/>
+      <c r="AD27" s="16" t="n"/>
       <c r="AF27" s="17" t="n"/>
       <c r="AG27" s="17" t="n"/>
       <c r="AH27" s="17" t="n"/>
@@ -3597,28 +4055,29 @@
       <c r="AJ27" s="17" t="n"/>
       <c r="AK27" s="17" t="n"/>
       <c r="AL27" s="17" t="n"/>
-      <c r="AN27" s="16" t="n"/>
-      <c r="AO27" s="16" t="n"/>
-      <c r="AP27" s="16" t="n"/>
-      <c r="AQ27" s="16" t="n"/>
-      <c r="AR27" s="16" t="n"/>
-      <c r="AS27" s="16" t="n"/>
+      <c r="AM27" s="17" t="n"/>
+      <c r="AN27" s="17" t="n"/>
+      <c r="AO27" s="17" t="n"/>
+      <c r="AP27" s="17" t="n"/>
+      <c r="AQ27" s="17" t="n"/>
+      <c r="AR27" s="17" t="n"/>
       <c r="AT27" s="16" t="n"/>
       <c r="AU27" s="16" t="n"/>
       <c r="AV27" s="16" t="n"/>
       <c r="AW27" s="16" t="n"/>
       <c r="AX27" s="16" t="n"/>
-      <c r="AZ27" s="18" t="n"/>
-      <c r="BA27" s="18" t="n"/>
-      <c r="BB27" s="18" t="n"/>
-      <c r="BC27" s="18" t="n"/>
-      <c r="BD27" s="18" t="n"/>
-      <c r="BE27" s="18" t="n"/>
-      <c r="BF27" s="18" t="n"/>
-      <c r="BG27" s="18" t="n"/>
+      <c r="AY27" s="16" t="n"/>
+      <c r="AZ27" s="16" t="n"/>
+      <c r="BA27" s="16" t="n"/>
+      <c r="BB27" s="16" t="n"/>
+      <c r="BC27" s="16" t="n"/>
+      <c r="BD27" s="16" t="n"/>
+      <c r="BE27" s="16" t="n"/>
+      <c r="BF27" s="16" t="n"/>
       <c r="BH27" s="18" t="n"/>
       <c r="BI27" s="18" t="n"/>
       <c r="BJ27" s="18" t="n"/>
+      <c r="BK27" s="18" t="n"/>
       <c r="BL27" s="18" t="n"/>
       <c r="BM27" s="18" t="n"/>
       <c r="BN27" s="18" t="n"/>
@@ -3628,53 +4087,72 @@
       <c r="BR27" s="18" t="n"/>
       <c r="BS27" s="18" t="n"/>
       <c r="BT27" s="18" t="n"/>
-      <c r="BU27" s="18" t="n"/>
       <c r="BV27" s="18" t="n"/>
-      <c r="BX27" s="17">
-        <f>IFERROR(BL27-AZ27,"")</f>
-        <v/>
-      </c>
-      <c r="BY27" s="17">
-        <f>IFERROR(BM27-BA27,"")</f>
-        <v/>
-      </c>
-      <c r="BZ27" s="17">
-        <f>IFERROR(BN27-BB27,"")</f>
-        <v/>
-      </c>
-      <c r="CA27" s="17">
-        <f>IFERROR(BO27-BC27,"")</f>
-        <v/>
-      </c>
-      <c r="CB27" s="17">
-        <f>IFERROR(BP27-BD27,"")</f>
-        <v/>
-      </c>
-      <c r="CC27" s="17">
-        <f>IFERROR(BQ27-BE27,"")</f>
-        <v/>
-      </c>
-      <c r="CD27" s="17">
-        <f>IFERROR(BR27-BF27,"")</f>
-        <v/>
-      </c>
-      <c r="CE27" s="17">
-        <f>IFERROR(BS27-BG27,"")</f>
-        <v/>
-      </c>
-      <c r="CF27" s="17">
-        <f>IFERROR(BT27-BH27,"")</f>
-        <v/>
-      </c>
-      <c r="CG27" s="17">
-        <f>IFERROR(BU27-BI27,"")</f>
-        <v/>
-      </c>
-      <c r="CH27" s="17">
-        <f>IFERROR(BV27-BJ27,"")</f>
-        <v/>
-      </c>
-      <c r="CJ27" s="2" t="inlineStr">
+      <c r="BW27" s="18" t="n"/>
+      <c r="BX27" s="18" t="n"/>
+      <c r="BY27" s="18" t="n"/>
+      <c r="BZ27" s="18" t="n"/>
+      <c r="CA27" s="18" t="n"/>
+      <c r="CB27" s="18" t="n"/>
+      <c r="CC27" s="18" t="n"/>
+      <c r="CD27" s="18" t="n"/>
+      <c r="CE27" s="18" t="n"/>
+      <c r="CF27" s="18" t="n"/>
+      <c r="CG27" s="18" t="n"/>
+      <c r="CH27" s="18" t="n"/>
+      <c r="CJ27" s="17">
+        <f>IFERROR(BV27-BH27,"")</f>
+        <v/>
+      </c>
+      <c r="CK27" s="17">
+        <f>IFERROR(BW27-BI27,"")</f>
+        <v/>
+      </c>
+      <c r="CL27" s="17">
+        <f>IFERROR(BX27-BJ27,"")</f>
+        <v/>
+      </c>
+      <c r="CM27" s="17">
+        <f>IFERROR(BY27-BK27,"")</f>
+        <v/>
+      </c>
+      <c r="CN27" s="17">
+        <f>IFERROR(BZ27-BL27,"")</f>
+        <v/>
+      </c>
+      <c r="CO27" s="17">
+        <f>IFERROR(CA27-BM27,"")</f>
+        <v/>
+      </c>
+      <c r="CP27" s="17">
+        <f>IFERROR(CB27-BN27,"")</f>
+        <v/>
+      </c>
+      <c r="CQ27" s="17">
+        <f>IFERROR(CC27-BO27,"")</f>
+        <v/>
+      </c>
+      <c r="CR27" s="17">
+        <f>IFERROR(CD27-BP27,"")</f>
+        <v/>
+      </c>
+      <c r="CS27" s="17">
+        <f>IFERROR(CE27-BQ27,"")</f>
+        <v/>
+      </c>
+      <c r="CT27" s="17">
+        <f>IFERROR(CF27-BR27,"")</f>
+        <v/>
+      </c>
+      <c r="CU27" s="17">
+        <f>IFERROR(CG27-BS27,"")</f>
+        <v/>
+      </c>
+      <c r="CV27" s="17">
+        <f>IFERROR(CH27-BT27,"")</f>
+        <v/>
+      </c>
+      <c r="CX27" s="2" t="inlineStr">
         <is>
           <t>IAPs</t>
         </is>
@@ -3700,8 +4178,8 @@
       <c r="L28" s="16" t="n"/>
       <c r="M28" s="16" t="n"/>
       <c r="N28" s="16" t="n"/>
+      <c r="O28" s="16" t="n"/>
       <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
       <c r="R28" s="16" t="n"/>
       <c r="S28" s="16" t="n"/>
       <c r="T28" s="16" t="n"/>
@@ -3711,10 +4189,10 @@
       <c r="X28" s="16" t="n"/>
       <c r="Y28" s="16" t="n"/>
       <c r="Z28" s="16" t="n"/>
-      <c r="AB28" s="17" t="n"/>
-      <c r="AC28" s="17" t="n"/>
-      <c r="AD28" s="17" t="n"/>
-      <c r="AE28" s="17" t="n"/>
+      <c r="AA28" s="16" t="n"/>
+      <c r="AB28" s="16" t="n"/>
+      <c r="AC28" s="16" t="n"/>
+      <c r="AD28" s="16" t="n"/>
       <c r="AF28" s="17" t="n"/>
       <c r="AG28" s="17" t="n"/>
       <c r="AH28" s="17" t="n"/>
@@ -3722,28 +4200,29 @@
       <c r="AJ28" s="17" t="n"/>
       <c r="AK28" s="17" t="n"/>
       <c r="AL28" s="17" t="n"/>
-      <c r="AN28" s="16" t="n"/>
-      <c r="AO28" s="16" t="n"/>
-      <c r="AP28" s="16" t="n"/>
-      <c r="AQ28" s="16" t="n"/>
-      <c r="AR28" s="16" t="n"/>
-      <c r="AS28" s="16" t="n"/>
+      <c r="AM28" s="17" t="n"/>
+      <c r="AN28" s="17" t="n"/>
+      <c r="AO28" s="17" t="n"/>
+      <c r="AP28" s="17" t="n"/>
+      <c r="AQ28" s="17" t="n"/>
+      <c r="AR28" s="17" t="n"/>
       <c r="AT28" s="16" t="n"/>
       <c r="AU28" s="16" t="n"/>
       <c r="AV28" s="16" t="n"/>
       <c r="AW28" s="16" t="n"/>
       <c r="AX28" s="16" t="n"/>
-      <c r="AZ28" s="18" t="n"/>
-      <c r="BA28" s="18" t="n"/>
-      <c r="BB28" s="18" t="n"/>
-      <c r="BC28" s="18" t="n"/>
-      <c r="BD28" s="18" t="n"/>
-      <c r="BE28" s="18" t="n"/>
-      <c r="BF28" s="18" t="n"/>
-      <c r="BG28" s="18" t="n"/>
+      <c r="AY28" s="16" t="n"/>
+      <c r="AZ28" s="16" t="n"/>
+      <c r="BA28" s="16" t="n"/>
+      <c r="BB28" s="16" t="n"/>
+      <c r="BC28" s="16" t="n"/>
+      <c r="BD28" s="16" t="n"/>
+      <c r="BE28" s="16" t="n"/>
+      <c r="BF28" s="16" t="n"/>
       <c r="BH28" s="18" t="n"/>
       <c r="BI28" s="18" t="n"/>
       <c r="BJ28" s="18" t="n"/>
+      <c r="BK28" s="18" t="n"/>
       <c r="BL28" s="18" t="n"/>
       <c r="BM28" s="18" t="n"/>
       <c r="BN28" s="18" t="n"/>
@@ -3753,50 +4232,69 @@
       <c r="BR28" s="18" t="n"/>
       <c r="BS28" s="18" t="n"/>
       <c r="BT28" s="18" t="n"/>
-      <c r="BU28" s="18" t="n"/>
       <c r="BV28" s="18" t="n"/>
-      <c r="BX28" s="17">
-        <f>IFERROR(BL28-AZ28,"")</f>
-        <v/>
-      </c>
-      <c r="BY28" s="17">
-        <f>IFERROR(BM28-BA28,"")</f>
-        <v/>
-      </c>
-      <c r="BZ28" s="17">
-        <f>IFERROR(BN28-BB28,"")</f>
-        <v/>
-      </c>
-      <c r="CA28" s="17">
-        <f>IFERROR(BO28-BC28,"")</f>
-        <v/>
-      </c>
-      <c r="CB28" s="17">
-        <f>IFERROR(BP28-BD28,"")</f>
-        <v/>
-      </c>
-      <c r="CC28" s="17">
-        <f>IFERROR(BQ28-BE28,"")</f>
-        <v/>
-      </c>
-      <c r="CD28" s="17">
-        <f>IFERROR(BR28-BF28,"")</f>
-        <v/>
-      </c>
-      <c r="CE28" s="17">
-        <f>IFERROR(BS28-BG28,"")</f>
-        <v/>
-      </c>
-      <c r="CF28" s="17">
-        <f>IFERROR(BT28-BH28,"")</f>
-        <v/>
-      </c>
-      <c r="CG28" s="17">
-        <f>IFERROR(BU28-BI28,"")</f>
-        <v/>
-      </c>
-      <c r="CH28" s="17">
-        <f>IFERROR(BV28-BJ28,"")</f>
+      <c r="BW28" s="18" t="n"/>
+      <c r="BX28" s="18" t="n"/>
+      <c r="BY28" s="18" t="n"/>
+      <c r="BZ28" s="18" t="n"/>
+      <c r="CA28" s="18" t="n"/>
+      <c r="CB28" s="18" t="n"/>
+      <c r="CC28" s="18" t="n"/>
+      <c r="CD28" s="18" t="n"/>
+      <c r="CE28" s="18" t="n"/>
+      <c r="CF28" s="18" t="n"/>
+      <c r="CG28" s="18" t="n"/>
+      <c r="CH28" s="18" t="n"/>
+      <c r="CJ28" s="17">
+        <f>IFERROR(BV28-BH28,"")</f>
+        <v/>
+      </c>
+      <c r="CK28" s="17">
+        <f>IFERROR(BW28-BI28,"")</f>
+        <v/>
+      </c>
+      <c r="CL28" s="17">
+        <f>IFERROR(BX28-BJ28,"")</f>
+        <v/>
+      </c>
+      <c r="CM28" s="17">
+        <f>IFERROR(BY28-BK28,"")</f>
+        <v/>
+      </c>
+      <c r="CN28" s="17">
+        <f>IFERROR(BZ28-BL28,"")</f>
+        <v/>
+      </c>
+      <c r="CO28" s="17">
+        <f>IFERROR(CA28-BM28,"")</f>
+        <v/>
+      </c>
+      <c r="CP28" s="17">
+        <f>IFERROR(CB28-BN28,"")</f>
+        <v/>
+      </c>
+      <c r="CQ28" s="17">
+        <f>IFERROR(CC28-BO28,"")</f>
+        <v/>
+      </c>
+      <c r="CR28" s="17">
+        <f>IFERROR(CD28-BP28,"")</f>
+        <v/>
+      </c>
+      <c r="CS28" s="17">
+        <f>IFERROR(CE28-BQ28,"")</f>
+        <v/>
+      </c>
+      <c r="CT28" s="17">
+        <f>IFERROR(CF28-BR28,"")</f>
+        <v/>
+      </c>
+      <c r="CU28" s="17">
+        <f>IFERROR(CG28-BS28,"")</f>
+        <v/>
+      </c>
+      <c r="CV28" s="17">
+        <f>IFERROR(CH28-BT28,"")</f>
         <v/>
       </c>
     </row>
@@ -3820,8 +4318,8 @@
       <c r="L29" s="16" t="n"/>
       <c r="M29" s="16" t="n"/>
       <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
       <c r="P29" s="16" t="n"/>
-      <c r="Q29" s="16" t="n"/>
       <c r="R29" s="16" t="n"/>
       <c r="S29" s="16" t="n"/>
       <c r="T29" s="16" t="n"/>
@@ -3831,10 +4329,10 @@
       <c r="X29" s="16" t="n"/>
       <c r="Y29" s="16" t="n"/>
       <c r="Z29" s="16" t="n"/>
-      <c r="AB29" s="17" t="n"/>
-      <c r="AC29" s="17" t="n"/>
-      <c r="AD29" s="17" t="n"/>
-      <c r="AE29" s="17" t="n"/>
+      <c r="AA29" s="16" t="n"/>
+      <c r="AB29" s="16" t="n"/>
+      <c r="AC29" s="16" t="n"/>
+      <c r="AD29" s="16" t="n"/>
       <c r="AF29" s="17" t="n"/>
       <c r="AG29" s="17" t="n"/>
       <c r="AH29" s="17" t="n"/>
@@ -3842,28 +4340,29 @@
       <c r="AJ29" s="17" t="n"/>
       <c r="AK29" s="17" t="n"/>
       <c r="AL29" s="17" t="n"/>
-      <c r="AN29" s="16" t="n"/>
-      <c r="AO29" s="16" t="n"/>
-      <c r="AP29" s="16" t="n"/>
-      <c r="AQ29" s="16" t="n"/>
-      <c r="AR29" s="16" t="n"/>
-      <c r="AS29" s="16" t="n"/>
+      <c r="AM29" s="17" t="n"/>
+      <c r="AN29" s="17" t="n"/>
+      <c r="AO29" s="17" t="n"/>
+      <c r="AP29" s="17" t="n"/>
+      <c r="AQ29" s="17" t="n"/>
+      <c r="AR29" s="17" t="n"/>
       <c r="AT29" s="16" t="n"/>
       <c r="AU29" s="16" t="n"/>
       <c r="AV29" s="16" t="n"/>
       <c r="AW29" s="16" t="n"/>
       <c r="AX29" s="16" t="n"/>
-      <c r="AZ29" s="18" t="n"/>
-      <c r="BA29" s="18" t="n"/>
-      <c r="BB29" s="18" t="n"/>
-      <c r="BC29" s="18" t="n"/>
-      <c r="BD29" s="18" t="n"/>
-      <c r="BE29" s="18" t="n"/>
-      <c r="BF29" s="18" t="n"/>
-      <c r="BG29" s="18" t="n"/>
+      <c r="AY29" s="16" t="n"/>
+      <c r="AZ29" s="16" t="n"/>
+      <c r="BA29" s="16" t="n"/>
+      <c r="BB29" s="16" t="n"/>
+      <c r="BC29" s="16" t="n"/>
+      <c r="BD29" s="16" t="n"/>
+      <c r="BE29" s="16" t="n"/>
+      <c r="BF29" s="16" t="n"/>
       <c r="BH29" s="18" t="n"/>
       <c r="BI29" s="18" t="n"/>
       <c r="BJ29" s="18" t="n"/>
+      <c r="BK29" s="18" t="n"/>
       <c r="BL29" s="18" t="n"/>
       <c r="BM29" s="18" t="n"/>
       <c r="BN29" s="18" t="n"/>
@@ -3873,50 +4372,69 @@
       <c r="BR29" s="18" t="n"/>
       <c r="BS29" s="18" t="n"/>
       <c r="BT29" s="18" t="n"/>
-      <c r="BU29" s="18" t="n"/>
       <c r="BV29" s="18" t="n"/>
-      <c r="BX29" s="17">
-        <f>IFERROR(BL29-AZ29,"")</f>
-        <v/>
-      </c>
-      <c r="BY29" s="17">
-        <f>IFERROR(BM29-BA29,"")</f>
-        <v/>
-      </c>
-      <c r="BZ29" s="17">
-        <f>IFERROR(BN29-BB29,"")</f>
-        <v/>
-      </c>
-      <c r="CA29" s="17">
-        <f>IFERROR(BO29-BC29,"")</f>
-        <v/>
-      </c>
-      <c r="CB29" s="17">
-        <f>IFERROR(BP29-BD29,"")</f>
-        <v/>
-      </c>
-      <c r="CC29" s="17">
-        <f>IFERROR(BQ29-BE29,"")</f>
-        <v/>
-      </c>
-      <c r="CD29" s="17">
-        <f>IFERROR(BR29-BF29,"")</f>
-        <v/>
-      </c>
-      <c r="CE29" s="17">
-        <f>IFERROR(BS29-BG29,"")</f>
-        <v/>
-      </c>
-      <c r="CF29" s="17">
-        <f>IFERROR(BT29-BH29,"")</f>
-        <v/>
-      </c>
-      <c r="CG29" s="17">
-        <f>IFERROR(BU29-BI29,"")</f>
-        <v/>
-      </c>
-      <c r="CH29" s="17">
-        <f>IFERROR(BV29-BJ29,"")</f>
+      <c r="BW29" s="18" t="n"/>
+      <c r="BX29" s="18" t="n"/>
+      <c r="BY29" s="18" t="n"/>
+      <c r="BZ29" s="18" t="n"/>
+      <c r="CA29" s="18" t="n"/>
+      <c r="CB29" s="18" t="n"/>
+      <c r="CC29" s="18" t="n"/>
+      <c r="CD29" s="18" t="n"/>
+      <c r="CE29" s="18" t="n"/>
+      <c r="CF29" s="18" t="n"/>
+      <c r="CG29" s="18" t="n"/>
+      <c r="CH29" s="18" t="n"/>
+      <c r="CJ29" s="17">
+        <f>IFERROR(BV29-BH29,"")</f>
+        <v/>
+      </c>
+      <c r="CK29" s="17">
+        <f>IFERROR(BW29-BI29,"")</f>
+        <v/>
+      </c>
+      <c r="CL29" s="17">
+        <f>IFERROR(BX29-BJ29,"")</f>
+        <v/>
+      </c>
+      <c r="CM29" s="17">
+        <f>IFERROR(BY29-BK29,"")</f>
+        <v/>
+      </c>
+      <c r="CN29" s="17">
+        <f>IFERROR(BZ29-BL29,"")</f>
+        <v/>
+      </c>
+      <c r="CO29" s="17">
+        <f>IFERROR(CA29-BM29,"")</f>
+        <v/>
+      </c>
+      <c r="CP29" s="17">
+        <f>IFERROR(CB29-BN29,"")</f>
+        <v/>
+      </c>
+      <c r="CQ29" s="17">
+        <f>IFERROR(CC29-BO29,"")</f>
+        <v/>
+      </c>
+      <c r="CR29" s="17">
+        <f>IFERROR(CD29-BP29,"")</f>
+        <v/>
+      </c>
+      <c r="CS29" s="17">
+        <f>IFERROR(CE29-BQ29,"")</f>
+        <v/>
+      </c>
+      <c r="CT29" s="17">
+        <f>IFERROR(CF29-BR29,"")</f>
+        <v/>
+      </c>
+      <c r="CU29" s="17">
+        <f>IFERROR(CG29-BS29,"")</f>
+        <v/>
+      </c>
+      <c r="CV29" s="17">
+        <f>IFERROR(CH29-BT29,"")</f>
         <v/>
       </c>
     </row>
@@ -3940,8 +4458,8 @@
       <c r="L30" s="16" t="n"/>
       <c r="M30" s="16" t="n"/>
       <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
       <c r="P30" s="16" t="n"/>
-      <c r="Q30" s="16" t="n"/>
       <c r="R30" s="16" t="n"/>
       <c r="S30" s="16" t="n"/>
       <c r="T30" s="16" t="n"/>
@@ -3951,10 +4469,10 @@
       <c r="X30" s="16" t="n"/>
       <c r="Y30" s="16" t="n"/>
       <c r="Z30" s="16" t="n"/>
-      <c r="AB30" s="17" t="n"/>
-      <c r="AC30" s="17" t="n"/>
-      <c r="AD30" s="17" t="n"/>
-      <c r="AE30" s="17" t="n"/>
+      <c r="AA30" s="16" t="n"/>
+      <c r="AB30" s="16" t="n"/>
+      <c r="AC30" s="16" t="n"/>
+      <c r="AD30" s="16" t="n"/>
       <c r="AF30" s="17" t="n"/>
       <c r="AG30" s="17" t="n"/>
       <c r="AH30" s="17" t="n"/>
@@ -3962,28 +4480,29 @@
       <c r="AJ30" s="17" t="n"/>
       <c r="AK30" s="17" t="n"/>
       <c r="AL30" s="17" t="n"/>
-      <c r="AN30" s="16" t="n"/>
-      <c r="AO30" s="16" t="n"/>
-      <c r="AP30" s="16" t="n"/>
-      <c r="AQ30" s="16" t="n"/>
-      <c r="AR30" s="16" t="n"/>
-      <c r="AS30" s="16" t="n"/>
+      <c r="AM30" s="17" t="n"/>
+      <c r="AN30" s="17" t="n"/>
+      <c r="AO30" s="17" t="n"/>
+      <c r="AP30" s="17" t="n"/>
+      <c r="AQ30" s="17" t="n"/>
+      <c r="AR30" s="17" t="n"/>
       <c r="AT30" s="16" t="n"/>
       <c r="AU30" s="16" t="n"/>
       <c r="AV30" s="16" t="n"/>
       <c r="AW30" s="16" t="n"/>
       <c r="AX30" s="16" t="n"/>
-      <c r="AZ30" s="18" t="n"/>
-      <c r="BA30" s="18" t="n"/>
-      <c r="BB30" s="18" t="n"/>
-      <c r="BC30" s="18" t="n"/>
-      <c r="BD30" s="18" t="n"/>
-      <c r="BE30" s="18" t="n"/>
-      <c r="BF30" s="18" t="n"/>
-      <c r="BG30" s="18" t="n"/>
+      <c r="AY30" s="16" t="n"/>
+      <c r="AZ30" s="16" t="n"/>
+      <c r="BA30" s="16" t="n"/>
+      <c r="BB30" s="16" t="n"/>
+      <c r="BC30" s="16" t="n"/>
+      <c r="BD30" s="16" t="n"/>
+      <c r="BE30" s="16" t="n"/>
+      <c r="BF30" s="16" t="n"/>
       <c r="BH30" s="18" t="n"/>
       <c r="BI30" s="18" t="n"/>
       <c r="BJ30" s="18" t="n"/>
+      <c r="BK30" s="18" t="n"/>
       <c r="BL30" s="18" t="n"/>
       <c r="BM30" s="18" t="n"/>
       <c r="BN30" s="18" t="n"/>
@@ -3993,50 +4512,69 @@
       <c r="BR30" s="18" t="n"/>
       <c r="BS30" s="18" t="n"/>
       <c r="BT30" s="18" t="n"/>
-      <c r="BU30" s="18" t="n"/>
       <c r="BV30" s="18" t="n"/>
-      <c r="BX30" s="17">
-        <f>IFERROR(BL30-AZ30,"")</f>
-        <v/>
-      </c>
-      <c r="BY30" s="17">
-        <f>IFERROR(BM30-BA30,"")</f>
-        <v/>
-      </c>
-      <c r="BZ30" s="17">
-        <f>IFERROR(BN30-BB30,"")</f>
-        <v/>
-      </c>
-      <c r="CA30" s="17">
-        <f>IFERROR(BO30-BC30,"")</f>
-        <v/>
-      </c>
-      <c r="CB30" s="17">
-        <f>IFERROR(BP30-BD30,"")</f>
-        <v/>
-      </c>
-      <c r="CC30" s="17">
-        <f>IFERROR(BQ30-BE30,"")</f>
-        <v/>
-      </c>
-      <c r="CD30" s="17">
-        <f>IFERROR(BR30-BF30,"")</f>
-        <v/>
-      </c>
-      <c r="CE30" s="17">
-        <f>IFERROR(BS30-BG30,"")</f>
-        <v/>
-      </c>
-      <c r="CF30" s="17">
-        <f>IFERROR(BT30-BH30,"")</f>
-        <v/>
-      </c>
-      <c r="CG30" s="17">
-        <f>IFERROR(BU30-BI30,"")</f>
-        <v/>
-      </c>
-      <c r="CH30" s="17">
-        <f>IFERROR(BV30-BJ30,"")</f>
+      <c r="BW30" s="18" t="n"/>
+      <c r="BX30" s="18" t="n"/>
+      <c r="BY30" s="18" t="n"/>
+      <c r="BZ30" s="18" t="n"/>
+      <c r="CA30" s="18" t="n"/>
+      <c r="CB30" s="18" t="n"/>
+      <c r="CC30" s="18" t="n"/>
+      <c r="CD30" s="18" t="n"/>
+      <c r="CE30" s="18" t="n"/>
+      <c r="CF30" s="18" t="n"/>
+      <c r="CG30" s="18" t="n"/>
+      <c r="CH30" s="18" t="n"/>
+      <c r="CJ30" s="17">
+        <f>IFERROR(BV30-BH30,"")</f>
+        <v/>
+      </c>
+      <c r="CK30" s="17">
+        <f>IFERROR(BW30-BI30,"")</f>
+        <v/>
+      </c>
+      <c r="CL30" s="17">
+        <f>IFERROR(BX30-BJ30,"")</f>
+        <v/>
+      </c>
+      <c r="CM30" s="17">
+        <f>IFERROR(BY30-BK30,"")</f>
+        <v/>
+      </c>
+      <c r="CN30" s="17">
+        <f>IFERROR(BZ30-BL30,"")</f>
+        <v/>
+      </c>
+      <c r="CO30" s="17">
+        <f>IFERROR(CA30-BM30,"")</f>
+        <v/>
+      </c>
+      <c r="CP30" s="17">
+        <f>IFERROR(CB30-BN30,"")</f>
+        <v/>
+      </c>
+      <c r="CQ30" s="17">
+        <f>IFERROR(CC30-BO30,"")</f>
+        <v/>
+      </c>
+      <c r="CR30" s="17">
+        <f>IFERROR(CD30-BP30,"")</f>
+        <v/>
+      </c>
+      <c r="CS30" s="17">
+        <f>IFERROR(CE30-BQ30,"")</f>
+        <v/>
+      </c>
+      <c r="CT30" s="17">
+        <f>IFERROR(CF30-BR30,"")</f>
+        <v/>
+      </c>
+      <c r="CU30" s="17">
+        <f>IFERROR(CG30-BS30,"")</f>
+        <v/>
+      </c>
+      <c r="CV30" s="17">
+        <f>IFERROR(CH30-BT30,"")</f>
         <v/>
       </c>
     </row>
@@ -4060,8 +4598,8 @@
       <c r="L31" s="16" t="n"/>
       <c r="M31" s="16" t="n"/>
       <c r="N31" s="16" t="n"/>
+      <c r="O31" s="16" t="n"/>
       <c r="P31" s="16" t="n"/>
-      <c r="Q31" s="16" t="n"/>
       <c r="R31" s="16" t="n"/>
       <c r="S31" s="16" t="n"/>
       <c r="T31" s="16" t="n"/>
@@ -4071,10 +4609,10 @@
       <c r="X31" s="16" t="n"/>
       <c r="Y31" s="16" t="n"/>
       <c r="Z31" s="16" t="n"/>
-      <c r="AB31" s="17" t="n"/>
-      <c r="AC31" s="17" t="n"/>
-      <c r="AD31" s="17" t="n"/>
-      <c r="AE31" s="17" t="n"/>
+      <c r="AA31" s="16" t="n"/>
+      <c r="AB31" s="16" t="n"/>
+      <c r="AC31" s="16" t="n"/>
+      <c r="AD31" s="16" t="n"/>
       <c r="AF31" s="17" t="n"/>
       <c r="AG31" s="17" t="n"/>
       <c r="AH31" s="17" t="n"/>
@@ -4082,28 +4620,29 @@
       <c r="AJ31" s="17" t="n"/>
       <c r="AK31" s="17" t="n"/>
       <c r="AL31" s="17" t="n"/>
-      <c r="AN31" s="16" t="n"/>
-      <c r="AO31" s="16" t="n"/>
-      <c r="AP31" s="16" t="n"/>
-      <c r="AQ31" s="16" t="n"/>
-      <c r="AR31" s="16" t="n"/>
-      <c r="AS31" s="16" t="n"/>
+      <c r="AM31" s="17" t="n"/>
+      <c r="AN31" s="17" t="n"/>
+      <c r="AO31" s="17" t="n"/>
+      <c r="AP31" s="17" t="n"/>
+      <c r="AQ31" s="17" t="n"/>
+      <c r="AR31" s="17" t="n"/>
       <c r="AT31" s="16" t="n"/>
       <c r="AU31" s="16" t="n"/>
       <c r="AV31" s="16" t="n"/>
       <c r="AW31" s="16" t="n"/>
       <c r="AX31" s="16" t="n"/>
-      <c r="AZ31" s="18" t="n"/>
-      <c r="BA31" s="18" t="n"/>
-      <c r="BB31" s="18" t="n"/>
-      <c r="BC31" s="18" t="n"/>
-      <c r="BD31" s="18" t="n"/>
-      <c r="BE31" s="18" t="n"/>
-      <c r="BF31" s="18" t="n"/>
-      <c r="BG31" s="18" t="n"/>
+      <c r="AY31" s="16" t="n"/>
+      <c r="AZ31" s="16" t="n"/>
+      <c r="BA31" s="16" t="n"/>
+      <c r="BB31" s="16" t="n"/>
+      <c r="BC31" s="16" t="n"/>
+      <c r="BD31" s="16" t="n"/>
+      <c r="BE31" s="16" t="n"/>
+      <c r="BF31" s="16" t="n"/>
       <c r="BH31" s="18" t="n"/>
       <c r="BI31" s="18" t="n"/>
       <c r="BJ31" s="18" t="n"/>
+      <c r="BK31" s="18" t="n"/>
       <c r="BL31" s="18" t="n"/>
       <c r="BM31" s="18" t="n"/>
       <c r="BN31" s="18" t="n"/>
@@ -4113,50 +4652,69 @@
       <c r="BR31" s="18" t="n"/>
       <c r="BS31" s="18" t="n"/>
       <c r="BT31" s="18" t="n"/>
-      <c r="BU31" s="18" t="n"/>
       <c r="BV31" s="18" t="n"/>
-      <c r="BX31" s="17">
-        <f>IFERROR(BL31-AZ31,"")</f>
-        <v/>
-      </c>
-      <c r="BY31" s="17">
-        <f>IFERROR(BM31-BA31,"")</f>
-        <v/>
-      </c>
-      <c r="BZ31" s="17">
-        <f>IFERROR(BN31-BB31,"")</f>
-        <v/>
-      </c>
-      <c r="CA31" s="17">
-        <f>IFERROR(BO31-BC31,"")</f>
-        <v/>
-      </c>
-      <c r="CB31" s="17">
-        <f>IFERROR(BP31-BD31,"")</f>
-        <v/>
-      </c>
-      <c r="CC31" s="17">
-        <f>IFERROR(BQ31-BE31,"")</f>
-        <v/>
-      </c>
-      <c r="CD31" s="17">
-        <f>IFERROR(BR31-BF31,"")</f>
-        <v/>
-      </c>
-      <c r="CE31" s="17">
-        <f>IFERROR(BS31-BG31,"")</f>
-        <v/>
-      </c>
-      <c r="CF31" s="17">
-        <f>IFERROR(BT31-BH31,"")</f>
-        <v/>
-      </c>
-      <c r="CG31" s="17">
-        <f>IFERROR(BU31-BI31,"")</f>
-        <v/>
-      </c>
-      <c r="CH31" s="17">
-        <f>IFERROR(BV31-BJ31,"")</f>
+      <c r="BW31" s="18" t="n"/>
+      <c r="BX31" s="18" t="n"/>
+      <c r="BY31" s="18" t="n"/>
+      <c r="BZ31" s="18" t="n"/>
+      <c r="CA31" s="18" t="n"/>
+      <c r="CB31" s="18" t="n"/>
+      <c r="CC31" s="18" t="n"/>
+      <c r="CD31" s="18" t="n"/>
+      <c r="CE31" s="18" t="n"/>
+      <c r="CF31" s="18" t="n"/>
+      <c r="CG31" s="18" t="n"/>
+      <c r="CH31" s="18" t="n"/>
+      <c r="CJ31" s="17">
+        <f>IFERROR(BV31-BH31,"")</f>
+        <v/>
+      </c>
+      <c r="CK31" s="17">
+        <f>IFERROR(BW31-BI31,"")</f>
+        <v/>
+      </c>
+      <c r="CL31" s="17">
+        <f>IFERROR(BX31-BJ31,"")</f>
+        <v/>
+      </c>
+      <c r="CM31" s="17">
+        <f>IFERROR(BY31-BK31,"")</f>
+        <v/>
+      </c>
+      <c r="CN31" s="17">
+        <f>IFERROR(BZ31-BL31,"")</f>
+        <v/>
+      </c>
+      <c r="CO31" s="17">
+        <f>IFERROR(CA31-BM31,"")</f>
+        <v/>
+      </c>
+      <c r="CP31" s="17">
+        <f>IFERROR(CB31-BN31,"")</f>
+        <v/>
+      </c>
+      <c r="CQ31" s="17">
+        <f>IFERROR(CC31-BO31,"")</f>
+        <v/>
+      </c>
+      <c r="CR31" s="17">
+        <f>IFERROR(CD31-BP31,"")</f>
+        <v/>
+      </c>
+      <c r="CS31" s="17">
+        <f>IFERROR(CE31-BQ31,"")</f>
+        <v/>
+      </c>
+      <c r="CT31" s="17">
+        <f>IFERROR(CF31-BR31,"")</f>
+        <v/>
+      </c>
+      <c r="CU31" s="17">
+        <f>IFERROR(CG31-BS31,"")</f>
+        <v/>
+      </c>
+      <c r="CV31" s="17">
+        <f>IFERROR(CH31-BT31,"")</f>
         <v/>
       </c>
     </row>
@@ -4180,8 +4738,8 @@
       <c r="L32" s="16" t="n"/>
       <c r="M32" s="16" t="n"/>
       <c r="N32" s="16" t="n"/>
+      <c r="O32" s="16" t="n"/>
       <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="16" t="n"/>
       <c r="R32" s="16" t="n"/>
       <c r="S32" s="16" t="n"/>
       <c r="T32" s="16" t="n"/>
@@ -4191,10 +4749,10 @@
       <c r="X32" s="16" t="n"/>
       <c r="Y32" s="16" t="n"/>
       <c r="Z32" s="16" t="n"/>
-      <c r="AB32" s="17" t="n"/>
-      <c r="AC32" s="17" t="n"/>
-      <c r="AD32" s="17" t="n"/>
-      <c r="AE32" s="17" t="n"/>
+      <c r="AA32" s="16" t="n"/>
+      <c r="AB32" s="16" t="n"/>
+      <c r="AC32" s="16" t="n"/>
+      <c r="AD32" s="16" t="n"/>
       <c r="AF32" s="17" t="n"/>
       <c r="AG32" s="17" t="n"/>
       <c r="AH32" s="17" t="n"/>
@@ -4202,28 +4760,29 @@
       <c r="AJ32" s="17" t="n"/>
       <c r="AK32" s="17" t="n"/>
       <c r="AL32" s="17" t="n"/>
-      <c r="AN32" s="16" t="n"/>
-      <c r="AO32" s="16" t="n"/>
-      <c r="AP32" s="16" t="n"/>
-      <c r="AQ32" s="16" t="n"/>
-      <c r="AR32" s="16" t="n"/>
-      <c r="AS32" s="16" t="n"/>
+      <c r="AM32" s="17" t="n"/>
+      <c r="AN32" s="17" t="n"/>
+      <c r="AO32" s="17" t="n"/>
+      <c r="AP32" s="17" t="n"/>
+      <c r="AQ32" s="17" t="n"/>
+      <c r="AR32" s="17" t="n"/>
       <c r="AT32" s="16" t="n"/>
       <c r="AU32" s="16" t="n"/>
       <c r="AV32" s="16" t="n"/>
       <c r="AW32" s="16" t="n"/>
       <c r="AX32" s="16" t="n"/>
-      <c r="AZ32" s="18" t="n"/>
-      <c r="BA32" s="18" t="n"/>
-      <c r="BB32" s="18" t="n"/>
-      <c r="BC32" s="18" t="n"/>
-      <c r="BD32" s="18" t="n"/>
-      <c r="BE32" s="18" t="n"/>
-      <c r="BF32" s="18" t="n"/>
-      <c r="BG32" s="18" t="n"/>
+      <c r="AY32" s="16" t="n"/>
+      <c r="AZ32" s="16" t="n"/>
+      <c r="BA32" s="16" t="n"/>
+      <c r="BB32" s="16" t="n"/>
+      <c r="BC32" s="16" t="n"/>
+      <c r="BD32" s="16" t="n"/>
+      <c r="BE32" s="16" t="n"/>
+      <c r="BF32" s="16" t="n"/>
       <c r="BH32" s="18" t="n"/>
       <c r="BI32" s="18" t="n"/>
       <c r="BJ32" s="18" t="n"/>
+      <c r="BK32" s="18" t="n"/>
       <c r="BL32" s="18" t="n"/>
       <c r="BM32" s="18" t="n"/>
       <c r="BN32" s="18" t="n"/>
@@ -4233,50 +4792,69 @@
       <c r="BR32" s="18" t="n"/>
       <c r="BS32" s="18" t="n"/>
       <c r="BT32" s="18" t="n"/>
-      <c r="BU32" s="18" t="n"/>
       <c r="BV32" s="18" t="n"/>
-      <c r="BX32" s="17">
-        <f>IFERROR(BL32-AZ32,"")</f>
-        <v/>
-      </c>
-      <c r="BY32" s="17">
-        <f>IFERROR(BM32-BA32,"")</f>
-        <v/>
-      </c>
-      <c r="BZ32" s="17">
-        <f>IFERROR(BN32-BB32,"")</f>
-        <v/>
-      </c>
-      <c r="CA32" s="17">
-        <f>IFERROR(BO32-BC32,"")</f>
-        <v/>
-      </c>
-      <c r="CB32" s="17">
-        <f>IFERROR(BP32-BD32,"")</f>
-        <v/>
-      </c>
-      <c r="CC32" s="17">
-        <f>IFERROR(BQ32-BE32,"")</f>
-        <v/>
-      </c>
-      <c r="CD32" s="17">
-        <f>IFERROR(BR32-BF32,"")</f>
-        <v/>
-      </c>
-      <c r="CE32" s="17">
-        <f>IFERROR(BS32-BG32,"")</f>
-        <v/>
-      </c>
-      <c r="CF32" s="17">
-        <f>IFERROR(BT32-BH32,"")</f>
-        <v/>
-      </c>
-      <c r="CG32" s="17">
-        <f>IFERROR(BU32-BI32,"")</f>
-        <v/>
-      </c>
-      <c r="CH32" s="17">
-        <f>IFERROR(BV32-BJ32,"")</f>
+      <c r="BW32" s="18" t="n"/>
+      <c r="BX32" s="18" t="n"/>
+      <c r="BY32" s="18" t="n"/>
+      <c r="BZ32" s="18" t="n"/>
+      <c r="CA32" s="18" t="n"/>
+      <c r="CB32" s="18" t="n"/>
+      <c r="CC32" s="18" t="n"/>
+      <c r="CD32" s="18" t="n"/>
+      <c r="CE32" s="18" t="n"/>
+      <c r="CF32" s="18" t="n"/>
+      <c r="CG32" s="18" t="n"/>
+      <c r="CH32" s="18" t="n"/>
+      <c r="CJ32" s="17">
+        <f>IFERROR(BV32-BH32,"")</f>
+        <v/>
+      </c>
+      <c r="CK32" s="17">
+        <f>IFERROR(BW32-BI32,"")</f>
+        <v/>
+      </c>
+      <c r="CL32" s="17">
+        <f>IFERROR(BX32-BJ32,"")</f>
+        <v/>
+      </c>
+      <c r="CM32" s="17">
+        <f>IFERROR(BY32-BK32,"")</f>
+        <v/>
+      </c>
+      <c r="CN32" s="17">
+        <f>IFERROR(BZ32-BL32,"")</f>
+        <v/>
+      </c>
+      <c r="CO32" s="17">
+        <f>IFERROR(CA32-BM32,"")</f>
+        <v/>
+      </c>
+      <c r="CP32" s="17">
+        <f>IFERROR(CB32-BN32,"")</f>
+        <v/>
+      </c>
+      <c r="CQ32" s="17">
+        <f>IFERROR(CC32-BO32,"")</f>
+        <v/>
+      </c>
+      <c r="CR32" s="17">
+        <f>IFERROR(CD32-BP32,"")</f>
+        <v/>
+      </c>
+      <c r="CS32" s="17">
+        <f>IFERROR(CE32-BQ32,"")</f>
+        <v/>
+      </c>
+      <c r="CT32" s="17">
+        <f>IFERROR(CF32-BR32,"")</f>
+        <v/>
+      </c>
+      <c r="CU32" s="17">
+        <f>IFERROR(CG32-BS32,"")</f>
+        <v/>
+      </c>
+      <c r="CV32" s="17">
+        <f>IFERROR(CH32-BT32,"")</f>
         <v/>
       </c>
     </row>
@@ -4300,8 +4878,8 @@
       <c r="L33" s="16" t="n"/>
       <c r="M33" s="16" t="n"/>
       <c r="N33" s="16" t="n"/>
+      <c r="O33" s="16" t="n"/>
       <c r="P33" s="16" t="n"/>
-      <c r="Q33" s="16" t="n"/>
       <c r="R33" s="16" t="n"/>
       <c r="S33" s="16" t="n"/>
       <c r="T33" s="16" t="n"/>
@@ -4311,10 +4889,10 @@
       <c r="X33" s="16" t="n"/>
       <c r="Y33" s="16" t="n"/>
       <c r="Z33" s="16" t="n"/>
-      <c r="AB33" s="17" t="n"/>
-      <c r="AC33" s="17" t="n"/>
-      <c r="AD33" s="17" t="n"/>
-      <c r="AE33" s="17" t="n"/>
+      <c r="AA33" s="16" t="n"/>
+      <c r="AB33" s="16" t="n"/>
+      <c r="AC33" s="16" t="n"/>
+      <c r="AD33" s="16" t="n"/>
       <c r="AF33" s="17" t="n"/>
       <c r="AG33" s="17" t="n"/>
       <c r="AH33" s="17" t="n"/>
@@ -4322,28 +4900,29 @@
       <c r="AJ33" s="17" t="n"/>
       <c r="AK33" s="17" t="n"/>
       <c r="AL33" s="17" t="n"/>
-      <c r="AN33" s="16" t="n"/>
-      <c r="AO33" s="16" t="n"/>
-      <c r="AP33" s="16" t="n"/>
-      <c r="AQ33" s="16" t="n"/>
-      <c r="AR33" s="16" t="n"/>
-      <c r="AS33" s="16" t="n"/>
+      <c r="AM33" s="17" t="n"/>
+      <c r="AN33" s="17" t="n"/>
+      <c r="AO33" s="17" t="n"/>
+      <c r="AP33" s="17" t="n"/>
+      <c r="AQ33" s="17" t="n"/>
+      <c r="AR33" s="17" t="n"/>
       <c r="AT33" s="16" t="n"/>
       <c r="AU33" s="16" t="n"/>
       <c r="AV33" s="16" t="n"/>
       <c r="AW33" s="16" t="n"/>
       <c r="AX33" s="16" t="n"/>
-      <c r="AZ33" s="18" t="n"/>
-      <c r="BA33" s="18" t="n"/>
-      <c r="BB33" s="18" t="n"/>
-      <c r="BC33" s="18" t="n"/>
-      <c r="BD33" s="18" t="n"/>
-      <c r="BE33" s="18" t="n"/>
-      <c r="BF33" s="18" t="n"/>
-      <c r="BG33" s="18" t="n"/>
+      <c r="AY33" s="16" t="n"/>
+      <c r="AZ33" s="16" t="n"/>
+      <c r="BA33" s="16" t="n"/>
+      <c r="BB33" s="16" t="n"/>
+      <c r="BC33" s="16" t="n"/>
+      <c r="BD33" s="16" t="n"/>
+      <c r="BE33" s="16" t="n"/>
+      <c r="BF33" s="16" t="n"/>
       <c r="BH33" s="18" t="n"/>
       <c r="BI33" s="18" t="n"/>
       <c r="BJ33" s="18" t="n"/>
+      <c r="BK33" s="18" t="n"/>
       <c r="BL33" s="18" t="n"/>
       <c r="BM33" s="18" t="n"/>
       <c r="BN33" s="18" t="n"/>
@@ -4353,50 +4932,69 @@
       <c r="BR33" s="18" t="n"/>
       <c r="BS33" s="18" t="n"/>
       <c r="BT33" s="18" t="n"/>
-      <c r="BU33" s="18" t="n"/>
       <c r="BV33" s="18" t="n"/>
-      <c r="BX33" s="17">
-        <f>IFERROR(BL33-AZ33,"")</f>
-        <v/>
-      </c>
-      <c r="BY33" s="17">
-        <f>IFERROR(BM33-BA33,"")</f>
-        <v/>
-      </c>
-      <c r="BZ33" s="17">
-        <f>IFERROR(BN33-BB33,"")</f>
-        <v/>
-      </c>
-      <c r="CA33" s="17">
-        <f>IFERROR(BO33-BC33,"")</f>
-        <v/>
-      </c>
-      <c r="CB33" s="17">
-        <f>IFERROR(BP33-BD33,"")</f>
-        <v/>
-      </c>
-      <c r="CC33" s="17">
-        <f>IFERROR(BQ33-BE33,"")</f>
-        <v/>
-      </c>
-      <c r="CD33" s="17">
-        <f>IFERROR(BR33-BF33,"")</f>
-        <v/>
-      </c>
-      <c r="CE33" s="17">
-        <f>IFERROR(BS33-BG33,"")</f>
-        <v/>
-      </c>
-      <c r="CF33" s="17">
-        <f>IFERROR(BT33-BH33,"")</f>
-        <v/>
-      </c>
-      <c r="CG33" s="17">
-        <f>IFERROR(BU33-BI33,"")</f>
-        <v/>
-      </c>
-      <c r="CH33" s="17">
-        <f>IFERROR(BV33-BJ33,"")</f>
+      <c r="BW33" s="18" t="n"/>
+      <c r="BX33" s="18" t="n"/>
+      <c r="BY33" s="18" t="n"/>
+      <c r="BZ33" s="18" t="n"/>
+      <c r="CA33" s="18" t="n"/>
+      <c r="CB33" s="18" t="n"/>
+      <c r="CC33" s="18" t="n"/>
+      <c r="CD33" s="18" t="n"/>
+      <c r="CE33" s="18" t="n"/>
+      <c r="CF33" s="18" t="n"/>
+      <c r="CG33" s="18" t="n"/>
+      <c r="CH33" s="18" t="n"/>
+      <c r="CJ33" s="17">
+        <f>IFERROR(BV33-BH33,"")</f>
+        <v/>
+      </c>
+      <c r="CK33" s="17">
+        <f>IFERROR(BW33-BI33,"")</f>
+        <v/>
+      </c>
+      <c r="CL33" s="17">
+        <f>IFERROR(BX33-BJ33,"")</f>
+        <v/>
+      </c>
+      <c r="CM33" s="17">
+        <f>IFERROR(BY33-BK33,"")</f>
+        <v/>
+      </c>
+      <c r="CN33" s="17">
+        <f>IFERROR(BZ33-BL33,"")</f>
+        <v/>
+      </c>
+      <c r="CO33" s="17">
+        <f>IFERROR(CA33-BM33,"")</f>
+        <v/>
+      </c>
+      <c r="CP33" s="17">
+        <f>IFERROR(CB33-BN33,"")</f>
+        <v/>
+      </c>
+      <c r="CQ33" s="17">
+        <f>IFERROR(CC33-BO33,"")</f>
+        <v/>
+      </c>
+      <c r="CR33" s="17">
+        <f>IFERROR(CD33-BP33,"")</f>
+        <v/>
+      </c>
+      <c r="CS33" s="17">
+        <f>IFERROR(CE33-BQ33,"")</f>
+        <v/>
+      </c>
+      <c r="CT33" s="17">
+        <f>IFERROR(CF33-BR33,"")</f>
+        <v/>
+      </c>
+      <c r="CU33" s="17">
+        <f>IFERROR(CG33-BS33,"")</f>
+        <v/>
+      </c>
+      <c r="CV33" s="17">
+        <f>IFERROR(CH33-BT33,"")</f>
         <v/>
       </c>
     </row>
@@ -4420,8 +5018,8 @@
       <c r="L34" s="16" t="n"/>
       <c r="M34" s="16" t="n"/>
       <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n"/>
       <c r="P34" s="16" t="n"/>
-      <c r="Q34" s="16" t="n"/>
       <c r="R34" s="16" t="n"/>
       <c r="S34" s="16" t="n"/>
       <c r="T34" s="16" t="n"/>
@@ -4431,10 +5029,10 @@
       <c r="X34" s="16" t="n"/>
       <c r="Y34" s="16" t="n"/>
       <c r="Z34" s="16" t="n"/>
-      <c r="AB34" s="17" t="n"/>
-      <c r="AC34" s="17" t="n"/>
-      <c r="AD34" s="17" t="n"/>
-      <c r="AE34" s="17" t="n"/>
+      <c r="AA34" s="16" t="n"/>
+      <c r="AB34" s="16" t="n"/>
+      <c r="AC34" s="16" t="n"/>
+      <c r="AD34" s="16" t="n"/>
       <c r="AF34" s="17" t="n"/>
       <c r="AG34" s="17" t="n"/>
       <c r="AH34" s="17" t="n"/>
@@ -4442,28 +5040,29 @@
       <c r="AJ34" s="17" t="n"/>
       <c r="AK34" s="17" t="n"/>
       <c r="AL34" s="17" t="n"/>
-      <c r="AN34" s="16" t="n"/>
-      <c r="AO34" s="16" t="n"/>
-      <c r="AP34" s="16" t="n"/>
-      <c r="AQ34" s="16" t="n"/>
-      <c r="AR34" s="16" t="n"/>
-      <c r="AS34" s="16" t="n"/>
+      <c r="AM34" s="17" t="n"/>
+      <c r="AN34" s="17" t="n"/>
+      <c r="AO34" s="17" t="n"/>
+      <c r="AP34" s="17" t="n"/>
+      <c r="AQ34" s="17" t="n"/>
+      <c r="AR34" s="17" t="n"/>
       <c r="AT34" s="16" t="n"/>
       <c r="AU34" s="16" t="n"/>
       <c r="AV34" s="16" t="n"/>
       <c r="AW34" s="16" t="n"/>
       <c r="AX34" s="16" t="n"/>
-      <c r="AZ34" s="18" t="n"/>
-      <c r="BA34" s="18" t="n"/>
-      <c r="BB34" s="18" t="n"/>
-      <c r="BC34" s="18" t="n"/>
-      <c r="BD34" s="18" t="n"/>
-      <c r="BE34" s="18" t="n"/>
-      <c r="BF34" s="18" t="n"/>
-      <c r="BG34" s="18" t="n"/>
+      <c r="AY34" s="16" t="n"/>
+      <c r="AZ34" s="16" t="n"/>
+      <c r="BA34" s="16" t="n"/>
+      <c r="BB34" s="16" t="n"/>
+      <c r="BC34" s="16" t="n"/>
+      <c r="BD34" s="16" t="n"/>
+      <c r="BE34" s="16" t="n"/>
+      <c r="BF34" s="16" t="n"/>
       <c r="BH34" s="18" t="n"/>
       <c r="BI34" s="18" t="n"/>
       <c r="BJ34" s="18" t="n"/>
+      <c r="BK34" s="18" t="n"/>
       <c r="BL34" s="18" t="n"/>
       <c r="BM34" s="18" t="n"/>
       <c r="BN34" s="18" t="n"/>
@@ -4473,50 +5072,69 @@
       <c r="BR34" s="18" t="n"/>
       <c r="BS34" s="18" t="n"/>
       <c r="BT34" s="18" t="n"/>
-      <c r="BU34" s="18" t="n"/>
       <c r="BV34" s="18" t="n"/>
-      <c r="BX34" s="17">
-        <f>IFERROR(BL34-AZ34,"")</f>
-        <v/>
-      </c>
-      <c r="BY34" s="17">
-        <f>IFERROR(BM34-BA34,"")</f>
-        <v/>
-      </c>
-      <c r="BZ34" s="17">
-        <f>IFERROR(BN34-BB34,"")</f>
-        <v/>
-      </c>
-      <c r="CA34" s="17">
-        <f>IFERROR(BO34-BC34,"")</f>
-        <v/>
-      </c>
-      <c r="CB34" s="17">
-        <f>IFERROR(BP34-BD34,"")</f>
-        <v/>
-      </c>
-      <c r="CC34" s="17">
-        <f>IFERROR(BQ34-BE34,"")</f>
-        <v/>
-      </c>
-      <c r="CD34" s="17">
-        <f>IFERROR(BR34-BF34,"")</f>
-        <v/>
-      </c>
-      <c r="CE34" s="17">
-        <f>IFERROR(BS34-BG34,"")</f>
-        <v/>
-      </c>
-      <c r="CF34" s="17">
-        <f>IFERROR(BT34-BH34,"")</f>
-        <v/>
-      </c>
-      <c r="CG34" s="17">
-        <f>IFERROR(BU34-BI34,"")</f>
-        <v/>
-      </c>
-      <c r="CH34" s="17">
-        <f>IFERROR(BV34-BJ34,"")</f>
+      <c r="BW34" s="18" t="n"/>
+      <c r="BX34" s="18" t="n"/>
+      <c r="BY34" s="18" t="n"/>
+      <c r="BZ34" s="18" t="n"/>
+      <c r="CA34" s="18" t="n"/>
+      <c r="CB34" s="18" t="n"/>
+      <c r="CC34" s="18" t="n"/>
+      <c r="CD34" s="18" t="n"/>
+      <c r="CE34" s="18" t="n"/>
+      <c r="CF34" s="18" t="n"/>
+      <c r="CG34" s="18" t="n"/>
+      <c r="CH34" s="18" t="n"/>
+      <c r="CJ34" s="17">
+        <f>IFERROR(BV34-BH34,"")</f>
+        <v/>
+      </c>
+      <c r="CK34" s="17">
+        <f>IFERROR(BW34-BI34,"")</f>
+        <v/>
+      </c>
+      <c r="CL34" s="17">
+        <f>IFERROR(BX34-BJ34,"")</f>
+        <v/>
+      </c>
+      <c r="CM34" s="17">
+        <f>IFERROR(BY34-BK34,"")</f>
+        <v/>
+      </c>
+      <c r="CN34" s="17">
+        <f>IFERROR(BZ34-BL34,"")</f>
+        <v/>
+      </c>
+      <c r="CO34" s="17">
+        <f>IFERROR(CA34-BM34,"")</f>
+        <v/>
+      </c>
+      <c r="CP34" s="17">
+        <f>IFERROR(CB34-BN34,"")</f>
+        <v/>
+      </c>
+      <c r="CQ34" s="17">
+        <f>IFERROR(CC34-BO34,"")</f>
+        <v/>
+      </c>
+      <c r="CR34" s="17">
+        <f>IFERROR(CD34-BP34,"")</f>
+        <v/>
+      </c>
+      <c r="CS34" s="17">
+        <f>IFERROR(CE34-BQ34,"")</f>
+        <v/>
+      </c>
+      <c r="CT34" s="17">
+        <f>IFERROR(CF34-BR34,"")</f>
+        <v/>
+      </c>
+      <c r="CU34" s="17">
+        <f>IFERROR(CG34-BS34,"")</f>
+        <v/>
+      </c>
+      <c r="CV34" s="17">
+        <f>IFERROR(CH34-BT34,"")</f>
         <v/>
       </c>
     </row>
@@ -4540,8 +5158,8 @@
       <c r="L35" s="16" t="n"/>
       <c r="M35" s="16" t="n"/>
       <c r="N35" s="16" t="n"/>
+      <c r="O35" s="16" t="n"/>
       <c r="P35" s="16" t="n"/>
-      <c r="Q35" s="16" t="n"/>
       <c r="R35" s="16" t="n"/>
       <c r="S35" s="16" t="n"/>
       <c r="T35" s="16" t="n"/>
@@ -4551,10 +5169,10 @@
       <c r="X35" s="16" t="n"/>
       <c r="Y35" s="16" t="n"/>
       <c r="Z35" s="16" t="n"/>
-      <c r="AB35" s="17" t="n"/>
-      <c r="AC35" s="17" t="n"/>
-      <c r="AD35" s="17" t="n"/>
-      <c r="AE35" s="17" t="n"/>
+      <c r="AA35" s="16" t="n"/>
+      <c r="AB35" s="16" t="n"/>
+      <c r="AC35" s="16" t="n"/>
+      <c r="AD35" s="16" t="n"/>
       <c r="AF35" s="17" t="n"/>
       <c r="AG35" s="17" t="n"/>
       <c r="AH35" s="17" t="n"/>
@@ -4562,28 +5180,29 @@
       <c r="AJ35" s="17" t="n"/>
       <c r="AK35" s="17" t="n"/>
       <c r="AL35" s="17" t="n"/>
-      <c r="AN35" s="16" t="n"/>
-      <c r="AO35" s="16" t="n"/>
-      <c r="AP35" s="16" t="n"/>
-      <c r="AQ35" s="16" t="n"/>
-      <c r="AR35" s="16" t="n"/>
-      <c r="AS35" s="16" t="n"/>
+      <c r="AM35" s="17" t="n"/>
+      <c r="AN35" s="17" t="n"/>
+      <c r="AO35" s="17" t="n"/>
+      <c r="AP35" s="17" t="n"/>
+      <c r="AQ35" s="17" t="n"/>
+      <c r="AR35" s="17" t="n"/>
       <c r="AT35" s="16" t="n"/>
       <c r="AU35" s="16" t="n"/>
       <c r="AV35" s="16" t="n"/>
       <c r="AW35" s="16" t="n"/>
       <c r="AX35" s="16" t="n"/>
-      <c r="AZ35" s="18" t="n"/>
-      <c r="BA35" s="18" t="n"/>
-      <c r="BB35" s="18" t="n"/>
-      <c r="BC35" s="18" t="n"/>
-      <c r="BD35" s="18" t="n"/>
-      <c r="BE35" s="18" t="n"/>
-      <c r="BF35" s="18" t="n"/>
-      <c r="BG35" s="18" t="n"/>
+      <c r="AY35" s="16" t="n"/>
+      <c r="AZ35" s="16" t="n"/>
+      <c r="BA35" s="16" t="n"/>
+      <c r="BB35" s="16" t="n"/>
+      <c r="BC35" s="16" t="n"/>
+      <c r="BD35" s="16" t="n"/>
+      <c r="BE35" s="16" t="n"/>
+      <c r="BF35" s="16" t="n"/>
       <c r="BH35" s="18" t="n"/>
       <c r="BI35" s="18" t="n"/>
       <c r="BJ35" s="18" t="n"/>
+      <c r="BK35" s="18" t="n"/>
       <c r="BL35" s="18" t="n"/>
       <c r="BM35" s="18" t="n"/>
       <c r="BN35" s="18" t="n"/>
@@ -4593,50 +5212,69 @@
       <c r="BR35" s="18" t="n"/>
       <c r="BS35" s="18" t="n"/>
       <c r="BT35" s="18" t="n"/>
-      <c r="BU35" s="18" t="n"/>
       <c r="BV35" s="18" t="n"/>
-      <c r="BX35" s="17">
-        <f>IFERROR(BL35-AZ35,"")</f>
-        <v/>
-      </c>
-      <c r="BY35" s="17">
-        <f>IFERROR(BM35-BA35,"")</f>
-        <v/>
-      </c>
-      <c r="BZ35" s="17">
-        <f>IFERROR(BN35-BB35,"")</f>
-        <v/>
-      </c>
-      <c r="CA35" s="17">
-        <f>IFERROR(BO35-BC35,"")</f>
-        <v/>
-      </c>
-      <c r="CB35" s="17">
-        <f>IFERROR(BP35-BD35,"")</f>
-        <v/>
-      </c>
-      <c r="CC35" s="17">
-        <f>IFERROR(BQ35-BE35,"")</f>
-        <v/>
-      </c>
-      <c r="CD35" s="17">
-        <f>IFERROR(BR35-BF35,"")</f>
-        <v/>
-      </c>
-      <c r="CE35" s="17">
-        <f>IFERROR(BS35-BG35,"")</f>
-        <v/>
-      </c>
-      <c r="CF35" s="17">
-        <f>IFERROR(BT35-BH35,"")</f>
-        <v/>
-      </c>
-      <c r="CG35" s="17">
-        <f>IFERROR(BU35-BI35,"")</f>
-        <v/>
-      </c>
-      <c r="CH35" s="17">
-        <f>IFERROR(BV35-BJ35,"")</f>
+      <c r="BW35" s="18" t="n"/>
+      <c r="BX35" s="18" t="n"/>
+      <c r="BY35" s="18" t="n"/>
+      <c r="BZ35" s="18" t="n"/>
+      <c r="CA35" s="18" t="n"/>
+      <c r="CB35" s="18" t="n"/>
+      <c r="CC35" s="18" t="n"/>
+      <c r="CD35" s="18" t="n"/>
+      <c r="CE35" s="18" t="n"/>
+      <c r="CF35" s="18" t="n"/>
+      <c r="CG35" s="18" t="n"/>
+      <c r="CH35" s="18" t="n"/>
+      <c r="CJ35" s="17">
+        <f>IFERROR(BV35-BH35,"")</f>
+        <v/>
+      </c>
+      <c r="CK35" s="17">
+        <f>IFERROR(BW35-BI35,"")</f>
+        <v/>
+      </c>
+      <c r="CL35" s="17">
+        <f>IFERROR(BX35-BJ35,"")</f>
+        <v/>
+      </c>
+      <c r="CM35" s="17">
+        <f>IFERROR(BY35-BK35,"")</f>
+        <v/>
+      </c>
+      <c r="CN35" s="17">
+        <f>IFERROR(BZ35-BL35,"")</f>
+        <v/>
+      </c>
+      <c r="CO35" s="17">
+        <f>IFERROR(CA35-BM35,"")</f>
+        <v/>
+      </c>
+      <c r="CP35" s="17">
+        <f>IFERROR(CB35-BN35,"")</f>
+        <v/>
+      </c>
+      <c r="CQ35" s="17">
+        <f>IFERROR(CC35-BO35,"")</f>
+        <v/>
+      </c>
+      <c r="CR35" s="17">
+        <f>IFERROR(CD35-BP35,"")</f>
+        <v/>
+      </c>
+      <c r="CS35" s="17">
+        <f>IFERROR(CE35-BQ35,"")</f>
+        <v/>
+      </c>
+      <c r="CT35" s="17">
+        <f>IFERROR(CF35-BR35,"")</f>
+        <v/>
+      </c>
+      <c r="CU35" s="17">
+        <f>IFERROR(CG35-BS35,"")</f>
+        <v/>
+      </c>
+      <c r="CV35" s="17">
+        <f>IFERROR(CH35-BT35,"")</f>
         <v/>
       </c>
     </row>
@@ -4660,8 +5298,8 @@
       <c r="L36" s="16" t="n"/>
       <c r="M36" s="16" t="n"/>
       <c r="N36" s="16" t="n"/>
+      <c r="O36" s="16" t="n"/>
       <c r="P36" s="16" t="n"/>
-      <c r="Q36" s="16" t="n"/>
       <c r="R36" s="16" t="n"/>
       <c r="S36" s="16" t="n"/>
       <c r="T36" s="16" t="n"/>
@@ -4671,10 +5309,10 @@
       <c r="X36" s="16" t="n"/>
       <c r="Y36" s="16" t="n"/>
       <c r="Z36" s="16" t="n"/>
-      <c r="AB36" s="17" t="n"/>
-      <c r="AC36" s="17" t="n"/>
-      <c r="AD36" s="17" t="n"/>
-      <c r="AE36" s="17" t="n"/>
+      <c r="AA36" s="16" t="n"/>
+      <c r="AB36" s="16" t="n"/>
+      <c r="AC36" s="16" t="n"/>
+      <c r="AD36" s="16" t="n"/>
       <c r="AF36" s="17" t="n"/>
       <c r="AG36" s="17" t="n"/>
       <c r="AH36" s="17" t="n"/>
@@ -4682,28 +5320,29 @@
       <c r="AJ36" s="17" t="n"/>
       <c r="AK36" s="17" t="n"/>
       <c r="AL36" s="17" t="n"/>
-      <c r="AN36" s="16" t="n"/>
-      <c r="AO36" s="16" t="n"/>
-      <c r="AP36" s="16" t="n"/>
-      <c r="AQ36" s="16" t="n"/>
-      <c r="AR36" s="16" t="n"/>
-      <c r="AS36" s="16" t="n"/>
+      <c r="AM36" s="17" t="n"/>
+      <c r="AN36" s="17" t="n"/>
+      <c r="AO36" s="17" t="n"/>
+      <c r="AP36" s="17" t="n"/>
+      <c r="AQ36" s="17" t="n"/>
+      <c r="AR36" s="17" t="n"/>
       <c r="AT36" s="16" t="n"/>
       <c r="AU36" s="16" t="n"/>
       <c r="AV36" s="16" t="n"/>
       <c r="AW36" s="16" t="n"/>
       <c r="AX36" s="16" t="n"/>
-      <c r="AZ36" s="18" t="n"/>
-      <c r="BA36" s="18" t="n"/>
-      <c r="BB36" s="18" t="n"/>
-      <c r="BC36" s="18" t="n"/>
-      <c r="BD36" s="18" t="n"/>
-      <c r="BE36" s="18" t="n"/>
-      <c r="BF36" s="18" t="n"/>
-      <c r="BG36" s="18" t="n"/>
+      <c r="AY36" s="16" t="n"/>
+      <c r="AZ36" s="16" t="n"/>
+      <c r="BA36" s="16" t="n"/>
+      <c r="BB36" s="16" t="n"/>
+      <c r="BC36" s="16" t="n"/>
+      <c r="BD36" s="16" t="n"/>
+      <c r="BE36" s="16" t="n"/>
+      <c r="BF36" s="16" t="n"/>
       <c r="BH36" s="18" t="n"/>
       <c r="BI36" s="18" t="n"/>
       <c r="BJ36" s="18" t="n"/>
+      <c r="BK36" s="18" t="n"/>
       <c r="BL36" s="18" t="n"/>
       <c r="BM36" s="18" t="n"/>
       <c r="BN36" s="18" t="n"/>
@@ -4713,50 +5352,69 @@
       <c r="BR36" s="18" t="n"/>
       <c r="BS36" s="18" t="n"/>
       <c r="BT36" s="18" t="n"/>
-      <c r="BU36" s="18" t="n"/>
       <c r="BV36" s="18" t="n"/>
-      <c r="BX36" s="17">
-        <f>IFERROR(BL36-AZ36,"")</f>
-        <v/>
-      </c>
-      <c r="BY36" s="17">
-        <f>IFERROR(BM36-BA36,"")</f>
-        <v/>
-      </c>
-      <c r="BZ36" s="17">
-        <f>IFERROR(BN36-BB36,"")</f>
-        <v/>
-      </c>
-      <c r="CA36" s="17">
-        <f>IFERROR(BO36-BC36,"")</f>
-        <v/>
-      </c>
-      <c r="CB36" s="17">
-        <f>IFERROR(BP36-BD36,"")</f>
-        <v/>
-      </c>
-      <c r="CC36" s="17">
-        <f>IFERROR(BQ36-BE36,"")</f>
-        <v/>
-      </c>
-      <c r="CD36" s="17">
-        <f>IFERROR(BR36-BF36,"")</f>
-        <v/>
-      </c>
-      <c r="CE36" s="17">
-        <f>IFERROR(BS36-BG36,"")</f>
-        <v/>
-      </c>
-      <c r="CF36" s="17">
-        <f>IFERROR(BT36-BH36,"")</f>
-        <v/>
-      </c>
-      <c r="CG36" s="17">
-        <f>IFERROR(BU36-BI36,"")</f>
-        <v/>
-      </c>
-      <c r="CH36" s="17">
-        <f>IFERROR(BV36-BJ36,"")</f>
+      <c r="BW36" s="18" t="n"/>
+      <c r="BX36" s="18" t="n"/>
+      <c r="BY36" s="18" t="n"/>
+      <c r="BZ36" s="18" t="n"/>
+      <c r="CA36" s="18" t="n"/>
+      <c r="CB36" s="18" t="n"/>
+      <c r="CC36" s="18" t="n"/>
+      <c r="CD36" s="18" t="n"/>
+      <c r="CE36" s="18" t="n"/>
+      <c r="CF36" s="18" t="n"/>
+      <c r="CG36" s="18" t="n"/>
+      <c r="CH36" s="18" t="n"/>
+      <c r="CJ36" s="17">
+        <f>IFERROR(BV36-BH36,"")</f>
+        <v/>
+      </c>
+      <c r="CK36" s="17">
+        <f>IFERROR(BW36-BI36,"")</f>
+        <v/>
+      </c>
+      <c r="CL36" s="17">
+        <f>IFERROR(BX36-BJ36,"")</f>
+        <v/>
+      </c>
+      <c r="CM36" s="17">
+        <f>IFERROR(BY36-BK36,"")</f>
+        <v/>
+      </c>
+      <c r="CN36" s="17">
+        <f>IFERROR(BZ36-BL36,"")</f>
+        <v/>
+      </c>
+      <c r="CO36" s="17">
+        <f>IFERROR(CA36-BM36,"")</f>
+        <v/>
+      </c>
+      <c r="CP36" s="17">
+        <f>IFERROR(CB36-BN36,"")</f>
+        <v/>
+      </c>
+      <c r="CQ36" s="17">
+        <f>IFERROR(CC36-BO36,"")</f>
+        <v/>
+      </c>
+      <c r="CR36" s="17">
+        <f>IFERROR(CD36-BP36,"")</f>
+        <v/>
+      </c>
+      <c r="CS36" s="17">
+        <f>IFERROR(CE36-BQ36,"")</f>
+        <v/>
+      </c>
+      <c r="CT36" s="17">
+        <f>IFERROR(CF36-BR36,"")</f>
+        <v/>
+      </c>
+      <c r="CU36" s="17">
+        <f>IFERROR(CG36-BS36,"")</f>
+        <v/>
+      </c>
+      <c r="CV36" s="17">
+        <f>IFERROR(CH36-BT36,"")</f>
         <v/>
       </c>
     </row>
@@ -4780,8 +5438,8 @@
       <c r="L37" s="16" t="n"/>
       <c r="M37" s="16" t="n"/>
       <c r="N37" s="16" t="n"/>
+      <c r="O37" s="16" t="n"/>
       <c r="P37" s="16" t="n"/>
-      <c r="Q37" s="16" t="n"/>
       <c r="R37" s="16" t="n"/>
       <c r="S37" s="16" t="n"/>
       <c r="T37" s="16" t="n"/>
@@ -4791,10 +5449,10 @@
       <c r="X37" s="16" t="n"/>
       <c r="Y37" s="16" t="n"/>
       <c r="Z37" s="16" t="n"/>
-      <c r="AB37" s="17" t="n"/>
-      <c r="AC37" s="17" t="n"/>
-      <c r="AD37" s="17" t="n"/>
-      <c r="AE37" s="17" t="n"/>
+      <c r="AA37" s="16" t="n"/>
+      <c r="AB37" s="16" t="n"/>
+      <c r="AC37" s="16" t="n"/>
+      <c r="AD37" s="16" t="n"/>
       <c r="AF37" s="17" t="n"/>
       <c r="AG37" s="17" t="n"/>
       <c r="AH37" s="17" t="n"/>
@@ -4802,28 +5460,29 @@
       <c r="AJ37" s="17" t="n"/>
       <c r="AK37" s="17" t="n"/>
       <c r="AL37" s="17" t="n"/>
-      <c r="AN37" s="16" t="n"/>
-      <c r="AO37" s="16" t="n"/>
-      <c r="AP37" s="16" t="n"/>
-      <c r="AQ37" s="16" t="n"/>
-      <c r="AR37" s="16" t="n"/>
-      <c r="AS37" s="16" t="n"/>
+      <c r="AM37" s="17" t="n"/>
+      <c r="AN37" s="17" t="n"/>
+      <c r="AO37" s="17" t="n"/>
+      <c r="AP37" s="17" t="n"/>
+      <c r="AQ37" s="17" t="n"/>
+      <c r="AR37" s="17" t="n"/>
       <c r="AT37" s="16" t="n"/>
       <c r="AU37" s="16" t="n"/>
       <c r="AV37" s="16" t="n"/>
       <c r="AW37" s="16" t="n"/>
       <c r="AX37" s="16" t="n"/>
-      <c r="AZ37" s="18" t="n"/>
-      <c r="BA37" s="18" t="n"/>
-      <c r="BB37" s="18" t="n"/>
-      <c r="BC37" s="18" t="n"/>
-      <c r="BD37" s="18" t="n"/>
-      <c r="BE37" s="18" t="n"/>
-      <c r="BF37" s="18" t="n"/>
-      <c r="BG37" s="18" t="n"/>
+      <c r="AY37" s="16" t="n"/>
+      <c r="AZ37" s="16" t="n"/>
+      <c r="BA37" s="16" t="n"/>
+      <c r="BB37" s="16" t="n"/>
+      <c r="BC37" s="16" t="n"/>
+      <c r="BD37" s="16" t="n"/>
+      <c r="BE37" s="16" t="n"/>
+      <c r="BF37" s="16" t="n"/>
       <c r="BH37" s="18" t="n"/>
       <c r="BI37" s="18" t="n"/>
       <c r="BJ37" s="18" t="n"/>
+      <c r="BK37" s="18" t="n"/>
       <c r="BL37" s="18" t="n"/>
       <c r="BM37" s="18" t="n"/>
       <c r="BN37" s="18" t="n"/>
@@ -4833,50 +5492,69 @@
       <c r="BR37" s="18" t="n"/>
       <c r="BS37" s="18" t="n"/>
       <c r="BT37" s="18" t="n"/>
-      <c r="BU37" s="18" t="n"/>
       <c r="BV37" s="18" t="n"/>
-      <c r="BX37" s="17">
-        <f>IFERROR(BL37-AZ37,"")</f>
-        <v/>
-      </c>
-      <c r="BY37" s="17">
-        <f>IFERROR(BM37-BA37,"")</f>
-        <v/>
-      </c>
-      <c r="BZ37" s="17">
-        <f>IFERROR(BN37-BB37,"")</f>
-        <v/>
-      </c>
-      <c r="CA37" s="17">
-        <f>IFERROR(BO37-BC37,"")</f>
-        <v/>
-      </c>
-      <c r="CB37" s="17">
-        <f>IFERROR(BP37-BD37,"")</f>
-        <v/>
-      </c>
-      <c r="CC37" s="17">
-        <f>IFERROR(BQ37-BE37,"")</f>
-        <v/>
-      </c>
-      <c r="CD37" s="17">
-        <f>IFERROR(BR37-BF37,"")</f>
-        <v/>
-      </c>
-      <c r="CE37" s="17">
-        <f>IFERROR(BS37-BG37,"")</f>
-        <v/>
-      </c>
-      <c r="CF37" s="17">
-        <f>IFERROR(BT37-BH37,"")</f>
-        <v/>
-      </c>
-      <c r="CG37" s="17">
-        <f>IFERROR(BU37-BI37,"")</f>
-        <v/>
-      </c>
-      <c r="CH37" s="17">
-        <f>IFERROR(BV37-BJ37,"")</f>
+      <c r="BW37" s="18" t="n"/>
+      <c r="BX37" s="18" t="n"/>
+      <c r="BY37" s="18" t="n"/>
+      <c r="BZ37" s="18" t="n"/>
+      <c r="CA37" s="18" t="n"/>
+      <c r="CB37" s="18" t="n"/>
+      <c r="CC37" s="18" t="n"/>
+      <c r="CD37" s="18" t="n"/>
+      <c r="CE37" s="18" t="n"/>
+      <c r="CF37" s="18" t="n"/>
+      <c r="CG37" s="18" t="n"/>
+      <c r="CH37" s="18" t="n"/>
+      <c r="CJ37" s="17">
+        <f>IFERROR(BV37-BH37,"")</f>
+        <v/>
+      </c>
+      <c r="CK37" s="17">
+        <f>IFERROR(BW37-BI37,"")</f>
+        <v/>
+      </c>
+      <c r="CL37" s="17">
+        <f>IFERROR(BX37-BJ37,"")</f>
+        <v/>
+      </c>
+      <c r="CM37" s="17">
+        <f>IFERROR(BY37-BK37,"")</f>
+        <v/>
+      </c>
+      <c r="CN37" s="17">
+        <f>IFERROR(BZ37-BL37,"")</f>
+        <v/>
+      </c>
+      <c r="CO37" s="17">
+        <f>IFERROR(CA37-BM37,"")</f>
+        <v/>
+      </c>
+      <c r="CP37" s="17">
+        <f>IFERROR(CB37-BN37,"")</f>
+        <v/>
+      </c>
+      <c r="CQ37" s="17">
+        <f>IFERROR(CC37-BO37,"")</f>
+        <v/>
+      </c>
+      <c r="CR37" s="17">
+        <f>IFERROR(CD37-BP37,"")</f>
+        <v/>
+      </c>
+      <c r="CS37" s="17">
+        <f>IFERROR(CE37-BQ37,"")</f>
+        <v/>
+      </c>
+      <c r="CT37" s="17">
+        <f>IFERROR(CF37-BR37,"")</f>
+        <v/>
+      </c>
+      <c r="CU37" s="17">
+        <f>IFERROR(CG37-BS37,"")</f>
+        <v/>
+      </c>
+      <c r="CV37" s="17">
+        <f>IFERROR(CH37-BT37,"")</f>
         <v/>
       </c>
     </row>
@@ -4900,8 +5578,8 @@
       <c r="L38" s="16" t="n"/>
       <c r="M38" s="16" t="n"/>
       <c r="N38" s="16" t="n"/>
+      <c r="O38" s="16" t="n"/>
       <c r="P38" s="16" t="n"/>
-      <c r="Q38" s="16" t="n"/>
       <c r="R38" s="16" t="n"/>
       <c r="S38" s="16" t="n"/>
       <c r="T38" s="16" t="n"/>
@@ -4911,10 +5589,10 @@
       <c r="X38" s="16" t="n"/>
       <c r="Y38" s="16" t="n"/>
       <c r="Z38" s="16" t="n"/>
-      <c r="AB38" s="17" t="n"/>
-      <c r="AC38" s="17" t="n"/>
-      <c r="AD38" s="17" t="n"/>
-      <c r="AE38" s="17" t="n"/>
+      <c r="AA38" s="16" t="n"/>
+      <c r="AB38" s="16" t="n"/>
+      <c r="AC38" s="16" t="n"/>
+      <c r="AD38" s="16" t="n"/>
       <c r="AF38" s="17" t="n"/>
       <c r="AG38" s="17" t="n"/>
       <c r="AH38" s="17" t="n"/>
@@ -4922,28 +5600,29 @@
       <c r="AJ38" s="17" t="n"/>
       <c r="AK38" s="17" t="n"/>
       <c r="AL38" s="17" t="n"/>
-      <c r="AN38" s="16" t="n"/>
-      <c r="AO38" s="16" t="n"/>
-      <c r="AP38" s="16" t="n"/>
-      <c r="AQ38" s="16" t="n"/>
-      <c r="AR38" s="16" t="n"/>
-      <c r="AS38" s="16" t="n"/>
+      <c r="AM38" s="17" t="n"/>
+      <c r="AN38" s="17" t="n"/>
+      <c r="AO38" s="17" t="n"/>
+      <c r="AP38" s="17" t="n"/>
+      <c r="AQ38" s="17" t="n"/>
+      <c r="AR38" s="17" t="n"/>
       <c r="AT38" s="16" t="n"/>
       <c r="AU38" s="16" t="n"/>
       <c r="AV38" s="16" t="n"/>
       <c r="AW38" s="16" t="n"/>
       <c r="AX38" s="16" t="n"/>
-      <c r="AZ38" s="18" t="n"/>
-      <c r="BA38" s="18" t="n"/>
-      <c r="BB38" s="18" t="n"/>
-      <c r="BC38" s="18" t="n"/>
-      <c r="BD38" s="18" t="n"/>
-      <c r="BE38" s="18" t="n"/>
-      <c r="BF38" s="18" t="n"/>
-      <c r="BG38" s="18" t="n"/>
+      <c r="AY38" s="16" t="n"/>
+      <c r="AZ38" s="16" t="n"/>
+      <c r="BA38" s="16" t="n"/>
+      <c r="BB38" s="16" t="n"/>
+      <c r="BC38" s="16" t="n"/>
+      <c r="BD38" s="16" t="n"/>
+      <c r="BE38" s="16" t="n"/>
+      <c r="BF38" s="16" t="n"/>
       <c r="BH38" s="18" t="n"/>
       <c r="BI38" s="18" t="n"/>
       <c r="BJ38" s="18" t="n"/>
+      <c r="BK38" s="18" t="n"/>
       <c r="BL38" s="18" t="n"/>
       <c r="BM38" s="18" t="n"/>
       <c r="BN38" s="18" t="n"/>
@@ -4953,50 +5632,69 @@
       <c r="BR38" s="18" t="n"/>
       <c r="BS38" s="18" t="n"/>
       <c r="BT38" s="18" t="n"/>
-      <c r="BU38" s="18" t="n"/>
       <c r="BV38" s="18" t="n"/>
-      <c r="BX38" s="17">
-        <f>IFERROR(BL38-AZ38,"")</f>
-        <v/>
-      </c>
-      <c r="BY38" s="17">
-        <f>IFERROR(BM38-BA38,"")</f>
-        <v/>
-      </c>
-      <c r="BZ38" s="17">
-        <f>IFERROR(BN38-BB38,"")</f>
-        <v/>
-      </c>
-      <c r="CA38" s="17">
-        <f>IFERROR(BO38-BC38,"")</f>
-        <v/>
-      </c>
-      <c r="CB38" s="17">
-        <f>IFERROR(BP38-BD38,"")</f>
-        <v/>
-      </c>
-      <c r="CC38" s="17">
-        <f>IFERROR(BQ38-BE38,"")</f>
-        <v/>
-      </c>
-      <c r="CD38" s="17">
-        <f>IFERROR(BR38-BF38,"")</f>
-        <v/>
-      </c>
-      <c r="CE38" s="17">
-        <f>IFERROR(BS38-BG38,"")</f>
-        <v/>
-      </c>
-      <c r="CF38" s="17">
-        <f>IFERROR(BT38-BH38,"")</f>
-        <v/>
-      </c>
-      <c r="CG38" s="17">
-        <f>IFERROR(BU38-BI38,"")</f>
-        <v/>
-      </c>
-      <c r="CH38" s="17">
-        <f>IFERROR(BV38-BJ38,"")</f>
+      <c r="BW38" s="18" t="n"/>
+      <c r="BX38" s="18" t="n"/>
+      <c r="BY38" s="18" t="n"/>
+      <c r="BZ38" s="18" t="n"/>
+      <c r="CA38" s="18" t="n"/>
+      <c r="CB38" s="18" t="n"/>
+      <c r="CC38" s="18" t="n"/>
+      <c r="CD38" s="18" t="n"/>
+      <c r="CE38" s="18" t="n"/>
+      <c r="CF38" s="18" t="n"/>
+      <c r="CG38" s="18" t="n"/>
+      <c r="CH38" s="18" t="n"/>
+      <c r="CJ38" s="17">
+        <f>IFERROR(BV38-BH38,"")</f>
+        <v/>
+      </c>
+      <c r="CK38" s="17">
+        <f>IFERROR(BW38-BI38,"")</f>
+        <v/>
+      </c>
+      <c r="CL38" s="17">
+        <f>IFERROR(BX38-BJ38,"")</f>
+        <v/>
+      </c>
+      <c r="CM38" s="17">
+        <f>IFERROR(BY38-BK38,"")</f>
+        <v/>
+      </c>
+      <c r="CN38" s="17">
+        <f>IFERROR(BZ38-BL38,"")</f>
+        <v/>
+      </c>
+      <c r="CO38" s="17">
+        <f>IFERROR(CA38-BM38,"")</f>
+        <v/>
+      </c>
+      <c r="CP38" s="17">
+        <f>IFERROR(CB38-BN38,"")</f>
+        <v/>
+      </c>
+      <c r="CQ38" s="17">
+        <f>IFERROR(CC38-BO38,"")</f>
+        <v/>
+      </c>
+      <c r="CR38" s="17">
+        <f>IFERROR(CD38-BP38,"")</f>
+        <v/>
+      </c>
+      <c r="CS38" s="17">
+        <f>IFERROR(CE38-BQ38,"")</f>
+        <v/>
+      </c>
+      <c r="CT38" s="17">
+        <f>IFERROR(CF38-BR38,"")</f>
+        <v/>
+      </c>
+      <c r="CU38" s="17">
+        <f>IFERROR(CG38-BS38,"")</f>
+        <v/>
+      </c>
+      <c r="CV38" s="17">
+        <f>IFERROR(CH38-BT38,"")</f>
         <v/>
       </c>
     </row>
@@ -5020,8 +5718,8 @@
       <c r="L39" s="16" t="n"/>
       <c r="M39" s="16" t="n"/>
       <c r="N39" s="16" t="n"/>
+      <c r="O39" s="16" t="n"/>
       <c r="P39" s="16" t="n"/>
-      <c r="Q39" s="16" t="n"/>
       <c r="R39" s="16" t="n"/>
       <c r="S39" s="16" t="n"/>
       <c r="T39" s="16" t="n"/>
@@ -5031,10 +5729,10 @@
       <c r="X39" s="16" t="n"/>
       <c r="Y39" s="16" t="n"/>
       <c r="Z39" s="16" t="n"/>
-      <c r="AB39" s="17" t="n"/>
-      <c r="AC39" s="17" t="n"/>
-      <c r="AD39" s="17" t="n"/>
-      <c r="AE39" s="17" t="n"/>
+      <c r="AA39" s="16" t="n"/>
+      <c r="AB39" s="16" t="n"/>
+      <c r="AC39" s="16" t="n"/>
+      <c r="AD39" s="16" t="n"/>
       <c r="AF39" s="17" t="n"/>
       <c r="AG39" s="17" t="n"/>
       <c r="AH39" s="17" t="n"/>
@@ -5042,28 +5740,29 @@
       <c r="AJ39" s="17" t="n"/>
       <c r="AK39" s="17" t="n"/>
       <c r="AL39" s="17" t="n"/>
-      <c r="AN39" s="16" t="n"/>
-      <c r="AO39" s="16" t="n"/>
-      <c r="AP39" s="16" t="n"/>
-      <c r="AQ39" s="16" t="n"/>
-      <c r="AR39" s="16" t="n"/>
-      <c r="AS39" s="16" t="n"/>
+      <c r="AM39" s="17" t="n"/>
+      <c r="AN39" s="17" t="n"/>
+      <c r="AO39" s="17" t="n"/>
+      <c r="AP39" s="17" t="n"/>
+      <c r="AQ39" s="17" t="n"/>
+      <c r="AR39" s="17" t="n"/>
       <c r="AT39" s="16" t="n"/>
       <c r="AU39" s="16" t="n"/>
       <c r="AV39" s="16" t="n"/>
       <c r="AW39" s="16" t="n"/>
       <c r="AX39" s="16" t="n"/>
-      <c r="AZ39" s="18" t="n"/>
-      <c r="BA39" s="18" t="n"/>
-      <c r="BB39" s="18" t="n"/>
-      <c r="BC39" s="18" t="n"/>
-      <c r="BD39" s="18" t="n"/>
-      <c r="BE39" s="18" t="n"/>
-      <c r="BF39" s="18" t="n"/>
-      <c r="BG39" s="18" t="n"/>
+      <c r="AY39" s="16" t="n"/>
+      <c r="AZ39" s="16" t="n"/>
+      <c r="BA39" s="16" t="n"/>
+      <c r="BB39" s="16" t="n"/>
+      <c r="BC39" s="16" t="n"/>
+      <c r="BD39" s="16" t="n"/>
+      <c r="BE39" s="16" t="n"/>
+      <c r="BF39" s="16" t="n"/>
       <c r="BH39" s="18" t="n"/>
       <c r="BI39" s="18" t="n"/>
       <c r="BJ39" s="18" t="n"/>
+      <c r="BK39" s="18" t="n"/>
       <c r="BL39" s="18" t="n"/>
       <c r="BM39" s="18" t="n"/>
       <c r="BN39" s="18" t="n"/>
@@ -5073,50 +5772,69 @@
       <c r="BR39" s="18" t="n"/>
       <c r="BS39" s="18" t="n"/>
       <c r="BT39" s="18" t="n"/>
-      <c r="BU39" s="18" t="n"/>
       <c r="BV39" s="18" t="n"/>
-      <c r="BX39" s="17">
-        <f>IFERROR(BL39-AZ39,"")</f>
-        <v/>
-      </c>
-      <c r="BY39" s="17">
-        <f>IFERROR(BM39-BA39,"")</f>
-        <v/>
-      </c>
-      <c r="BZ39" s="17">
-        <f>IFERROR(BN39-BB39,"")</f>
-        <v/>
-      </c>
-      <c r="CA39" s="17">
-        <f>IFERROR(BO39-BC39,"")</f>
-        <v/>
-      </c>
-      <c r="CB39" s="17">
-        <f>IFERROR(BP39-BD39,"")</f>
-        <v/>
-      </c>
-      <c r="CC39" s="17">
-        <f>IFERROR(BQ39-BE39,"")</f>
-        <v/>
-      </c>
-      <c r="CD39" s="17">
-        <f>IFERROR(BR39-BF39,"")</f>
-        <v/>
-      </c>
-      <c r="CE39" s="17">
-        <f>IFERROR(BS39-BG39,"")</f>
-        <v/>
-      </c>
-      <c r="CF39" s="17">
-        <f>IFERROR(BT39-BH39,"")</f>
-        <v/>
-      </c>
-      <c r="CG39" s="17">
-        <f>IFERROR(BU39-BI39,"")</f>
-        <v/>
-      </c>
-      <c r="CH39" s="17">
-        <f>IFERROR(BV39-BJ39,"")</f>
+      <c r="BW39" s="18" t="n"/>
+      <c r="BX39" s="18" t="n"/>
+      <c r="BY39" s="18" t="n"/>
+      <c r="BZ39" s="18" t="n"/>
+      <c r="CA39" s="18" t="n"/>
+      <c r="CB39" s="18" t="n"/>
+      <c r="CC39" s="18" t="n"/>
+      <c r="CD39" s="18" t="n"/>
+      <c r="CE39" s="18" t="n"/>
+      <c r="CF39" s="18" t="n"/>
+      <c r="CG39" s="18" t="n"/>
+      <c r="CH39" s="18" t="n"/>
+      <c r="CJ39" s="17">
+        <f>IFERROR(BV39-BH39,"")</f>
+        <v/>
+      </c>
+      <c r="CK39" s="17">
+        <f>IFERROR(BW39-BI39,"")</f>
+        <v/>
+      </c>
+      <c r="CL39" s="17">
+        <f>IFERROR(BX39-BJ39,"")</f>
+        <v/>
+      </c>
+      <c r="CM39" s="17">
+        <f>IFERROR(BY39-BK39,"")</f>
+        <v/>
+      </c>
+      <c r="CN39" s="17">
+        <f>IFERROR(BZ39-BL39,"")</f>
+        <v/>
+      </c>
+      <c r="CO39" s="17">
+        <f>IFERROR(CA39-BM39,"")</f>
+        <v/>
+      </c>
+      <c r="CP39" s="17">
+        <f>IFERROR(CB39-BN39,"")</f>
+        <v/>
+      </c>
+      <c r="CQ39" s="17">
+        <f>IFERROR(CC39-BO39,"")</f>
+        <v/>
+      </c>
+      <c r="CR39" s="17">
+        <f>IFERROR(CD39-BP39,"")</f>
+        <v/>
+      </c>
+      <c r="CS39" s="17">
+        <f>IFERROR(CE39-BQ39,"")</f>
+        <v/>
+      </c>
+      <c r="CT39" s="17">
+        <f>IFERROR(CF39-BR39,"")</f>
+        <v/>
+      </c>
+      <c r="CU39" s="17">
+        <f>IFERROR(CG39-BS39,"")</f>
+        <v/>
+      </c>
+      <c r="CV39" s="17">
+        <f>IFERROR(CH39-BT39,"")</f>
         <v/>
       </c>
     </row>
@@ -5140,8 +5858,8 @@
       <c r="L40" s="16" t="n"/>
       <c r="M40" s="16" t="n"/>
       <c r="N40" s="16" t="n"/>
+      <c r="O40" s="16" t="n"/>
       <c r="P40" s="16" t="n"/>
-      <c r="Q40" s="16" t="n"/>
       <c r="R40" s="16" t="n"/>
       <c r="S40" s="16" t="n"/>
       <c r="T40" s="16" t="n"/>
@@ -5151,10 +5869,10 @@
       <c r="X40" s="16" t="n"/>
       <c r="Y40" s="16" t="n"/>
       <c r="Z40" s="16" t="n"/>
-      <c r="AB40" s="17" t="n"/>
-      <c r="AC40" s="17" t="n"/>
-      <c r="AD40" s="17" t="n"/>
-      <c r="AE40" s="17" t="n"/>
+      <c r="AA40" s="16" t="n"/>
+      <c r="AB40" s="16" t="n"/>
+      <c r="AC40" s="16" t="n"/>
+      <c r="AD40" s="16" t="n"/>
       <c r="AF40" s="17" t="n"/>
       <c r="AG40" s="17" t="n"/>
       <c r="AH40" s="17" t="n"/>
@@ -5162,28 +5880,29 @@
       <c r="AJ40" s="17" t="n"/>
       <c r="AK40" s="17" t="n"/>
       <c r="AL40" s="17" t="n"/>
-      <c r="AN40" s="16" t="n"/>
-      <c r="AO40" s="16" t="n"/>
-      <c r="AP40" s="16" t="n"/>
-      <c r="AQ40" s="16" t="n"/>
-      <c r="AR40" s="16" t="n"/>
-      <c r="AS40" s="16" t="n"/>
+      <c r="AM40" s="17" t="n"/>
+      <c r="AN40" s="17" t="n"/>
+      <c r="AO40" s="17" t="n"/>
+      <c r="AP40" s="17" t="n"/>
+      <c r="AQ40" s="17" t="n"/>
+      <c r="AR40" s="17" t="n"/>
       <c r="AT40" s="16" t="n"/>
       <c r="AU40" s="16" t="n"/>
       <c r="AV40" s="16" t="n"/>
       <c r="AW40" s="16" t="n"/>
       <c r="AX40" s="16" t="n"/>
-      <c r="AZ40" s="18" t="n"/>
-      <c r="BA40" s="18" t="n"/>
-      <c r="BB40" s="18" t="n"/>
-      <c r="BC40" s="18" t="n"/>
-      <c r="BD40" s="18" t="n"/>
-      <c r="BE40" s="18" t="n"/>
-      <c r="BF40" s="18" t="n"/>
-      <c r="BG40" s="18" t="n"/>
+      <c r="AY40" s="16" t="n"/>
+      <c r="AZ40" s="16" t="n"/>
+      <c r="BA40" s="16" t="n"/>
+      <c r="BB40" s="16" t="n"/>
+      <c r="BC40" s="16" t="n"/>
+      <c r="BD40" s="16" t="n"/>
+      <c r="BE40" s="16" t="n"/>
+      <c r="BF40" s="16" t="n"/>
       <c r="BH40" s="18" t="n"/>
       <c r="BI40" s="18" t="n"/>
       <c r="BJ40" s="18" t="n"/>
+      <c r="BK40" s="18" t="n"/>
       <c r="BL40" s="18" t="n"/>
       <c r="BM40" s="18" t="n"/>
       <c r="BN40" s="18" t="n"/>
@@ -5193,50 +5912,69 @@
       <c r="BR40" s="18" t="n"/>
       <c r="BS40" s="18" t="n"/>
       <c r="BT40" s="18" t="n"/>
-      <c r="BU40" s="18" t="n"/>
       <c r="BV40" s="18" t="n"/>
-      <c r="BX40" s="17">
-        <f>IFERROR(BL40-AZ40,"")</f>
-        <v/>
-      </c>
-      <c r="BY40" s="17">
-        <f>IFERROR(BM40-BA40,"")</f>
-        <v/>
-      </c>
-      <c r="BZ40" s="17">
-        <f>IFERROR(BN40-BB40,"")</f>
-        <v/>
-      </c>
-      <c r="CA40" s="17">
-        <f>IFERROR(BO40-BC40,"")</f>
-        <v/>
-      </c>
-      <c r="CB40" s="17">
-        <f>IFERROR(BP40-BD40,"")</f>
-        <v/>
-      </c>
-      <c r="CC40" s="17">
-        <f>IFERROR(BQ40-BE40,"")</f>
-        <v/>
-      </c>
-      <c r="CD40" s="17">
-        <f>IFERROR(BR40-BF40,"")</f>
-        <v/>
-      </c>
-      <c r="CE40" s="17">
-        <f>IFERROR(BS40-BG40,"")</f>
-        <v/>
-      </c>
-      <c r="CF40" s="17">
-        <f>IFERROR(BT40-BH40,"")</f>
-        <v/>
-      </c>
-      <c r="CG40" s="17">
-        <f>IFERROR(BU40-BI40,"")</f>
-        <v/>
-      </c>
-      <c r="CH40" s="17">
-        <f>IFERROR(BV40-BJ40,"")</f>
+      <c r="BW40" s="18" t="n"/>
+      <c r="BX40" s="18" t="n"/>
+      <c r="BY40" s="18" t="n"/>
+      <c r="BZ40" s="18" t="n"/>
+      <c r="CA40" s="18" t="n"/>
+      <c r="CB40" s="18" t="n"/>
+      <c r="CC40" s="18" t="n"/>
+      <c r="CD40" s="18" t="n"/>
+      <c r="CE40" s="18" t="n"/>
+      <c r="CF40" s="18" t="n"/>
+      <c r="CG40" s="18" t="n"/>
+      <c r="CH40" s="18" t="n"/>
+      <c r="CJ40" s="17">
+        <f>IFERROR(BV40-BH40,"")</f>
+        <v/>
+      </c>
+      <c r="CK40" s="17">
+        <f>IFERROR(BW40-BI40,"")</f>
+        <v/>
+      </c>
+      <c r="CL40" s="17">
+        <f>IFERROR(BX40-BJ40,"")</f>
+        <v/>
+      </c>
+      <c r="CM40" s="17">
+        <f>IFERROR(BY40-BK40,"")</f>
+        <v/>
+      </c>
+      <c r="CN40" s="17">
+        <f>IFERROR(BZ40-BL40,"")</f>
+        <v/>
+      </c>
+      <c r="CO40" s="17">
+        <f>IFERROR(CA40-BM40,"")</f>
+        <v/>
+      </c>
+      <c r="CP40" s="17">
+        <f>IFERROR(CB40-BN40,"")</f>
+        <v/>
+      </c>
+      <c r="CQ40" s="17">
+        <f>IFERROR(CC40-BO40,"")</f>
+        <v/>
+      </c>
+      <c r="CR40" s="17">
+        <f>IFERROR(CD40-BP40,"")</f>
+        <v/>
+      </c>
+      <c r="CS40" s="17">
+        <f>IFERROR(CE40-BQ40,"")</f>
+        <v/>
+      </c>
+      <c r="CT40" s="17">
+        <f>IFERROR(CF40-BR40,"")</f>
+        <v/>
+      </c>
+      <c r="CU40" s="17">
+        <f>IFERROR(CG40-BS40,"")</f>
+        <v/>
+      </c>
+      <c r="CV40" s="17">
+        <f>IFERROR(CH40-BT40,"")</f>
         <v/>
       </c>
     </row>
@@ -5260,8 +5998,8 @@
       <c r="L41" s="16" t="n"/>
       <c r="M41" s="16" t="n"/>
       <c r="N41" s="16" t="n"/>
+      <c r="O41" s="16" t="n"/>
       <c r="P41" s="16" t="n"/>
-      <c r="Q41" s="16" t="n"/>
       <c r="R41" s="16" t="n"/>
       <c r="S41" s="16" t="n"/>
       <c r="T41" s="16" t="n"/>
@@ -5271,10 +6009,10 @@
       <c r="X41" s="16" t="n"/>
       <c r="Y41" s="16" t="n"/>
       <c r="Z41" s="16" t="n"/>
-      <c r="AB41" s="17" t="n"/>
-      <c r="AC41" s="17" t="n"/>
-      <c r="AD41" s="17" t="n"/>
-      <c r="AE41" s="17" t="n"/>
+      <c r="AA41" s="16" t="n"/>
+      <c r="AB41" s="16" t="n"/>
+      <c r="AC41" s="16" t="n"/>
+      <c r="AD41" s="16" t="n"/>
       <c r="AF41" s="17" t="n"/>
       <c r="AG41" s="17" t="n"/>
       <c r="AH41" s="17" t="n"/>
@@ -5282,28 +6020,29 @@
       <c r="AJ41" s="17" t="n"/>
       <c r="AK41" s="17" t="n"/>
       <c r="AL41" s="17" t="n"/>
-      <c r="AN41" s="16" t="n"/>
-      <c r="AO41" s="16" t="n"/>
-      <c r="AP41" s="16" t="n"/>
-      <c r="AQ41" s="16" t="n"/>
-      <c r="AR41" s="16" t="n"/>
-      <c r="AS41" s="16" t="n"/>
+      <c r="AM41" s="17" t="n"/>
+      <c r="AN41" s="17" t="n"/>
+      <c r="AO41" s="17" t="n"/>
+      <c r="AP41" s="17" t="n"/>
+      <c r="AQ41" s="17" t="n"/>
+      <c r="AR41" s="17" t="n"/>
       <c r="AT41" s="16" t="n"/>
       <c r="AU41" s="16" t="n"/>
       <c r="AV41" s="16" t="n"/>
       <c r="AW41" s="16" t="n"/>
       <c r="AX41" s="16" t="n"/>
-      <c r="AZ41" s="18" t="n"/>
-      <c r="BA41" s="18" t="n"/>
-      <c r="BB41" s="18" t="n"/>
-      <c r="BC41" s="18" t="n"/>
-      <c r="BD41" s="18" t="n"/>
-      <c r="BE41" s="18" t="n"/>
-      <c r="BF41" s="18" t="n"/>
-      <c r="BG41" s="18" t="n"/>
+      <c r="AY41" s="16" t="n"/>
+      <c r="AZ41" s="16" t="n"/>
+      <c r="BA41" s="16" t="n"/>
+      <c r="BB41" s="16" t="n"/>
+      <c r="BC41" s="16" t="n"/>
+      <c r="BD41" s="16" t="n"/>
+      <c r="BE41" s="16" t="n"/>
+      <c r="BF41" s="16" t="n"/>
       <c r="BH41" s="18" t="n"/>
       <c r="BI41" s="18" t="n"/>
       <c r="BJ41" s="18" t="n"/>
+      <c r="BK41" s="18" t="n"/>
       <c r="BL41" s="18" t="n"/>
       <c r="BM41" s="18" t="n"/>
       <c r="BN41" s="18" t="n"/>
@@ -5313,50 +6052,69 @@
       <c r="BR41" s="18" t="n"/>
       <c r="BS41" s="18" t="n"/>
       <c r="BT41" s="18" t="n"/>
-      <c r="BU41" s="18" t="n"/>
       <c r="BV41" s="18" t="n"/>
-      <c r="BX41" s="17">
-        <f>IFERROR(BL41-AZ41,"")</f>
-        <v/>
-      </c>
-      <c r="BY41" s="17">
-        <f>IFERROR(BM41-BA41,"")</f>
-        <v/>
-      </c>
-      <c r="BZ41" s="17">
-        <f>IFERROR(BN41-BB41,"")</f>
-        <v/>
-      </c>
-      <c r="CA41" s="17">
-        <f>IFERROR(BO41-BC41,"")</f>
-        <v/>
-      </c>
-      <c r="CB41" s="17">
-        <f>IFERROR(BP41-BD41,"")</f>
-        <v/>
-      </c>
-      <c r="CC41" s="17">
-        <f>IFERROR(BQ41-BE41,"")</f>
-        <v/>
-      </c>
-      <c r="CD41" s="17">
-        <f>IFERROR(BR41-BF41,"")</f>
-        <v/>
-      </c>
-      <c r="CE41" s="17">
-        <f>IFERROR(BS41-BG41,"")</f>
-        <v/>
-      </c>
-      <c r="CF41" s="17">
-        <f>IFERROR(BT41-BH41,"")</f>
-        <v/>
-      </c>
-      <c r="CG41" s="17">
-        <f>IFERROR(BU41-BI41,"")</f>
-        <v/>
-      </c>
-      <c r="CH41" s="17">
-        <f>IFERROR(BV41-BJ41,"")</f>
+      <c r="BW41" s="18" t="n"/>
+      <c r="BX41" s="18" t="n"/>
+      <c r="BY41" s="18" t="n"/>
+      <c r="BZ41" s="18" t="n"/>
+      <c r="CA41" s="18" t="n"/>
+      <c r="CB41" s="18" t="n"/>
+      <c r="CC41" s="18" t="n"/>
+      <c r="CD41" s="18" t="n"/>
+      <c r="CE41" s="18" t="n"/>
+      <c r="CF41" s="18" t="n"/>
+      <c r="CG41" s="18" t="n"/>
+      <c r="CH41" s="18" t="n"/>
+      <c r="CJ41" s="17">
+        <f>IFERROR(BV41-BH41,"")</f>
+        <v/>
+      </c>
+      <c r="CK41" s="17">
+        <f>IFERROR(BW41-BI41,"")</f>
+        <v/>
+      </c>
+      <c r="CL41" s="17">
+        <f>IFERROR(BX41-BJ41,"")</f>
+        <v/>
+      </c>
+      <c r="CM41" s="17">
+        <f>IFERROR(BY41-BK41,"")</f>
+        <v/>
+      </c>
+      <c r="CN41" s="17">
+        <f>IFERROR(BZ41-BL41,"")</f>
+        <v/>
+      </c>
+      <c r="CO41" s="17">
+        <f>IFERROR(CA41-BM41,"")</f>
+        <v/>
+      </c>
+      <c r="CP41" s="17">
+        <f>IFERROR(CB41-BN41,"")</f>
+        <v/>
+      </c>
+      <c r="CQ41" s="17">
+        <f>IFERROR(CC41-BO41,"")</f>
+        <v/>
+      </c>
+      <c r="CR41" s="17">
+        <f>IFERROR(CD41-BP41,"")</f>
+        <v/>
+      </c>
+      <c r="CS41" s="17">
+        <f>IFERROR(CE41-BQ41,"")</f>
+        <v/>
+      </c>
+      <c r="CT41" s="17">
+        <f>IFERROR(CF41-BR41,"")</f>
+        <v/>
+      </c>
+      <c r="CU41" s="17">
+        <f>IFERROR(CG41-BS41,"")</f>
+        <v/>
+      </c>
+      <c r="CV41" s="17">
+        <f>IFERROR(CH41-BT41,"")</f>
         <v/>
       </c>
     </row>
@@ -5411,12 +6169,12 @@
         <f>SUM(N9:N41)</f>
         <v/>
       </c>
-      <c r="P42" s="22">
+      <c r="O42" s="21">
+        <f>SUM(O9:O41)</f>
+        <v/>
+      </c>
+      <c r="P42" s="21">
         <f>SUM(P9:P41)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="22">
-        <f>SUM(Q9:Q41)</f>
         <v/>
       </c>
       <c r="R42" s="22">
@@ -5455,20 +6213,20 @@
         <f>SUM(Z9:Z41)</f>
         <v/>
       </c>
-      <c r="AB42" s="23">
+      <c r="AA42" s="22">
+        <f>SUM(AA9:AA41)</f>
+        <v/>
+      </c>
+      <c r="AB42" s="22">
         <f>SUM(AB9:AB41)</f>
         <v/>
       </c>
-      <c r="AC42" s="23">
+      <c r="AC42" s="22">
         <f>SUM(AC9:AC41)</f>
         <v/>
       </c>
-      <c r="AD42" s="23">
+      <c r="AD42" s="22">
         <f>SUM(AD9:AD41)</f>
-        <v/>
-      </c>
-      <c r="AE42" s="23">
-        <f>SUM(AE9:AE41)</f>
         <v/>
       </c>
       <c r="AF42" s="23">
@@ -5499,28 +6257,28 @@
         <f>SUM(AL9:AL41)</f>
         <v/>
       </c>
-      <c r="AN42" s="24">
-        <f>IF(COUNT(AN9:AN41)=0,"",SUM(AN9:AN41))</f>
-        <v/>
-      </c>
-      <c r="AO42" s="24">
-        <f>IF(COUNT(AO9:AO41)=0,"",SUM(AO9:AO41))</f>
-        <v/>
-      </c>
-      <c r="AP42" s="24">
-        <f>IF(COUNT(AP9:AP41)=0,"",SUM(AP9:AP41))</f>
-        <v/>
-      </c>
-      <c r="AQ42" s="24">
-        <f>IF(COUNT(AQ9:AQ41)=0,"",SUM(AQ9:AQ41))</f>
-        <v/>
-      </c>
-      <c r="AR42" s="24">
-        <f>IF(COUNT(AR9:AR41)=0,"",SUM(AR9:AR41))</f>
-        <v/>
-      </c>
-      <c r="AS42" s="24">
-        <f>IF(COUNT(AS9:AS41)=0,"",SUM(AS9:AS41))</f>
+      <c r="AM42" s="23">
+        <f>SUM(AM9:AM41)</f>
+        <v/>
+      </c>
+      <c r="AN42" s="23">
+        <f>SUM(AN9:AN41)</f>
+        <v/>
+      </c>
+      <c r="AO42" s="23">
+        <f>SUM(AO9:AO41)</f>
+        <v/>
+      </c>
+      <c r="AP42" s="23">
+        <f>SUM(AP9:AP41)</f>
+        <v/>
+      </c>
+      <c r="AQ42" s="23">
+        <f>SUM(AQ9:AQ41)</f>
+        <v/>
+      </c>
+      <c r="AR42" s="23">
+        <f>SUM(AR9:AR41)</f>
         <v/>
       </c>
       <c r="AT42" s="24">
@@ -5543,36 +6301,36 @@
         <f>IF(COUNT(AX9:AX41)=0,"",SUM(AX9:AX41))</f>
         <v/>
       </c>
-      <c r="AZ42" s="25">
+      <c r="AY42" s="24">
+        <f>IF(COUNT(AY9:AY41)=0,"",SUM(AY9:AY41))</f>
+        <v/>
+      </c>
+      <c r="AZ42" s="24">
         <f>IF(COUNT(AZ9:AZ41)=0,"",SUM(AZ9:AZ41))</f>
         <v/>
       </c>
-      <c r="BA42" s="25">
+      <c r="BA42" s="24">
         <f>IF(COUNT(BA9:BA41)=0,"",SUM(BA9:BA41))</f>
         <v/>
       </c>
-      <c r="BB42" s="25">
+      <c r="BB42" s="24">
         <f>IF(COUNT(BB9:BB41)=0,"",SUM(BB9:BB41))</f>
         <v/>
       </c>
-      <c r="BC42" s="25">
+      <c r="BC42" s="24">
         <f>IF(COUNT(BC9:BC41)=0,"",SUM(BC9:BC41))</f>
         <v/>
       </c>
-      <c r="BD42" s="25">
+      <c r="BD42" s="24">
         <f>IF(COUNT(BD9:BD41)=0,"",SUM(BD9:BD41))</f>
         <v/>
       </c>
-      <c r="BE42" s="25">
+      <c r="BE42" s="24">
         <f>IF(COUNT(BE9:BE41)=0,"",SUM(BE9:BE41))</f>
         <v/>
       </c>
-      <c r="BF42" s="25">
+      <c r="BF42" s="24">
         <f>IF(COUNT(BF9:BF41)=0,"",SUM(BF9:BF41))</f>
-        <v/>
-      </c>
-      <c r="BG42" s="25">
-        <f>IF(COUNT(BG9:BG41)=0,"",SUM(BG9:BG41))</f>
         <v/>
       </c>
       <c r="BH42" s="25">
@@ -5587,6 +6345,10 @@
         <f>IF(COUNT(BJ9:BJ41)=0,"",SUM(BJ9:BJ41))</f>
         <v/>
       </c>
+      <c r="BK42" s="25">
+        <f>IF(COUNT(BK9:BK41)=0,"",SUM(BK9:BK41))</f>
+        <v/>
+      </c>
       <c r="BL42" s="25">
         <f>IF(COUNT(BL9:BL41)=0,"",SUM(BL9:BL41))</f>
         <v/>
@@ -5623,56 +6385,108 @@
         <f>IF(COUNT(BT9:BT41)=0,"",SUM(BT9:BT41))</f>
         <v/>
       </c>
-      <c r="BU42" s="25">
-        <f>IF(COUNT(BU9:BU41)=0,"",SUM(BU9:BU41))</f>
-        <v/>
-      </c>
       <c r="BV42" s="25">
         <f>IF(COUNT(BV9:BV41)=0,"",SUM(BV9:BV41))</f>
         <v/>
       </c>
-      <c r="BX42" s="23">
+      <c r="BW42" s="25">
+        <f>IF(COUNT(BW9:BW41)=0,"",SUM(BW9:BW41))</f>
+        <v/>
+      </c>
+      <c r="BX42" s="25">
         <f>IF(COUNT(BX9:BX41)=0,"",SUM(BX9:BX41))</f>
         <v/>
       </c>
-      <c r="BY42" s="23">
+      <c r="BY42" s="25">
         <f>IF(COUNT(BY9:BY41)=0,"",SUM(BY9:BY41))</f>
         <v/>
       </c>
-      <c r="BZ42" s="23">
+      <c r="BZ42" s="25">
         <f>IF(COUNT(BZ9:BZ41)=0,"",SUM(BZ9:BZ41))</f>
         <v/>
       </c>
-      <c r="CA42" s="23">
+      <c r="CA42" s="25">
         <f>IF(COUNT(CA9:CA41)=0,"",SUM(CA9:CA41))</f>
         <v/>
       </c>
-      <c r="CB42" s="23">
+      <c r="CB42" s="25">
         <f>IF(COUNT(CB9:CB41)=0,"",SUM(CB9:CB41))</f>
         <v/>
       </c>
-      <c r="CC42" s="23">
+      <c r="CC42" s="25">
         <f>IF(COUNT(CC9:CC41)=0,"",SUM(CC9:CC41))</f>
         <v/>
       </c>
-      <c r="CD42" s="23">
+      <c r="CD42" s="25">
         <f>IF(COUNT(CD9:CD41)=0,"",SUM(CD9:CD41))</f>
         <v/>
       </c>
-      <c r="CE42" s="23">
+      <c r="CE42" s="25">
         <f>IF(COUNT(CE9:CE41)=0,"",SUM(CE9:CE41))</f>
         <v/>
       </c>
-      <c r="CF42" s="23">
+      <c r="CF42" s="25">
         <f>IF(COUNT(CF9:CF41)=0,"",SUM(CF9:CF41))</f>
         <v/>
       </c>
-      <c r="CG42" s="23">
+      <c r="CG42" s="25">
         <f>IF(COUNT(CG9:CG41)=0,"",SUM(CG9:CG41))</f>
         <v/>
       </c>
-      <c r="CH42" s="23">
+      <c r="CH42" s="25">
         <f>IF(COUNT(CH9:CH41)=0,"",SUM(CH9:CH41))</f>
+        <v/>
+      </c>
+      <c r="CJ42" s="23">
+        <f>IF(COUNT(CJ9:CJ41)=0,"",SUM(CJ9:CJ41))</f>
+        <v/>
+      </c>
+      <c r="CK42" s="23">
+        <f>IF(COUNT(CK9:CK41)=0,"",SUM(CK9:CK41))</f>
+        <v/>
+      </c>
+      <c r="CL42" s="23">
+        <f>IF(COUNT(CL9:CL41)=0,"",SUM(CL9:CL41))</f>
+        <v/>
+      </c>
+      <c r="CM42" s="23">
+        <f>IF(COUNT(CM9:CM41)=0,"",SUM(CM9:CM41))</f>
+        <v/>
+      </c>
+      <c r="CN42" s="23">
+        <f>IF(COUNT(CN9:CN41)=0,"",SUM(CN9:CN41))</f>
+        <v/>
+      </c>
+      <c r="CO42" s="23">
+        <f>IF(COUNT(CO9:CO41)=0,"",SUM(CO9:CO41))</f>
+        <v/>
+      </c>
+      <c r="CP42" s="23">
+        <f>IF(COUNT(CP9:CP41)=0,"",SUM(CP9:CP41))</f>
+        <v/>
+      </c>
+      <c r="CQ42" s="23">
+        <f>IF(COUNT(CQ9:CQ41)=0,"",SUM(CQ9:CQ41))</f>
+        <v/>
+      </c>
+      <c r="CR42" s="23">
+        <f>IF(COUNT(CR9:CR41)=0,"",SUM(CR9:CR41))</f>
+        <v/>
+      </c>
+      <c r="CS42" s="23">
+        <f>IF(COUNT(CS9:CS41)=0,"",SUM(CS9:CS41))</f>
+        <v/>
+      </c>
+      <c r="CT42" s="23">
+        <f>IF(COUNT(CT9:CT41)=0,"",SUM(CT9:CT41))</f>
+        <v/>
+      </c>
+      <c r="CU42" s="23">
+        <f>IF(COUNT(CU9:CU41)=0,"",SUM(CU9:CU41))</f>
+        <v/>
+      </c>
+      <c r="CV42" s="23">
+        <f>IF(COUNT(CV9:CV41)=0,"",SUM(CV9:CV41))</f>
         <v/>
       </c>
     </row>
@@ -5707,7 +6521,7 @@
     <row r="48">
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Core / Saga / Daily Gift pay daily ∝ weekday/weekend active rate; Night Sky over its daily instances. Non-calendar sources (Ads, Teams, Season Pass, Other, IAPs; River Rush current side) are flat ÷33 — their DIFF is uniform.</t>
+          <t>Core / Saga / Daily Gift pay daily ∝ weekday/weekend active rate; Night Sky over its daily instances. Season Pass (Free) spreads ∝ active rate across its season-lane instances (tier claims are continuous — same treatment as Rainbow Maker). Non-calendar sources (Ads, Teams, Other, IAPs; River Rush current side) are flat ÷33 — their DIFF is uniform.</t>
         </is>
       </c>
     </row>
@@ -5721,7 +6535,7 @@
     <row r="50">
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>NET blocks (AN:CH, per EARNER): ACTUAL SPEND and the gain side come from the data_econ_daily sheet (real per-day telemetry, window-earner denominator). CURRENT NET = actual gain − spend; NEW NET = actual gain + the sim’s day shift (NEW − CURRENT) − spend, so spend is held constant and net Δ == the DIFF block.</t>
+          <t>NET blocks (AT:CH, per EARNER; 13 resources incl. SPT/SPTx2): ACTUAL SPEND and the gain side come from the data_econ_daily sheet (real per-day telemetry, window-earner denominator). CURRENT NET = actual gain − spend; NEW NET = actual gain + the sim’s day shift (NEW − CURRENT) − spend, so spend is held constant and net Δ == the DIFF block.</t>
         </is>
       </c>
     </row>
@@ -5733,7 +6547,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AB9:AL41">
+  <conditionalFormatting sqref="AF9:AR41">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0</formula>
     </cfRule>
@@ -5741,7 +6555,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX9:CH41">
+  <conditionalFormatting sqref="CJ9:CV41">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0</formula>
     </cfRule>
@@ -5749,7 +6563,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:CH41">
+  <conditionalFormatting sqref="B9:CV41">
     <cfRule type="expression" priority="5" dxfId="2">
       <formula>OR($C9="Fri",$C9="Sat",$C9="Sun")</formula>
     </cfRule>
@@ -5762,7 +6576,7 @@
       <formula1>"0-9,10-19,20-39,40-99,100+"</formula1>
     </dataValidation>
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=$CJ$2:$CJ$27</formula1>
+      <formula1>=$CX$2:$CX$27</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
